--- a/data/COMPRAS_PENDENTES.xlsx
+++ b/data/COMPRAS_PENDENTES.xlsx
@@ -502,7 +502,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -534,7 +534,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -566,7 +566,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -630,7 +630,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -662,7 +662,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -790,7 +790,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -982,7 +982,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -1046,7 +1046,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -1110,7 +1110,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -1206,7 +1206,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -1334,7 +1334,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -1366,7 +1366,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -1398,7 +1398,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -1462,7 +1462,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -1494,7 +1494,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -1526,7 +1526,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -1558,7 +1558,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -1590,7 +1590,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -1622,7 +1622,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -1686,7 +1686,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -1782,7 +1782,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -2070,7 +2070,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -2102,7 +2102,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -2294,7 +2294,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -2390,7 +2390,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -2422,7 +2422,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -2454,17 +2454,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="74" customHeight="1" ht="20">
       <c r="A74" s="1" t="n">
-        <v>1607866</v>
+        <v>1604593</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C74" s="1" t="n">
         <v>9584</v>
@@ -2479,24 +2479,24 @@
         </is>
       </c>
       <c r="E74" s="1" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/11/2026</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="75" customHeight="1" ht="20">
       <c r="A75" s="1" t="n">
-        <v>1604593</v>
+        <v>1607866</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C75" s="1" t="n">
         <v>9584</v>
@@ -2511,14 +2511,14 @@
         </is>
       </c>
       <c r="E75" s="1" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">19/11/2026</t>
           </r>
         </is>
       </c>
@@ -2550,7 +2550,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -2646,7 +2646,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -2742,7 +2742,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -2774,7 +2774,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -2934,7 +2934,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -3062,7 +3062,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -3318,7 +3318,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -3670,7 +3670,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -3862,7 +3862,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -3894,7 +3894,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -3958,7 +3958,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -3990,7 +3990,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -4086,7 +4086,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -4182,7 +4182,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -4214,7 +4214,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -4278,7 +4278,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -4342,7 +4342,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -4374,7 +4374,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -4886,7 +4886,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -5206,7 +5206,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -5238,7 +5238,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -5270,7 +5270,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -5494,7 +5494,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -5750,7 +5750,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -6134,7 +6134,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -6902,7 +6902,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -7190,7 +7190,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -7734,7 +7734,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="244" customHeight="1" ht="20">
       <c r="A244" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B244" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C244" s="1" t="n">
         <v>12593</v>
@@ -7919,24 +7919,24 @@
         </is>
       </c>
       <c r="E244" s="1" t="n">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="F244" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="245" customHeight="1" ht="20">
       <c r="A245" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B245" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C245" s="1" t="n">
         <v>12593</v>
@@ -7951,14 +7951,14 @@
         </is>
       </c>
       <c r="E245" s="1" t="n">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="F245" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -7990,7 +7990,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -8022,7 +8022,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -8054,7 +8054,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -8086,7 +8086,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -8118,7 +8118,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -8150,7 +8150,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -8214,7 +8214,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -8438,7 +8438,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -8470,7 +8470,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -8502,7 +8502,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -8534,7 +8534,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -8566,7 +8566,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -8982,7 +8982,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -9014,7 +9014,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -9046,7 +9046,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -9078,7 +9078,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -9174,7 +9174,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -9206,7 +9206,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -9238,7 +9238,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -9430,7 +9430,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -9462,7 +9462,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -9846,7 +9846,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -9878,7 +9878,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -9910,7 +9910,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -9942,7 +9942,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -10717,10 +10717,10 @@
     </row>
     <row r="332" customHeight="1" ht="20">
       <c r="A332" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B332" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C332" s="1" t="n">
         <v>13318</v>
@@ -10735,24 +10735,24 @@
         </is>
       </c>
       <c r="E332" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F332" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="333" customHeight="1" ht="20">
       <c r="A333" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B333" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C333" s="1" t="n">
         <v>13318</v>
@@ -10767,14 +10767,14 @@
         </is>
       </c>
       <c r="E333" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F333" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -10902,7 +10902,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -11702,7 +11702,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -15101,10 +15101,10 @@
     </row>
     <row r="469" customHeight="1" ht="20">
       <c r="A469" s="1" t="n">
-        <v>1523488</v>
+        <v>1587245</v>
       </c>
       <c r="B469" s="1" t="n">
-        <v>24896</v>
+        <v>27413</v>
       </c>
       <c r="C469" s="1" t="n">
         <v>14730</v>
@@ -15119,24 +15119,24 @@
         </is>
       </c>
       <c r="E469" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F469" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="470" customHeight="1" ht="20">
       <c r="A470" s="1" t="n">
-        <v>1587245</v>
+        <v>1523488</v>
       </c>
       <c r="B470" s="1" t="n">
-        <v>27413</v>
+        <v>24896</v>
       </c>
       <c r="C470" s="1" t="n">
         <v>14730</v>
@@ -15151,14 +15151,14 @@
         </is>
       </c>
       <c r="E470" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F470" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -15261,10 +15261,10 @@
     </row>
     <row r="474" customHeight="1" ht="20">
       <c r="A474" s="1" t="n">
-        <v>1523488</v>
+        <v>1587245</v>
       </c>
       <c r="B474" s="1" t="n">
-        <v>24896</v>
+        <v>27413</v>
       </c>
       <c r="C474" s="1" t="n">
         <v>14733</v>
@@ -15279,24 +15279,24 @@
         </is>
       </c>
       <c r="E474" s="1" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F474" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="475" customHeight="1" ht="20">
       <c r="A475" s="1" t="n">
-        <v>1587245</v>
+        <v>1523488</v>
       </c>
       <c r="B475" s="1" t="n">
-        <v>27413</v>
+        <v>24896</v>
       </c>
       <c r="C475" s="1" t="n">
         <v>14733</v>
@@ -15311,14 +15311,14 @@
         </is>
       </c>
       <c r="E475" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F475" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -16598,7 +16598,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -21494,7 +21494,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -21814,7 +21814,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -25718,7 +25718,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -26166,7 +26166,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -26582,7 +26582,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -26934,7 +26934,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -27030,7 +27030,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -27478,7 +27478,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -28150,7 +28150,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -28182,7 +28182,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -28278,7 +28278,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -30230,7 +30230,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -31407,7 +31407,7 @@
         </is>
       </c>
       <c r="E978" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F978" s="1" t="inlineStr">
         <is>
@@ -31439,7 +31439,7 @@
         </is>
       </c>
       <c r="E979" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F979" s="1" t="inlineStr">
         <is>
@@ -36925,10 +36925,10 @@
     </row>
     <row r="1151" customHeight="1" ht="20">
       <c r="A1151" s="1" t="n">
-        <v>1523488</v>
+        <v>1587245</v>
       </c>
       <c r="B1151" s="1" t="n">
-        <v>24896</v>
+        <v>27413</v>
       </c>
       <c r="C1151" s="1" t="n">
         <v>31738</v>
@@ -36943,14 +36943,14 @@
         </is>
       </c>
       <c r="E1151" s="1" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F1151" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
@@ -36989,10 +36989,10 @@
     </row>
     <row r="1153" customHeight="1" ht="20">
       <c r="A1153" s="1" t="n">
-        <v>1587245</v>
+        <v>1523488</v>
       </c>
       <c r="B1153" s="1" t="n">
-        <v>27413</v>
+        <v>24896</v>
       </c>
       <c r="C1153" s="1" t="n">
         <v>31738</v>
@@ -37007,14 +37007,14 @@
         </is>
       </c>
       <c r="E1153" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F1153" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -37110,7 +37110,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -37149,10 +37149,10 @@
     </row>
     <row r="1158" customHeight="1" ht="20">
       <c r="A1158" s="1" t="n">
-        <v>1523488</v>
+        <v>1587245</v>
       </c>
       <c r="B1158" s="1" t="n">
-        <v>24896</v>
+        <v>27413</v>
       </c>
       <c r="C1158" s="1" t="n">
         <v>31737</v>
@@ -37167,24 +37167,24 @@
         </is>
       </c>
       <c r="E1158" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F1158" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1159" customHeight="1" ht="20">
       <c r="A1159" s="1" t="n">
-        <v>1587245</v>
+        <v>1523488</v>
       </c>
       <c r="B1159" s="1" t="n">
-        <v>27413</v>
+        <v>24896</v>
       </c>
       <c r="C1159" s="1" t="n">
         <v>31737</v>
@@ -37199,14 +37199,14 @@
         </is>
       </c>
       <c r="E1159" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F1159" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -38006,7 +38006,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -38774,7 +38774,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -39421,10 +39421,10 @@
     </row>
     <row r="1229" customHeight="1" ht="20">
       <c r="A1229" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1229" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1229" s="1" t="n">
         <v>33659</v>
@@ -39439,24 +39439,24 @@
         </is>
       </c>
       <c r="E1229" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F1229" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1230" customHeight="1" ht="20">
       <c r="A1230" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1230" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1230" s="1" t="n">
         <v>33659</v>
@@ -39471,14 +39471,14 @@
         </is>
       </c>
       <c r="E1230" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F1230" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -39542,7 +39542,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -39574,7 +39574,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -39638,7 +39638,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -40214,7 +40214,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -40246,7 +40246,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -40438,7 +40438,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -42678,7 +42678,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -42902,7 +42902,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -43357,10 +43357,10 @@
     </row>
     <row r="1352" customHeight="1" ht="20">
       <c r="A1352" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1352" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1352" s="1" t="n">
         <v>37934</v>
@@ -43375,24 +43375,24 @@
         </is>
       </c>
       <c r="E1352" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F1352" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1353" customHeight="1" ht="20">
       <c r="A1353" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1353" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1353" s="1" t="n">
         <v>37934</v>
@@ -43407,14 +43407,14 @@
         </is>
       </c>
       <c r="E1353" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F1353" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -43478,17 +43478,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1356" customHeight="1" ht="20">
       <c r="A1356" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1356" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1356" s="1" t="n">
         <v>39413</v>
@@ -43503,24 +43503,24 @@
         </is>
       </c>
       <c r="E1356" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1356" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1357" customHeight="1" ht="20">
       <c r="A1357" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1357" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1357" s="1" t="n">
         <v>39413</v>
@@ -43535,14 +43535,14 @@
         </is>
       </c>
       <c r="E1357" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1357" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -43734,7 +43734,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -44118,7 +44118,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -44150,7 +44150,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -44310,7 +44310,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -44342,7 +44342,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -44374,7 +44374,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -44662,7 +44662,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -44694,7 +44694,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -44918,7 +44918,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -44950,7 +44950,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -45462,7 +45462,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -45622,7 +45622,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -45750,7 +45750,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -45782,7 +45782,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -46070,7 +46070,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -46326,7 +46326,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -46358,7 +46358,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -46646,7 +46646,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -46678,7 +46678,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -47414,7 +47414,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -47478,7 +47478,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -47542,7 +47542,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -47677,32 +47677,32 @@
     </row>
     <row r="1487" customHeight="1" ht="20">
       <c r="A1487" s="1" t="n">
-        <v>1523488</v>
+        <v>1635888</v>
       </c>
       <c r="B1487" s="1" t="n">
-        <v>24896</v>
+        <v>49</v>
       </c>
       <c r="C1487" s="1" t="n">
-        <v>43093</v>
+        <v>42937</v>
       </c>
       <c r="D1487" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">P-7V200M-R2</t>
+            <t xml:space="preserve">LM32340G-BR</t>
           </r>
         </is>
       </c>
       <c r="E1487" s="1" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F1487" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/10/2026</t>
           </r>
         </is>
       </c>
@@ -47715,19 +47715,19 @@
         <v>24896</v>
       </c>
       <c r="C1488" s="1" t="n">
-        <v>42458</v>
+        <v>43093</v>
       </c>
       <c r="D1488" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LRM15RL-H-D</t>
+            <t xml:space="preserve">P-7V200M-R2</t>
           </r>
         </is>
       </c>
       <c r="E1488" s="1" t="n">
-        <v>20000</v>
+        <v>5</v>
       </c>
       <c r="F1488" s="1" t="inlineStr">
         <is>
@@ -47741,32 +47741,32 @@
     </row>
     <row r="1489" customHeight="1" ht="20">
       <c r="A1489" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1489" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1489" s="1" t="n">
-        <v>43439</v>
+        <v>42458</v>
       </c>
       <c r="D1489" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">7SV130C06BDG</t>
+            <t xml:space="preserve">LRM15RL-H-D</t>
           </r>
         </is>
       </c>
       <c r="E1489" s="1" t="n">
-        <v>20</v>
+        <v>20000</v>
       </c>
       <c r="F1489" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -47779,19 +47779,19 @@
         <v>27486</v>
       </c>
       <c r="C1490" s="1" t="n">
-        <v>43882</v>
+        <v>43439</v>
       </c>
       <c r="D1490" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TCL63X50S</t>
+            <t xml:space="preserve">7SV130C06BDG</t>
           </r>
         </is>
       </c>
       <c r="E1490" s="1" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F1490" s="1" t="inlineStr">
         <is>
@@ -47811,14 +47811,14 @@
         <v>27486</v>
       </c>
       <c r="C1491" s="1" t="n">
-        <v>43878</v>
+        <v>43882</v>
       </c>
       <c r="D1491" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACQ125X20SB</t>
+            <t xml:space="preserve">TCL63X50S</t>
           </r>
         </is>
       </c>
@@ -47837,42 +47837,42 @@
     </row>
     <row r="1492" customHeight="1" ht="20">
       <c r="A1492" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1492" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1492" s="1" t="n">
-        <v>43444</v>
+        <v>43878</v>
       </c>
       <c r="D1492" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">7SV230E08BDG</t>
+            <t xml:space="preserve">ACQ125X20SB</t>
           </r>
         </is>
       </c>
       <c r="E1492" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1492" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1493" customHeight="1" ht="20">
       <c r="A1493" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1493" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1493" s="1" t="n">
         <v>43444</v>
@@ -47887,14 +47887,14 @@
         </is>
       </c>
       <c r="E1493" s="1" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F1493" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -47907,14 +47907,14 @@
         <v>27486</v>
       </c>
       <c r="C1494" s="1" t="n">
-        <v>43440</v>
+        <v>43444</v>
       </c>
       <c r="D1494" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">7SV130E06BDG</t>
+            <t xml:space="preserve">7SV230E08BDG</t>
           </r>
         </is>
       </c>
@@ -47965,32 +47965,32 @@
     </row>
     <row r="1496" customHeight="1" ht="20">
       <c r="A1496" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1496" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1496" s="1" t="n">
-        <v>44196</v>
+        <v>43440</v>
       </c>
       <c r="D1496" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SAI40X100SNG</t>
+            <t xml:space="preserve">7SV130E06BDG</t>
           </r>
         </is>
       </c>
       <c r="E1496" s="1" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F1496" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
@@ -48003,14 +48003,14 @@
         <v>24896</v>
       </c>
       <c r="C1497" s="1" t="n">
-        <v>44198</v>
+        <v>44196</v>
       </c>
       <c r="D1497" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SAI50X80SNG</t>
+            <t xml:space="preserve">SAI40X100SNG</t>
           </r>
         </is>
       </c>
@@ -48029,138 +48029,138 @@
     </row>
     <row r="1498" customHeight="1" ht="20">
       <c r="A1498" s="1" t="n">
-        <v>1634902</v>
+        <v>1523488</v>
       </c>
       <c r="B1498" s="1" t="n">
-        <v>47</v>
+        <v>24896</v>
       </c>
       <c r="C1498" s="1" t="n">
-        <v>43844</v>
+        <v>44198</v>
       </c>
       <c r="D1498" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LU1100P-BR</t>
+            <t xml:space="preserve">SAI50X80SNG</t>
           </r>
         </is>
       </c>
       <c r="E1498" s="1" t="n">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="F1498" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1499" customHeight="1" ht="20">
       <c r="A1499" s="1" t="n">
-        <v>1523488</v>
+        <v>1634902</v>
       </c>
       <c r="B1499" s="1" t="n">
-        <v>24896</v>
+        <v>47</v>
       </c>
       <c r="C1499" s="1" t="n">
-        <v>44044</v>
+        <v>43844</v>
       </c>
       <c r="D1499" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">UWS98A080050050MY</t>
+            <t xml:space="preserve">LU1100P-BR</t>
           </r>
         </is>
       </c>
       <c r="E1499" s="1" t="n">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="F1499" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">27/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1500" customHeight="1" ht="20">
       <c r="A1500" s="1" t="n">
-        <v>1563222</v>
+        <v>1523488</v>
       </c>
       <c r="B1500" s="1" t="n">
-        <v>25042</v>
+        <v>24896</v>
       </c>
       <c r="C1500" s="1" t="n">
-        <v>44090</v>
+        <v>44044</v>
       </c>
       <c r="D1500" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">FWL06-G02</t>
+            <t xml:space="preserve">UWS98A080050050MY</t>
           </r>
         </is>
       </c>
       <c r="E1500" s="1" t="n">
-        <v>300</v>
+        <v>4</v>
       </c>
       <c r="F1500" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">09/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1501" customHeight="1" ht="20">
       <c r="A1501" s="1" t="n">
-        <v>1523488</v>
+        <v>1563222</v>
       </c>
       <c r="B1501" s="1" t="n">
-        <v>24896</v>
+        <v>25042</v>
       </c>
       <c r="C1501" s="1" t="n">
-        <v>43441</v>
+        <v>44090</v>
       </c>
       <c r="D1501" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">7SV21008BDG</t>
+            <t xml:space="preserve">FWL06-G02</t>
           </r>
         </is>
       </c>
       <c r="E1501" s="1" t="n">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="F1501" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">09/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1502" customHeight="1" ht="20">
       <c r="A1502" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1502" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1502" s="1" t="n">
         <v>43441</v>
@@ -48175,14 +48175,14 @@
         </is>
       </c>
       <c r="E1502" s="1" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F1502" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -48207,7 +48207,7 @@
         </is>
       </c>
       <c r="E1503" s="1" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="F1503" s="1" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         </is>
       </c>
       <c r="E1504" s="1" t="n">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="F1504" s="1" t="inlineStr">
         <is>
@@ -48253,10 +48253,10 @@
     </row>
     <row r="1505" customHeight="1" ht="20">
       <c r="A1505" s="1" t="n">
-        <v>1598892</v>
+        <v>1624906</v>
       </c>
       <c r="B1505" s="1" t="n">
-        <v>27486</v>
+        <v>29565</v>
       </c>
       <c r="C1505" s="1" t="n">
         <v>43441</v>
@@ -48271,24 +48271,24 @@
         </is>
       </c>
       <c r="E1505" s="1" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F1505" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">08/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1506" customHeight="1" ht="20">
       <c r="A1506" s="1" t="n">
-        <v>1624906</v>
+        <v>1598892</v>
       </c>
       <c r="B1506" s="1" t="n">
-        <v>29565</v>
+        <v>27486</v>
       </c>
       <c r="C1506" s="1" t="n">
         <v>43441</v>
@@ -48303,98 +48303,98 @@
         </is>
       </c>
       <c r="E1506" s="1" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F1506" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/11/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1507" customHeight="1" ht="20">
       <c r="A1507" s="1" t="n">
-        <v>1634902</v>
+        <v>1598892</v>
       </c>
       <c r="B1507" s="1" t="n">
-        <v>47</v>
+        <v>27486</v>
       </c>
       <c r="C1507" s="1" t="n">
-        <v>43846</v>
+        <v>43441</v>
       </c>
       <c r="D1507" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BRP-110-3M-BR</t>
+            <t xml:space="preserve">7SV21008BDG</t>
           </r>
         </is>
       </c>
       <c r="E1507" s="1" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="F1507" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1508" customHeight="1" ht="20">
       <c r="A1508" s="1" t="n">
-        <v>1624906</v>
+        <v>1634902</v>
       </c>
       <c r="B1508" s="1" t="n">
-        <v>29565</v>
+        <v>47</v>
       </c>
       <c r="C1508" s="1" t="n">
-        <v>43805</v>
+        <v>43846</v>
       </c>
       <c r="D1508" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NPB2X8SCAT</t>
+            <t xml:space="preserve">BRP-110-3M-BR</t>
           </r>
         </is>
       </c>
       <c r="E1508" s="1" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="F1508" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/11/2026</t>
+            <t xml:space="preserve">27/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1509" customHeight="1" ht="20">
       <c r="A1509" s="1" t="n">
-        <v>1598892</v>
+        <v>1624906</v>
       </c>
       <c r="B1509" s="1" t="n">
-        <v>27486</v>
+        <v>29565</v>
       </c>
       <c r="C1509" s="1" t="n">
-        <v>43877</v>
+        <v>43805</v>
       </c>
       <c r="D1509" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACQ125X10SB</t>
+            <t xml:space="preserve">NPB2X8SCAT</t>
           </r>
         </is>
       </c>
@@ -48406,39 +48406,39 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">08/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1510" customHeight="1" ht="20">
       <c r="A1510" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1510" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1510" s="1" t="n">
-        <v>44048</v>
+        <v>43877</v>
       </c>
       <c r="D1510" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">UWS98A100065050MGN</t>
+            <t xml:space="preserve">ACQ125X10SB</t>
           </r>
         </is>
       </c>
       <c r="E1510" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F1510" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
@@ -48451,19 +48451,19 @@
         <v>24896</v>
       </c>
       <c r="C1511" s="1" t="n">
-        <v>44193</v>
+        <v>44048</v>
       </c>
       <c r="D1511" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MI25X70SCAG</t>
+            <t xml:space="preserve">UWS98A100065050MGN</t>
           </r>
         </is>
       </c>
       <c r="E1511" s="1" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F1511" s="1" t="inlineStr">
         <is>
@@ -48483,14 +48483,14 @@
         <v>24896</v>
       </c>
       <c r="C1512" s="1" t="n">
-        <v>44178</v>
+        <v>44193</v>
       </c>
       <c r="D1512" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">4V430E15G-X0</t>
+            <t xml:space="preserve">MI25X70SCAG</t>
           </r>
         </is>
       </c>
@@ -48547,19 +48547,19 @@
         <v>24896</v>
       </c>
       <c r="C1514" s="1" t="n">
-        <v>44002</v>
+        <v>44178</v>
       </c>
       <c r="D1514" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">2SA20020AG</t>
+            <t xml:space="preserve">4V430E15G-X0</t>
           </r>
         </is>
       </c>
       <c r="E1514" s="1" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F1514" s="1" t="inlineStr">
         <is>
@@ -48579,19 +48579,19 @@
         <v>24896</v>
       </c>
       <c r="C1515" s="1" t="n">
-        <v>44181</v>
+        <v>44002</v>
       </c>
       <c r="D1515" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACE25X30SB</t>
+            <t xml:space="preserve">2SA20020AG</t>
           </r>
         </is>
       </c>
       <c r="E1515" s="1" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F1515" s="1" t="inlineStr">
         <is>
@@ -48611,19 +48611,19 @@
         <v>24896</v>
       </c>
       <c r="C1516" s="1" t="n">
-        <v>43442</v>
+        <v>44181</v>
       </c>
       <c r="D1516" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">7SV22008BDG</t>
+            <t xml:space="preserve">ACE25X30SB</t>
           </r>
         </is>
       </c>
       <c r="E1516" s="1" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F1516" s="1" t="inlineStr">
         <is>
@@ -48637,10 +48637,10 @@
     </row>
     <row r="1517" customHeight="1" ht="20">
       <c r="A1517" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1517" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1517" s="1" t="n">
         <v>43442</v>
@@ -48655,78 +48655,78 @@
         </is>
       </c>
       <c r="E1517" s="1" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F1517" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1518" customHeight="1" ht="20">
       <c r="A1518" s="1" t="n">
-        <v>1624906</v>
+        <v>1598892</v>
       </c>
       <c r="B1518" s="1" t="n">
-        <v>29565</v>
+        <v>27486</v>
       </c>
       <c r="C1518" s="1" t="n">
-        <v>43886</v>
+        <v>43442</v>
       </c>
       <c r="D1518" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">7SV100M7FG</t>
+            <t xml:space="preserve">7SV22008BDG</t>
           </r>
         </is>
       </c>
       <c r="E1518" s="1" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F1518" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/11/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1519" customHeight="1" ht="20">
       <c r="A1519" s="1" t="n">
-        <v>1523488</v>
+        <v>1624906</v>
       </c>
       <c r="B1519" s="1" t="n">
-        <v>24896</v>
+        <v>29565</v>
       </c>
       <c r="C1519" s="1" t="n">
-        <v>44050</v>
+        <v>43886</v>
       </c>
       <c r="D1519" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACE63X10SG</t>
+            <t xml:space="preserve">7SV100M7FG</t>
           </r>
         </is>
       </c>
       <c r="E1519" s="1" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F1519" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">08/11/2026</t>
           </r>
         </is>
       </c>
@@ -48739,19 +48739,19 @@
         <v>24896</v>
       </c>
       <c r="C1520" s="1" t="n">
-        <v>44192</v>
+        <v>44050</v>
       </c>
       <c r="D1520" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MI25X200SCAG</t>
+            <t xml:space="preserve">ACE63X10SG</t>
           </r>
         </is>
       </c>
       <c r="E1520" s="1" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F1520" s="1" t="inlineStr">
         <is>
@@ -48771,14 +48771,14 @@
         <v>24896</v>
       </c>
       <c r="C1521" s="1" t="n">
-        <v>44184</v>
+        <v>44192</v>
       </c>
       <c r="D1521" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACE25X50SB</t>
+            <t xml:space="preserve">MI25X200SCAG</t>
           </r>
         </is>
       </c>
@@ -48803,19 +48803,19 @@
         <v>24896</v>
       </c>
       <c r="C1522" s="1" t="n">
-        <v>44043</v>
+        <v>44184</v>
       </c>
       <c r="D1522" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">UWS98A080050050MR</t>
+            <t xml:space="preserve">ACE25X50SB</t>
           </r>
         </is>
       </c>
       <c r="E1522" s="1" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F1522" s="1" t="inlineStr">
         <is>
@@ -48829,64 +48829,64 @@
     </row>
     <row r="1523" customHeight="1" ht="20">
       <c r="A1523" s="1" t="n">
-        <v>1563222</v>
+        <v>1523488</v>
       </c>
       <c r="B1523" s="1" t="n">
-        <v>25042</v>
+        <v>24896</v>
       </c>
       <c r="C1523" s="1" t="n">
-        <v>44073</v>
+        <v>44043</v>
       </c>
       <c r="D1523" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VN502-PC-P</t>
+            <t xml:space="preserve">UWS98A080050050MR</t>
           </r>
         </is>
       </c>
       <c r="E1523" s="1" t="n">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="F1523" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">09/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1524" customHeight="1" ht="20">
       <c r="A1524" s="1" t="n">
-        <v>1523488</v>
+        <v>1563222</v>
       </c>
       <c r="B1524" s="1" t="n">
-        <v>24896</v>
+        <v>25042</v>
       </c>
       <c r="C1524" s="1" t="n">
-        <v>44087</v>
+        <v>44073</v>
       </c>
       <c r="D1524" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">2JWK15015Q50G</t>
+            <t xml:space="preserve">VN502-PC-P</t>
           </r>
         </is>
       </c>
       <c r="E1524" s="1" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="F1524" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">09/11/2026</t>
           </r>
         </is>
       </c>
@@ -48925,96 +48925,96 @@
     </row>
     <row r="1526" customHeight="1" ht="20">
       <c r="A1526" s="1" t="n">
-        <v>1628645</v>
+        <v>1523488</v>
       </c>
       <c r="B1526" s="1" t="n">
-        <v>45</v>
+        <v>24896</v>
       </c>
       <c r="C1526" s="1" t="n">
-        <v>43864</v>
+        <v>44087</v>
       </c>
       <c r="D1526" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TR6325P-BR</t>
+            <t xml:space="preserve">2JWK15015Q50G</t>
           </r>
         </is>
       </c>
       <c r="E1526" s="1" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F1526" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1527" customHeight="1" ht="20">
       <c r="A1527" s="1" t="n">
-        <v>1624906</v>
+        <v>1628645</v>
       </c>
       <c r="B1527" s="1" t="n">
-        <v>29565</v>
+        <v>45</v>
       </c>
       <c r="C1527" s="1" t="n">
-        <v>43885</v>
+        <v>43864</v>
       </c>
       <c r="D1527" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">7SV100M5FG</t>
+            <t xml:space="preserve">TR6325P-BR</t>
           </r>
         </is>
       </c>
       <c r="E1527" s="1" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F1527" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/11/2026</t>
+            <t xml:space="preserve">16/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1528" customHeight="1" ht="20">
       <c r="A1528" s="1" t="n">
-        <v>1523488</v>
+        <v>1624906</v>
       </c>
       <c r="B1528" s="1" t="n">
-        <v>24896</v>
+        <v>29565</v>
       </c>
       <c r="C1528" s="1" t="n">
-        <v>44042</v>
+        <v>43885</v>
       </c>
       <c r="D1528" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">UWS98A080050050MGN</t>
+            <t xml:space="preserve">7SV100M5FG</t>
           </r>
         </is>
       </c>
       <c r="E1528" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F1528" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">08/11/2026</t>
           </r>
         </is>
       </c>
@@ -49027,14 +49027,14 @@
         <v>24896</v>
       </c>
       <c r="C1529" s="1" t="n">
-        <v>44046</v>
+        <v>44042</v>
       </c>
       <c r="D1529" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">UWS98A100065050MY</t>
+            <t xml:space="preserve">UWS98A080050050MGN</t>
           </r>
         </is>
       </c>
@@ -49059,19 +49059,19 @@
         <v>24896</v>
       </c>
       <c r="C1530" s="1" t="n">
-        <v>44049</v>
+        <v>44046</v>
       </c>
       <c r="D1530" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">UWS98A100065050MBU</t>
+            <t xml:space="preserve">UWS98A100065050MY</t>
           </r>
         </is>
       </c>
       <c r="E1530" s="1" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F1530" s="1" t="inlineStr">
         <is>
@@ -49091,19 +49091,19 @@
         <v>24896</v>
       </c>
       <c r="C1531" s="1" t="n">
-        <v>44083</v>
+        <v>44049</v>
       </c>
       <c r="D1531" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">7V200M3FG</t>
+            <t xml:space="preserve">UWS98A100065050MBU</t>
           </r>
         </is>
       </c>
       <c r="E1531" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F1531" s="1" t="inlineStr">
         <is>
@@ -49117,64 +49117,64 @@
     </row>
     <row r="1532" customHeight="1" ht="20">
       <c r="A1532" s="1" t="n">
-        <v>1563222</v>
+        <v>1523488</v>
       </c>
       <c r="B1532" s="1" t="n">
-        <v>25042</v>
+        <v>24896</v>
       </c>
       <c r="C1532" s="1" t="n">
-        <v>44089</v>
+        <v>44083</v>
       </c>
       <c r="D1532" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">FWL06-G01</t>
+            <t xml:space="preserve">7V200M3FG</t>
           </r>
         </is>
       </c>
       <c r="E1532" s="1" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="F1532" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">09/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1533" customHeight="1" ht="20">
       <c r="A1533" s="1" t="n">
-        <v>1523488</v>
+        <v>1563222</v>
       </c>
       <c r="B1533" s="1" t="n">
-        <v>24896</v>
+        <v>25042</v>
       </c>
       <c r="C1533" s="1" t="n">
-        <v>44038</v>
+        <v>44089</v>
       </c>
       <c r="D1533" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SCT80X110X40S</t>
+            <t xml:space="preserve">FWL06-G01</t>
           </r>
         </is>
       </c>
       <c r="E1533" s="1" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="F1533" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">09/11/2026</t>
           </r>
         </is>
       </c>
@@ -49187,19 +49187,19 @@
         <v>24896</v>
       </c>
       <c r="C1534" s="1" t="n">
-        <v>44099</v>
+        <v>44038</v>
       </c>
       <c r="D1534" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">7V200M4FG</t>
+            <t xml:space="preserve">SCT80X110X40S</t>
           </r>
         </is>
       </c>
       <c r="E1534" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1534" s="1" t="inlineStr">
         <is>
@@ -49219,19 +49219,19 @@
         <v>24896</v>
       </c>
       <c r="C1535" s="1" t="n">
-        <v>44185</v>
+        <v>44099</v>
       </c>
       <c r="D1535" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACE32X30SBG</t>
+            <t xml:space="preserve">7V200M4FG</t>
           </r>
         </is>
       </c>
       <c r="E1535" s="1" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F1535" s="1" t="inlineStr">
         <is>
@@ -49251,14 +49251,14 @@
         <v>24896</v>
       </c>
       <c r="C1536" s="1" t="n">
-        <v>44188</v>
+        <v>44185</v>
       </c>
       <c r="D1536" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACE32X60SBG</t>
+            <t xml:space="preserve">ACE32X30SBG</t>
           </r>
         </is>
       </c>
@@ -49277,10 +49277,10 @@
     </row>
     <row r="1537" customHeight="1" ht="20">
       <c r="A1537" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1537" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1537" s="1" t="n">
         <v>44188</v>
@@ -49302,27 +49302,27 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1538" customHeight="1" ht="20">
       <c r="A1538" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1538" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1538" s="1" t="n">
-        <v>44179</v>
+        <v>44188</v>
       </c>
       <c r="D1538" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MI32S-P2CM</t>
+            <t xml:space="preserve">ACE32X60SBG</t>
           </r>
         </is>
       </c>
@@ -49334,7 +49334,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
@@ -49347,14 +49347,14 @@
         <v>24896</v>
       </c>
       <c r="C1539" s="1" t="n">
-        <v>44180</v>
+        <v>44179</v>
       </c>
       <c r="D1539" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MI16X30SCA</t>
+            <t xml:space="preserve">MI32S-P2CM</t>
           </r>
         </is>
       </c>
@@ -49379,19 +49379,19 @@
         <v>24896</v>
       </c>
       <c r="C1540" s="1" t="n">
-        <v>44182</v>
+        <v>44180</v>
       </c>
       <c r="D1540" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MIC25X25SCAG</t>
+            <t xml:space="preserve">MI16X30SCA</t>
           </r>
         </is>
       </c>
       <c r="E1540" s="1" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F1540" s="1" t="inlineStr">
         <is>
@@ -49411,14 +49411,14 @@
         <v>24896</v>
       </c>
       <c r="C1541" s="1" t="n">
-        <v>44195</v>
+        <v>44182</v>
       </c>
       <c r="D1541" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SAI100X100SNG</t>
+            <t xml:space="preserve">MIC25X25SCAG</t>
           </r>
         </is>
       </c>
@@ -49437,96 +49437,96 @@
     </row>
     <row r="1542" customHeight="1" ht="20">
       <c r="A1542" s="1" t="n">
-        <v>1634902</v>
+        <v>1523488</v>
       </c>
       <c r="B1542" s="1" t="n">
-        <v>47</v>
+        <v>24896</v>
       </c>
       <c r="C1542" s="1" t="n">
-        <v>44237</v>
+        <v>44195</v>
       </c>
       <c r="D1542" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TE1600P-BR</t>
+            <t xml:space="preserve">SAI100X100SNG</t>
           </r>
         </is>
       </c>
       <c r="E1542" s="1" t="n">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="F1542" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1543" customHeight="1" ht="20">
       <c r="A1543" s="1" t="n">
-        <v>1523488</v>
+        <v>1634902</v>
       </c>
       <c r="B1543" s="1" t="n">
-        <v>24896</v>
+        <v>47</v>
       </c>
       <c r="C1543" s="1" t="n">
-        <v>44183</v>
+        <v>44237</v>
       </c>
       <c r="D1543" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACE20X30SB</t>
+            <t xml:space="preserve">TE1600P-BR</t>
           </r>
         </is>
       </c>
       <c r="E1543" s="1" t="n">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F1543" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">27/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1544" customHeight="1" ht="20">
       <c r="A1544" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1544" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1544" s="1" t="n">
-        <v>43437</v>
+        <v>44183</v>
       </c>
       <c r="D1544" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">7SV11006BDG</t>
+            <t xml:space="preserve">ACE20X30SB</t>
           </r>
         </is>
       </c>
       <c r="E1544" s="1" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F1544" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -49571,19 +49571,19 @@
         <v>27486</v>
       </c>
       <c r="C1546" s="1" t="n">
-        <v>43904</v>
+        <v>43437</v>
       </c>
       <c r="D1546" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACQ100X25G</t>
+            <t xml:space="preserve">7SV11006BDG</t>
           </r>
         </is>
       </c>
       <c r="E1546" s="1" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F1546" s="1" t="inlineStr">
         <is>
@@ -49597,32 +49597,32 @@
     </row>
     <row r="1547" customHeight="1" ht="20">
       <c r="A1547" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1547" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1547" s="1" t="n">
-        <v>44189</v>
+        <v>43904</v>
       </c>
       <c r="D1547" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACE40X20SBG</t>
+            <t xml:space="preserve">ACQ100X25G</t>
           </r>
         </is>
       </c>
       <c r="E1547" s="1" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F1547" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
@@ -49635,19 +49635,19 @@
         <v>24896</v>
       </c>
       <c r="C1548" s="1" t="n">
-        <v>44190</v>
+        <v>44189</v>
       </c>
       <c r="D1548" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MI16X10SCA</t>
+            <t xml:space="preserve">ACE40X20SBG</t>
           </r>
         </is>
       </c>
       <c r="E1548" s="1" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F1548" s="1" t="inlineStr">
         <is>
@@ -49667,19 +49667,19 @@
         <v>24896</v>
       </c>
       <c r="C1549" s="1" t="n">
-        <v>44197</v>
+        <v>44190</v>
       </c>
       <c r="D1549" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SAI50X60SNG</t>
+            <t xml:space="preserve">MI16X10SCA</t>
           </r>
         </is>
       </c>
       <c r="E1549" s="1" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F1549" s="1" t="inlineStr">
         <is>
@@ -49693,10 +49693,10 @@
     </row>
     <row r="1550" customHeight="1" ht="20">
       <c r="A1550" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1550" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1550" s="1" t="n">
         <v>44197</v>
@@ -49711,120 +49711,120 @@
         </is>
       </c>
       <c r="E1550" s="1" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F1550" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1551" customHeight="1" ht="20">
       <c r="A1551" s="1" t="n">
-        <v>1634902</v>
+        <v>1598892</v>
       </c>
       <c r="B1551" s="1" t="n">
-        <v>47</v>
+        <v>27486</v>
       </c>
       <c r="C1551" s="1" t="n">
-        <v>44238</v>
+        <v>44197</v>
       </c>
       <c r="D1551" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TE1100P-BR</t>
+            <t xml:space="preserve">SAI50X60SNG</t>
           </r>
         </is>
       </c>
       <c r="E1551" s="1" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F1551" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1552" customHeight="1" ht="20">
       <c r="A1552" s="1" t="n">
-        <v>1523488</v>
+        <v>1634902</v>
       </c>
       <c r="B1552" s="1" t="n">
-        <v>24896</v>
+        <v>47</v>
       </c>
       <c r="C1552" s="1" t="n">
-        <v>44199</v>
+        <v>44238</v>
       </c>
       <c r="D1552" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SAI63X80SNG</t>
+            <t xml:space="preserve">TE1100P-BR</t>
           </r>
         </is>
       </c>
       <c r="E1552" s="1" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F1552" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">27/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1553" customHeight="1" ht="20">
       <c r="A1553" s="1" t="n">
-        <v>1634902</v>
+        <v>1523488</v>
       </c>
       <c r="B1553" s="1" t="n">
-        <v>47</v>
+        <v>24896</v>
       </c>
       <c r="C1553" s="1" t="n">
-        <v>44240</v>
+        <v>44199</v>
       </c>
       <c r="D1553" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">UNFA1100P-BR</t>
+            <t xml:space="preserve">SAI63X80SNG</t>
           </r>
         </is>
       </c>
       <c r="E1553" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F1553" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1554" customHeight="1" ht="20">
       <c r="A1554" s="1" t="n">
-        <v>1628645</v>
+        <v>1634902</v>
       </c>
       <c r="B1554" s="1" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C1554" s="1" t="n">
         <v>44240</v>
@@ -49839,46 +49839,46 @@
         </is>
       </c>
       <c r="E1554" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F1554" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">27/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1555" customHeight="1" ht="20">
       <c r="A1555" s="1" t="n">
-        <v>1598892</v>
+        <v>1628645</v>
       </c>
       <c r="B1555" s="1" t="n">
-        <v>27486</v>
+        <v>45</v>
       </c>
       <c r="C1555" s="1" t="n">
-        <v>43879</v>
+        <v>44240</v>
       </c>
       <c r="D1555" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACQ100X50B</t>
+            <t xml:space="preserve">UNFA1100P-BR</t>
           </r>
         </is>
       </c>
       <c r="E1555" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F1555" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">16/10/2026</t>
           </r>
         </is>
       </c>
@@ -49891,14 +49891,14 @@
         <v>27486</v>
       </c>
       <c r="C1556" s="1" t="n">
-        <v>43883</v>
+        <v>43879</v>
       </c>
       <c r="D1556" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TCL32X30S</t>
+            <t xml:space="preserve">ACQ100X50B</t>
           </r>
         </is>
       </c>
@@ -49923,14 +49923,14 @@
         <v>27486</v>
       </c>
       <c r="C1557" s="1" t="n">
-        <v>43880</v>
+        <v>43883</v>
       </c>
       <c r="D1557" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MBL25X25CA</t>
+            <t xml:space="preserve">TCL32X30S</t>
           </r>
         </is>
       </c>
@@ -49955,14 +49955,14 @@
         <v>27486</v>
       </c>
       <c r="C1558" s="1" t="n">
-        <v>43881</v>
+        <v>43880</v>
       </c>
       <c r="D1558" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TCL40X30S</t>
+            <t xml:space="preserve">MBL25X25CA</t>
           </r>
         </is>
       </c>
@@ -49981,96 +49981,96 @@
     </row>
     <row r="1559" customHeight="1" ht="20">
       <c r="A1559" s="1" t="n">
-        <v>1634902</v>
+        <v>1598892</v>
       </c>
       <c r="B1559" s="1" t="n">
-        <v>47</v>
+        <v>27486</v>
       </c>
       <c r="C1559" s="1" t="n">
-        <v>44236</v>
+        <v>43881</v>
       </c>
       <c r="D1559" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BRP-160-6M-BR</t>
+            <t xml:space="preserve">TCL40X30S</t>
           </r>
         </is>
       </c>
       <c r="E1559" s="1" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="F1559" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1560" customHeight="1" ht="20">
       <c r="A1560" s="1" t="n">
-        <v>1598892</v>
+        <v>1634902</v>
       </c>
       <c r="B1560" s="1" t="n">
-        <v>27486</v>
+        <v>47</v>
       </c>
       <c r="C1560" s="1" t="n">
-        <v>44328</v>
+        <v>44236</v>
       </c>
       <c r="D1560" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TCL40X150SG</t>
+            <t xml:space="preserve">BRP-160-6M-BR</t>
           </r>
         </is>
       </c>
       <c r="E1560" s="1" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="F1560" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">27/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1561" customHeight="1" ht="20">
       <c r="A1561" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1561" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1561" s="1" t="n">
-        <v>43928</v>
+        <v>44328</v>
       </c>
       <c r="D1561" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">EAV310</t>
+            <t xml:space="preserve">TCL40X150SG</t>
           </r>
         </is>
       </c>
       <c r="E1561" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F1561" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
@@ -50083,19 +50083,19 @@
         <v>24896</v>
       </c>
       <c r="C1562" s="1" t="n">
-        <v>44045</v>
+        <v>43928</v>
       </c>
       <c r="D1562" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">UWS98A080050050MBU</t>
+            <t xml:space="preserve">EAV310</t>
           </r>
         </is>
       </c>
       <c r="E1562" s="1" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F1562" s="1" t="inlineStr">
         <is>
@@ -50109,10 +50109,10 @@
     </row>
     <row r="1563" customHeight="1" ht="20">
       <c r="A1563" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1563" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1563" s="1" t="n">
         <v>44045</v>
@@ -50127,46 +50127,46 @@
         </is>
       </c>
       <c r="E1563" s="1" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F1563" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1564" customHeight="1" ht="20">
       <c r="A1564" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1564" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1564" s="1" t="n">
-        <v>44047</v>
+        <v>44045</v>
       </c>
       <c r="D1564" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">UWS98A100065050MR</t>
+            <t xml:space="preserve">UWS98A080050050MBU</t>
           </r>
         </is>
       </c>
       <c r="E1564" s="1" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F1564" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
@@ -50179,19 +50179,19 @@
         <v>24896</v>
       </c>
       <c r="C1565" s="1" t="n">
-        <v>43774</v>
+        <v>44047</v>
       </c>
       <c r="D1565" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">2WA05010AG</t>
+            <t xml:space="preserve">UWS98A100065050MR</t>
           </r>
         </is>
       </c>
       <c r="E1565" s="1" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F1565" s="1" t="inlineStr">
         <is>
@@ -50205,96 +50205,96 @@
     </row>
     <row r="1566" customHeight="1" ht="20">
       <c r="A1566" s="1" t="n">
-        <v>1634902</v>
+        <v>1523488</v>
       </c>
       <c r="B1566" s="1" t="n">
-        <v>47</v>
+        <v>24896</v>
       </c>
       <c r="C1566" s="1" t="n">
-        <v>44239</v>
+        <v>43774</v>
       </c>
       <c r="D1566" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">UNFA160P-BR</t>
+            <t xml:space="preserve">2WA05010AG</t>
           </r>
         </is>
       </c>
       <c r="E1566" s="1" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F1566" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1567" customHeight="1" ht="20">
       <c r="A1567" s="1" t="n">
-        <v>1598892</v>
+        <v>1634902</v>
       </c>
       <c r="B1567" s="1" t="n">
-        <v>27486</v>
+        <v>47</v>
       </c>
       <c r="C1567" s="1" t="n">
-        <v>43438</v>
+        <v>44239</v>
       </c>
       <c r="D1567" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">7SV12006BDG</t>
+            <t xml:space="preserve">UNFA160P-BR</t>
           </r>
         </is>
       </c>
       <c r="E1567" s="1" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F1567" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">27/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1568" customHeight="1" ht="20">
       <c r="A1568" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1568" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1568" s="1" t="n">
-        <v>44194</v>
+        <v>43438</v>
       </c>
       <c r="D1568" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MI25X75SCAG</t>
+            <t xml:space="preserve">7SV12006BDG</t>
           </r>
         </is>
       </c>
       <c r="E1568" s="1" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F1568" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
@@ -50307,19 +50307,19 @@
         <v>24896</v>
       </c>
       <c r="C1569" s="1" t="n">
-        <v>44186</v>
+        <v>44194</v>
       </c>
       <c r="D1569" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACE32X40SBG</t>
+            <t xml:space="preserve">MI25X75SCAG</t>
           </r>
         </is>
       </c>
       <c r="E1569" s="1" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F1569" s="1" t="inlineStr">
         <is>
@@ -50339,19 +50339,19 @@
         <v>24896</v>
       </c>
       <c r="C1570" s="1" t="n">
-        <v>43443</v>
+        <v>44186</v>
       </c>
       <c r="D1570" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">7SV230C08BDG</t>
+            <t xml:space="preserve">ACE32X40SBG</t>
           </r>
         </is>
       </c>
       <c r="E1570" s="1" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F1570" s="1" t="inlineStr">
         <is>
@@ -50365,10 +50365,10 @@
     </row>
     <row r="1571" customHeight="1" ht="20">
       <c r="A1571" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1571" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1571" s="1" t="n">
         <v>43443</v>
@@ -50383,14 +50383,14 @@
         </is>
       </c>
       <c r="E1571" s="1" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F1571" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -50403,19 +50403,19 @@
         <v>27486</v>
       </c>
       <c r="C1572" s="1" t="n">
-        <v>43544</v>
+        <v>43443</v>
       </c>
       <c r="D1572" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MA20X50SCA</t>
+            <t xml:space="preserve">7SV230C08BDG</t>
           </r>
         </is>
       </c>
       <c r="E1572" s="1" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F1572" s="1" t="inlineStr">
         <is>
@@ -50429,32 +50429,32 @@
     </row>
     <row r="1573" customHeight="1" ht="20">
       <c r="A1573" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1573" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1573" s="1" t="n">
-        <v>44187</v>
+        <v>43544</v>
       </c>
       <c r="D1573" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACE32X50SG</t>
+            <t xml:space="preserve">MA20X50SCA</t>
           </r>
         </is>
       </c>
       <c r="E1573" s="1" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F1573" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
@@ -50467,19 +50467,19 @@
         <v>24896</v>
       </c>
       <c r="C1574" s="1" t="n">
-        <v>44191</v>
+        <v>44187</v>
       </c>
       <c r="D1574" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MI25X125SCAG</t>
+            <t xml:space="preserve">ACE32X50SG</t>
           </r>
         </is>
       </c>
       <c r="E1574" s="1" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F1574" s="1" t="inlineStr">
         <is>
@@ -50493,10 +50493,10 @@
     </row>
     <row r="1575" customHeight="1" ht="20">
       <c r="A1575" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1575" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1575" s="1" t="n">
         <v>44191</v>
@@ -50518,49 +50518,49 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1576" customHeight="1" ht="20">
       <c r="A1576" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1576" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1576" s="1" t="n">
-        <v>43451</v>
+        <v>44191</v>
       </c>
       <c r="D1576" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">GPLL802</t>
+            <t xml:space="preserve">MI25X125SCAG</t>
           </r>
         </is>
       </c>
       <c r="E1576" s="1" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F1576" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1577" customHeight="1" ht="20">
       <c r="A1577" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1577" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1577" s="1" t="n">
         <v>43451</v>
@@ -50575,136 +50575,136 @@
         </is>
       </c>
       <c r="E1577" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F1577" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1578" customHeight="1" ht="20">
       <c r="A1578" s="1" t="n">
-        <v>1470972</v>
+        <v>1598892</v>
       </c>
       <c r="B1578" s="1" t="n">
-        <v>24001</v>
+        <v>27486</v>
       </c>
       <c r="C1578" s="1" t="n">
-        <v>43643</v>
+        <v>43451</v>
       </c>
       <c r="D1578" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">FLANGE-CT125-X73#</t>
+            <t xml:space="preserve">GPLL802</t>
           </r>
         </is>
       </c>
       <c r="E1578" s="1" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="F1578" s="1" t="inlineStr">
-        <is/>
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">30/11/2026</t>
+          </r>
+        </is>
       </c>
     </row>
     <row r="1579" customHeight="1" ht="20">
       <c r="A1579" s="1" t="n">
-        <v>1542689</v>
+        <v>1470972</v>
       </c>
       <c r="B1579" s="1" t="n">
-        <v>24951</v>
+        <v>24001</v>
       </c>
       <c r="C1579" s="1" t="n">
-        <v>44467</v>
+        <v>43643</v>
       </c>
       <c r="D1579" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TPUC-0425-BL-100M</t>
+            <t xml:space="preserve">FLANGE-CT125-X73#</t>
           </r>
         </is>
       </c>
       <c r="E1579" s="1" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="F1579" s="1" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-       </rPr>
-            <t xml:space="preserve">23/11/2026</t>
-          </r>
-        </is>
+        <is/>
       </c>
     </row>
     <row r="1580" customHeight="1" ht="20">
       <c r="A1580" s="1" t="n">
-        <v>1624906</v>
+        <v>1542689</v>
       </c>
       <c r="B1580" s="1" t="n">
-        <v>29565</v>
+        <v>24951</v>
       </c>
       <c r="C1580" s="1" t="n">
-        <v>44758</v>
+        <v>44467</v>
       </c>
       <c r="D1580" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TACE40X20SG</t>
+            <t xml:space="preserve">TPUC-0425-BL-100M</t>
           </r>
         </is>
       </c>
       <c r="E1580" s="1" t="n">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="F1580" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/11/2026</t>
+            <t xml:space="preserve">23/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1581" customHeight="1" ht="20">
       <c r="A1581" s="1" t="n">
-        <v>1542689</v>
+        <v>1624906</v>
       </c>
       <c r="B1581" s="1" t="n">
-        <v>24951</v>
+        <v>29565</v>
       </c>
       <c r="C1581" s="1" t="n">
-        <v>44462</v>
+        <v>44758</v>
       </c>
       <c r="D1581" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TPU-0604-BL-100M</t>
+            <t xml:space="preserve">TACE40X20SG</t>
           </r>
         </is>
       </c>
       <c r="E1581" s="1" t="n">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="F1581" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/11/2026</t>
+            <t xml:space="preserve">08/11/2026</t>
           </r>
         </is>
       </c>
@@ -50717,19 +50717,19 @@
         <v>24951</v>
       </c>
       <c r="C1582" s="1" t="n">
-        <v>44466</v>
+        <v>44462</v>
       </c>
       <c r="D1582" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TPU-1612-BL-100M</t>
+            <t xml:space="preserve">TPU-0604-BL-100M</t>
           </r>
         </is>
       </c>
       <c r="E1582" s="1" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="F1582" s="1" t="inlineStr">
         <is>
@@ -50743,32 +50743,32 @@
     </row>
     <row r="1583" customHeight="1" ht="20">
       <c r="A1583" s="1" t="n">
-        <v>1598892</v>
+        <v>1542689</v>
       </c>
       <c r="B1583" s="1" t="n">
-        <v>27486</v>
+        <v>24951</v>
       </c>
       <c r="C1583" s="1" t="n">
-        <v>45075</v>
+        <v>44466</v>
       </c>
       <c r="D1583" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">GPLL1002</t>
+            <t xml:space="preserve">TPU-1612-BL-100M</t>
           </r>
         </is>
       </c>
       <c r="E1583" s="1" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="F1583" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/11/2026</t>
           </r>
         </is>
       </c>
@@ -50781,19 +50781,19 @@
         <v>27486</v>
       </c>
       <c r="C1584" s="1" t="n">
-        <v>45087</v>
+        <v>45075</v>
       </c>
       <c r="D1584" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PB12X100SU</t>
+            <t xml:space="preserve">GPLL1002</t>
           </r>
         </is>
       </c>
       <c r="E1584" s="1" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="F1584" s="1" t="inlineStr">
         <is>
@@ -50813,19 +50813,19 @@
         <v>27486</v>
       </c>
       <c r="C1585" s="1" t="n">
-        <v>45082</v>
+        <v>45087</v>
       </c>
       <c r="D1585" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">GPLL602</t>
+            <t xml:space="preserve">PB12X100SU</t>
           </r>
         </is>
       </c>
       <c r="E1585" s="1" t="n">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="F1585" s="1" t="inlineStr">
         <is>
@@ -50839,32 +50839,32 @@
     </row>
     <row r="1586" customHeight="1" ht="20">
       <c r="A1586" s="1" t="n">
-        <v>1542689</v>
+        <v>1598892</v>
       </c>
       <c r="B1586" s="1" t="n">
-        <v>24951</v>
+        <v>27486</v>
       </c>
       <c r="C1586" s="1" t="n">
-        <v>44469</v>
+        <v>45082</v>
       </c>
       <c r="D1586" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TPUC-0855-BL-100M</t>
+            <t xml:space="preserve">GPLL602</t>
           </r>
         </is>
       </c>
       <c r="E1586" s="1" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F1586" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/11/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
@@ -50877,19 +50877,19 @@
         <v>24951</v>
       </c>
       <c r="C1587" s="1" t="n">
-        <v>44471</v>
+        <v>44469</v>
       </c>
       <c r="D1587" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TPUC-1208-BL-100M</t>
+            <t xml:space="preserve">TPUC-0855-BL-100M</t>
           </r>
         </is>
       </c>
       <c r="E1587" s="1" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="F1587" s="1" t="inlineStr">
         <is>
@@ -50903,64 +50903,64 @@
     </row>
     <row r="1588" customHeight="1" ht="20">
       <c r="A1588" s="1" t="n">
-        <v>1634902</v>
+        <v>1542689</v>
       </c>
       <c r="B1588" s="1" t="n">
-        <v>47</v>
+        <v>24951</v>
       </c>
       <c r="C1588" s="1" t="n">
-        <v>44447</v>
+        <v>44471</v>
       </c>
       <c r="D1588" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LU500P-BR</t>
+            <t xml:space="preserve">TPUC-1208-BL-100M</t>
           </r>
         </is>
       </c>
       <c r="E1588" s="1" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="F1588" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/10/2026</t>
+            <t xml:space="preserve">23/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1589" customHeight="1" ht="20">
       <c r="A1589" s="1" t="n">
-        <v>1607866</v>
+        <v>1634902</v>
       </c>
       <c r="B1589" s="1" t="n">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="C1589" s="1" t="n">
-        <v>44796</v>
+        <v>44447</v>
       </c>
       <c r="D1589" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">HCH25-M</t>
+            <t xml:space="preserve">LU500P-BR</t>
           </r>
         </is>
       </c>
       <c r="E1589" s="1" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="F1589" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/11/2026</t>
+            <t xml:space="preserve">27/10/2026</t>
           </r>
         </is>
       </c>
@@ -50973,19 +50973,19 @@
         <v>82</v>
       </c>
       <c r="C1590" s="1" t="n">
-        <v>44799</v>
+        <v>44796</v>
       </c>
       <c r="D1590" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">HCW15-M</t>
+            <t xml:space="preserve">HCH25-M</t>
           </r>
         </is>
       </c>
       <c r="E1590" s="1" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F1590" s="1" t="inlineStr">
         <is>
@@ -50999,96 +50999,96 @@
     </row>
     <row r="1591" customHeight="1" ht="20">
       <c r="A1591" s="1" t="n">
-        <v>1598892</v>
+        <v>1607866</v>
       </c>
       <c r="B1591" s="1" t="n">
-        <v>27486</v>
+        <v>82</v>
       </c>
       <c r="C1591" s="1" t="n">
-        <v>44860</v>
+        <v>44799</v>
       </c>
       <c r="D1591" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RMT20X250S</t>
+            <t xml:space="preserve">HCW15-M</t>
           </r>
         </is>
       </c>
       <c r="E1591" s="1" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="F1591" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">19/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1592" customHeight="1" ht="20">
       <c r="A1592" s="1" t="n">
-        <v>1607866</v>
+        <v>1598892</v>
       </c>
       <c r="B1592" s="1" t="n">
-        <v>82</v>
+        <v>27486</v>
       </c>
       <c r="C1592" s="1" t="n">
-        <v>44801</v>
+        <v>44860</v>
       </c>
       <c r="D1592" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">HCW25-M</t>
+            <t xml:space="preserve">RMT20X250S</t>
           </r>
         </is>
       </c>
       <c r="E1592" s="1" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="F1592" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/11/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1593" customHeight="1" ht="20">
       <c r="A1593" s="1" t="n">
-        <v>1542689</v>
+        <v>1607866</v>
       </c>
       <c r="B1593" s="1" t="n">
-        <v>24951</v>
+        <v>82</v>
       </c>
       <c r="C1593" s="1" t="n">
-        <v>44463</v>
+        <v>44801</v>
       </c>
       <c r="D1593" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TPU-0855-BL-100M</t>
+            <t xml:space="preserve">HCW25-M</t>
           </r>
         </is>
       </c>
       <c r="E1593" s="1" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F1593" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/11/2026</t>
+            <t xml:space="preserve">19/11/2026</t>
           </r>
         </is>
       </c>
@@ -51101,14 +51101,14 @@
         <v>24951</v>
       </c>
       <c r="C1594" s="1" t="n">
-        <v>44470</v>
+        <v>44463</v>
       </c>
       <c r="D1594" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TPUC-1065-BL-100M</t>
+            <t xml:space="preserve">TPU-0855-BL-100M</t>
           </r>
         </is>
       </c>
@@ -51127,32 +51127,32 @@
     </row>
     <row r="1595" customHeight="1" ht="20">
       <c r="A1595" s="1" t="n">
-        <v>1607866</v>
+        <v>1542689</v>
       </c>
       <c r="B1595" s="1" t="n">
-        <v>82</v>
+        <v>24951</v>
       </c>
       <c r="C1595" s="1" t="n">
-        <v>44794</v>
+        <v>44470</v>
       </c>
       <c r="D1595" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">HCH15-M</t>
+            <t xml:space="preserve">TPUC-1065-BL-100M</t>
           </r>
         </is>
       </c>
       <c r="E1595" s="1" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F1595" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/11/2026</t>
+            <t xml:space="preserve">23/11/2026</t>
           </r>
         </is>
       </c>
@@ -51165,19 +51165,19 @@
         <v>82</v>
       </c>
       <c r="C1596" s="1" t="n">
-        <v>44795</v>
+        <v>44794</v>
       </c>
       <c r="D1596" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">HCH20-M</t>
+            <t xml:space="preserve">HCH15-M</t>
           </r>
         </is>
       </c>
       <c r="E1596" s="1" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F1596" s="1" t="inlineStr">
         <is>
@@ -51191,128 +51191,128 @@
     </row>
     <row r="1597" customHeight="1" ht="20">
       <c r="A1597" s="1" t="n">
-        <v>1598892</v>
+        <v>1607866</v>
       </c>
       <c r="B1597" s="1" t="n">
-        <v>27486</v>
+        <v>82</v>
       </c>
       <c r="C1597" s="1" t="n">
-        <v>45086</v>
+        <v>44795</v>
       </c>
       <c r="D1597" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">PB12X90SU</t>
+            <t xml:space="preserve">HCH20-M</t>
           </r>
         </is>
       </c>
       <c r="E1597" s="1" t="n">
-        <v>10</v>
+        <v>400</v>
       </c>
       <c r="F1597" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">19/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1598" customHeight="1" ht="20">
       <c r="A1598" s="1" t="n">
-        <v>1542689</v>
+        <v>1598892</v>
       </c>
       <c r="B1598" s="1" t="n">
-        <v>24951</v>
+        <v>27486</v>
       </c>
       <c r="C1598" s="1" t="n">
-        <v>44460</v>
+        <v>45086</v>
       </c>
       <c r="D1598" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TPE-0855-BL-5</t>
+            <t xml:space="preserve">PB12X90SU</t>
           </r>
         </is>
       </c>
       <c r="E1598" s="1" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="F1598" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/11/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1599" customHeight="1" ht="20">
       <c r="A1599" s="1" t="n">
-        <v>1628645</v>
+        <v>1542689</v>
       </c>
       <c r="B1599" s="1" t="n">
-        <v>45</v>
+        <v>24951</v>
       </c>
       <c r="C1599" s="1" t="n">
-        <v>44976</v>
+        <v>44460</v>
       </c>
       <c r="D1599" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TR4025P-BR</t>
+            <t xml:space="preserve">TPE-0855-BL-5</t>
           </r>
         </is>
       </c>
       <c r="E1599" s="1" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="F1599" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">23/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1600" customHeight="1" ht="20">
       <c r="A1600" s="1" t="n">
-        <v>1598892</v>
+        <v>1628645</v>
       </c>
       <c r="B1600" s="1" t="n">
-        <v>27486</v>
+        <v>45</v>
       </c>
       <c r="C1600" s="1" t="n">
-        <v>44613</v>
+        <v>44976</v>
       </c>
       <c r="D1600" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MFCJ32X40-20S</t>
+            <t xml:space="preserve">TR4025P-BR</t>
           </r>
         </is>
       </c>
       <c r="E1600" s="1" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F1600" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">16/10/2026</t>
           </r>
         </is>
       </c>
@@ -51325,19 +51325,19 @@
         <v>27486</v>
       </c>
       <c r="C1601" s="1" t="n">
-        <v>44858</v>
+        <v>44613</v>
       </c>
       <c r="D1601" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RMTL10X50S</t>
+            <t xml:space="preserve">MFCJ32X40-20S</t>
           </r>
         </is>
       </c>
       <c r="E1601" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1601" s="1" t="inlineStr">
         <is>
@@ -51351,313 +51351,313 @@
     </row>
     <row r="1602" customHeight="1" ht="20">
       <c r="A1602" s="1" t="n">
-        <v>1542689</v>
+        <v>1598892</v>
       </c>
       <c r="B1602" s="1" t="n">
-        <v>24951</v>
+        <v>27486</v>
       </c>
       <c r="C1602" s="1" t="n">
-        <v>44465</v>
+        <v>44858</v>
       </c>
       <c r="D1602" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TPU-1208-BL-100M</t>
+            <t xml:space="preserve">RMTL10X50S</t>
           </r>
         </is>
       </c>
       <c r="E1602" s="1" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F1602" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/11/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1603" customHeight="1" ht="20">
       <c r="A1603" s="1" t="n">
-        <v>1598892</v>
+        <v>1542689</v>
       </c>
       <c r="B1603" s="1" t="n">
-        <v>27486</v>
+        <v>24951</v>
       </c>
       <c r="C1603" s="1" t="n">
-        <v>44859</v>
+        <v>44465</v>
       </c>
       <c r="D1603" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RMT20X150S</t>
+            <t xml:space="preserve">TPU-1208-BL-100M</t>
           </r>
         </is>
       </c>
       <c r="E1603" s="1" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F1603" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1604" customHeight="1" ht="20">
       <c r="A1604" s="1" t="n">
-        <v>1542689</v>
+        <v>1598892</v>
       </c>
       <c r="B1604" s="1" t="n">
-        <v>24951</v>
+        <v>27486</v>
       </c>
       <c r="C1604" s="1" t="n">
-        <v>44464</v>
+        <v>44859</v>
       </c>
       <c r="D1604" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TPU-1065-BL-100M</t>
+            <t xml:space="preserve">RMT20X150S</t>
           </r>
         </is>
       </c>
       <c r="E1604" s="1" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="F1604" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/11/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1605" customHeight="1" ht="20">
       <c r="A1605" s="1" t="n">
-        <v>1598892</v>
+        <v>1542689</v>
       </c>
       <c r="B1605" s="1" t="n">
-        <v>27486</v>
+        <v>24951</v>
       </c>
       <c r="C1605" s="1" t="n">
-        <v>45081</v>
+        <v>44464</v>
       </c>
       <c r="D1605" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">GPLL803</t>
+            <t xml:space="preserve">TPU-1065-BL-100M</t>
           </r>
         </is>
       </c>
       <c r="E1605" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F1605" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1606" customHeight="1" ht="20">
       <c r="A1606" s="1" t="n">
-        <v>1607866</v>
+        <v>1598892</v>
       </c>
       <c r="B1606" s="1" t="n">
-        <v>82</v>
+        <v>27486</v>
       </c>
       <c r="C1606" s="1" t="n">
-        <v>44800</v>
+        <v>45081</v>
       </c>
       <c r="D1606" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">HCW20-M</t>
+            <t xml:space="preserve">GPLL803</t>
           </r>
         </is>
       </c>
       <c r="E1606" s="1" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F1606" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/11/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1607" customHeight="1" ht="20">
       <c r="A1607" s="1" t="n">
-        <v>1542689</v>
+        <v>1607866</v>
       </c>
       <c r="B1607" s="1" t="n">
-        <v>24951</v>
+        <v>82</v>
       </c>
       <c r="C1607" s="1" t="n">
-        <v>44468</v>
+        <v>44800</v>
       </c>
       <c r="D1607" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TPUC-0604-BL-100M</t>
+            <t xml:space="preserve">HCW20-M</t>
           </r>
         </is>
       </c>
       <c r="E1607" s="1" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="F1607" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/11/2026</t>
+            <t xml:space="preserve">19/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1608" customHeight="1" ht="20">
       <c r="A1608" s="1" t="n">
-        <v>1598892</v>
+        <v>1542689</v>
       </c>
       <c r="B1608" s="1" t="n">
-        <v>27486</v>
+        <v>24951</v>
       </c>
       <c r="C1608" s="1" t="n">
-        <v>45101</v>
+        <v>44468</v>
       </c>
       <c r="D1608" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">6D1H6F-J06BD6</t>
+            <t xml:space="preserve">TPUC-0604-BL-100M</t>
           </r>
         </is>
       </c>
       <c r="E1608" s="1" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="F1608" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1609" customHeight="1" ht="20">
       <c r="A1609" s="1" t="n">
-        <v>1542689</v>
+        <v>1598892</v>
       </c>
       <c r="B1609" s="1" t="n">
-        <v>24951</v>
+        <v>27486</v>
       </c>
       <c r="C1609" s="1" t="n">
-        <v>44461</v>
+        <v>45101</v>
       </c>
       <c r="D1609" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TPU-0425-BL-100M</t>
+            <t xml:space="preserve">6D1H6F-J06BD6</t>
           </r>
         </is>
       </c>
       <c r="E1609" s="1" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="F1609" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/11/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1610" customHeight="1" ht="20">
       <c r="A1610" s="1" t="n">
-        <v>1523488</v>
+        <v>1542689</v>
       </c>
       <c r="B1610" s="1" t="n">
-        <v>24896</v>
+        <v>24951</v>
       </c>
       <c r="C1610" s="1" t="n">
-        <v>44696</v>
+        <v>44461</v>
       </c>
       <c r="D1610" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">NBRGHP-0113A</t>
+            <t xml:space="preserve">TPU-0425-BL-100M</t>
           </r>
         </is>
       </c>
       <c r="E1610" s="1" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="F1610" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">23/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1611" customHeight="1" ht="20">
       <c r="A1611" s="1" t="n">
-        <v>1632953</v>
+        <v>1523488</v>
       </c>
       <c r="B1611" s="1" t="n">
-        <v>46</v>
+        <v>24896</v>
       </c>
       <c r="C1611" s="1" t="n">
-        <v>46147</v>
+        <v>44696</v>
       </c>
       <c r="D1611" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">AD32340G-BR</t>
+            <t xml:space="preserve">NBRGHP-0113A</t>
           </r>
         </is>
       </c>
       <c r="E1611" s="1" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="F1611" s="1" t="inlineStr">
         <is>
@@ -51671,96 +51671,96 @@
     </row>
     <row r="1612" customHeight="1" ht="20">
       <c r="A1612" s="1" t="n">
-        <v>1598892</v>
+        <v>1632953</v>
       </c>
       <c r="B1612" s="1" t="n">
-        <v>27486</v>
+        <v>46</v>
       </c>
       <c r="C1612" s="1" t="n">
-        <v>45945</v>
+        <v>46147</v>
       </c>
       <c r="D1612" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MD20X40S</t>
+            <t xml:space="preserve">AD32340G-BR</t>
           </r>
         </is>
       </c>
       <c r="E1612" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F1612" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1613" customHeight="1" ht="20">
       <c r="A1613" s="1" t="n">
-        <v>1604593</v>
+        <v>1598892</v>
       </c>
       <c r="B1613" s="1" t="n">
-        <v>81</v>
+        <v>27486</v>
       </c>
       <c r="C1613" s="1" t="n">
-        <v>45951</v>
+        <v>45945</v>
       </c>
       <c r="D1613" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">HCR15-700-E20</t>
+            <t xml:space="preserve">MD20X40S</t>
           </r>
         </is>
       </c>
       <c r="E1613" s="1" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F1613" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1614" customHeight="1" ht="20">
       <c r="A1614" s="1" t="n">
-        <v>1598892</v>
+        <v>1604593</v>
       </c>
       <c r="B1614" s="1" t="n">
-        <v>27486</v>
+        <v>81</v>
       </c>
       <c r="C1614" s="1" t="n">
-        <v>45775</v>
+        <v>45951</v>
       </c>
       <c r="D1614" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">F-SI50LB</t>
+            <t xml:space="preserve">HCR15-700-E20</t>
           </r>
         </is>
       </c>
       <c r="E1614" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F1614" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -51773,19 +51773,19 @@
         <v>27486</v>
       </c>
       <c r="C1615" s="1" t="n">
-        <v>45776</v>
+        <v>45775</v>
       </c>
       <c r="D1615" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">F-SI32LB</t>
+            <t xml:space="preserve">F-SI50LB</t>
           </r>
         </is>
       </c>
       <c r="E1615" s="1" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="F1615" s="1" t="inlineStr">
         <is>
@@ -51805,19 +51805,19 @@
         <v>27486</v>
       </c>
       <c r="C1616" s="1" t="n">
-        <v>45736</v>
+        <v>45776</v>
       </c>
       <c r="D1616" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACE25X10SB</t>
+            <t xml:space="preserve">F-SI32LB</t>
           </r>
         </is>
       </c>
       <c r="E1616" s="1" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F1616" s="1" t="inlineStr">
         <is>
@@ -51837,19 +51837,19 @@
         <v>27486</v>
       </c>
       <c r="C1617" s="1" t="n">
-        <v>45470</v>
+        <v>45736</v>
       </c>
       <c r="D1617" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">GPH802</t>
+            <t xml:space="preserve">ACE25X10SB</t>
           </r>
         </is>
       </c>
       <c r="E1617" s="1" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F1617" s="1" t="inlineStr">
         <is>
@@ -51869,19 +51869,19 @@
         <v>27486</v>
       </c>
       <c r="C1618" s="1" t="n">
-        <v>45790</v>
+        <v>45470</v>
       </c>
       <c r="D1618" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">7SV31010BD</t>
+            <t xml:space="preserve">GPH802</t>
           </r>
         </is>
       </c>
       <c r="E1618" s="1" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="F1618" s="1" t="inlineStr">
         <is>
@@ -51901,14 +51901,14 @@
         <v>27486</v>
       </c>
       <c r="C1619" s="1" t="n">
-        <v>45738</v>
+        <v>45790</v>
       </c>
       <c r="D1619" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACE40X10SBG</t>
+            <t xml:space="preserve">7SV31010BD</t>
           </r>
         </is>
       </c>
@@ -51933,19 +51933,19 @@
         <v>27486</v>
       </c>
       <c r="C1620" s="1" t="n">
-        <v>45469</v>
+        <v>45738</v>
       </c>
       <c r="D1620" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">GPH801</t>
+            <t xml:space="preserve">ACE40X10SBG</t>
           </r>
         </is>
       </c>
       <c r="E1620" s="1" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F1620" s="1" t="inlineStr">
         <is>
@@ -51965,19 +51965,19 @@
         <v>27486</v>
       </c>
       <c r="C1621" s="1" t="n">
-        <v>45777</v>
+        <v>45469</v>
       </c>
       <c r="D1621" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">F-SI40LB</t>
+            <t xml:space="preserve">GPH801</t>
           </r>
         </is>
       </c>
       <c r="E1621" s="1" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F1621" s="1" t="inlineStr">
         <is>
@@ -51997,19 +51997,19 @@
         <v>27486</v>
       </c>
       <c r="C1622" s="1" t="n">
-        <v>45572</v>
+        <v>45777</v>
       </c>
       <c r="D1622" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CMSG-020-H</t>
+            <t xml:space="preserve">F-SI40LB</t>
           </r>
         </is>
       </c>
       <c r="E1622" s="1" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F1622" s="1" t="inlineStr">
         <is>
@@ -52023,10 +52023,10 @@
     </row>
     <row r="1623" customHeight="1" ht="20">
       <c r="A1623" s="1" t="n">
-        <v>1624906</v>
+        <v>1598892</v>
       </c>
       <c r="B1623" s="1" t="n">
-        <v>29565</v>
+        <v>27486</v>
       </c>
       <c r="C1623" s="1" t="n">
         <v>45572</v>
@@ -52041,46 +52041,46 @@
         </is>
       </c>
       <c r="E1623" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1623" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/11/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1624" customHeight="1" ht="20">
       <c r="A1624" s="1" t="n">
-        <v>1598892</v>
+        <v>1624906</v>
       </c>
       <c r="B1624" s="1" t="n">
-        <v>27486</v>
+        <v>29565</v>
       </c>
       <c r="C1624" s="1" t="n">
-        <v>45743</v>
+        <v>45572</v>
       </c>
       <c r="D1624" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SAI100X200SNG</t>
+            <t xml:space="preserve">CMSG-020-H</t>
           </r>
         </is>
       </c>
       <c r="E1624" s="1" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F1624" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">08/11/2026</t>
           </r>
         </is>
       </c>
@@ -52093,14 +52093,14 @@
         <v>27486</v>
       </c>
       <c r="C1625" s="1" t="n">
-        <v>45746</v>
+        <v>45743</v>
       </c>
       <c r="D1625" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SAI40X30SNG</t>
+            <t xml:space="preserve">SAI100X200SNG</t>
           </r>
         </is>
       </c>
@@ -52125,19 +52125,19 @@
         <v>27486</v>
       </c>
       <c r="C1626" s="1" t="n">
-        <v>45605</v>
+        <v>45746</v>
       </c>
       <c r="D1626" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">UWS98A06004050MBU</t>
+            <t xml:space="preserve">SAI40X30SNG</t>
           </r>
         </is>
       </c>
       <c r="E1626" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F1626" s="1" t="inlineStr">
         <is>
@@ -52157,19 +52157,19 @@
         <v>27486</v>
       </c>
       <c r="C1627" s="1" t="n">
-        <v>45762</v>
+        <v>45605</v>
       </c>
       <c r="D1627" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MIC25X75SCAG</t>
+            <t xml:space="preserve">UWS98A06004050MBU</t>
           </r>
         </is>
       </c>
       <c r="E1627" s="1" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F1627" s="1" t="inlineStr">
         <is>
@@ -52183,128 +52183,128 @@
     </row>
     <row r="1628" customHeight="1" ht="20">
       <c r="A1628" s="1" t="n">
-        <v>1604593</v>
+        <v>1598892</v>
       </c>
       <c r="B1628" s="1" t="n">
-        <v>81</v>
+        <v>27486</v>
       </c>
       <c r="C1628" s="1" t="n">
-        <v>45900</v>
+        <v>45762</v>
       </c>
       <c r="D1628" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BK25</t>
+            <t xml:space="preserve">MIC25X75SCAG</t>
           </r>
         </is>
       </c>
       <c r="E1628" s="1" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F1628" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1629" customHeight="1" ht="20">
       <c r="A1629" s="1" t="n">
-        <v>1598892</v>
+        <v>1604593</v>
       </c>
       <c r="B1629" s="1" t="n">
-        <v>27486</v>
+        <v>81</v>
       </c>
       <c r="C1629" s="1" t="n">
-        <v>45468</v>
+        <v>45900</v>
       </c>
       <c r="D1629" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">GPH602</t>
+            <t xml:space="preserve">BK25</t>
           </r>
         </is>
       </c>
       <c r="E1629" s="1" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F1629" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1630" customHeight="1" ht="20">
       <c r="A1630" s="1" t="n">
-        <v>1604593</v>
+        <v>1598892</v>
       </c>
       <c r="B1630" s="1" t="n">
-        <v>81</v>
+        <v>27486</v>
       </c>
       <c r="C1630" s="1" t="n">
-        <v>45950</v>
+        <v>45468</v>
       </c>
       <c r="D1630" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">HCR15-2000-E10</t>
+            <t xml:space="preserve">GPH602</t>
           </r>
         </is>
       </c>
       <c r="E1630" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F1630" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1631" customHeight="1" ht="20">
       <c r="A1631" s="1" t="n">
-        <v>1598892</v>
+        <v>1604593</v>
       </c>
       <c r="B1631" s="1" t="n">
-        <v>27486</v>
+        <v>81</v>
       </c>
       <c r="C1631" s="1" t="n">
-        <v>45737</v>
+        <v>45950</v>
       </c>
       <c r="D1631" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACE32X40SG</t>
+            <t xml:space="preserve">HCR15-2000-E10</t>
           </r>
         </is>
       </c>
       <c r="E1631" s="1" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F1631" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -52317,19 +52317,19 @@
         <v>27486</v>
       </c>
       <c r="C1632" s="1" t="n">
-        <v>45739</v>
+        <v>45737</v>
       </c>
       <c r="D1632" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACE50X25SG</t>
+            <t xml:space="preserve">ACE32X40SG</t>
           </r>
         </is>
       </c>
       <c r="E1632" s="1" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F1632" s="1" t="inlineStr">
         <is>
@@ -52349,14 +52349,14 @@
         <v>27486</v>
       </c>
       <c r="C1633" s="1" t="n">
-        <v>45740</v>
+        <v>45739</v>
       </c>
       <c r="D1633" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACE50X30SG</t>
+            <t xml:space="preserve">ACE50X25SG</t>
           </r>
         </is>
       </c>
@@ -52381,19 +52381,19 @@
         <v>27486</v>
       </c>
       <c r="C1634" s="1" t="n">
-        <v>45814</v>
+        <v>45740</v>
       </c>
       <c r="D1634" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TCM80X60SG</t>
+            <t xml:space="preserve">ACE50X30SG</t>
           </r>
         </is>
       </c>
       <c r="E1634" s="1" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F1634" s="1" t="inlineStr">
         <is>
@@ -52413,19 +52413,19 @@
         <v>27486</v>
       </c>
       <c r="C1635" s="1" t="n">
-        <v>45744</v>
+        <v>45814</v>
       </c>
       <c r="D1635" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SAI32X60SNG</t>
+            <t xml:space="preserve">TCM80X60SG</t>
           </r>
         </is>
       </c>
       <c r="E1635" s="1" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F1635" s="1" t="inlineStr">
         <is>
@@ -52439,128 +52439,128 @@
     </row>
     <row r="1636" customHeight="1" ht="20">
       <c r="A1636" s="1" t="n">
-        <v>1604593</v>
+        <v>1598892</v>
       </c>
       <c r="B1636" s="1" t="n">
-        <v>81</v>
+        <v>27486</v>
       </c>
       <c r="C1636" s="1" t="n">
-        <v>45955</v>
+        <v>45744</v>
       </c>
       <c r="D1636" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">HCR20-2000-E10</t>
+            <t xml:space="preserve">SAI32X60SNG</t>
           </r>
         </is>
       </c>
       <c r="E1636" s="1" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F1636" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1637" customHeight="1" ht="20">
       <c r="A1637" s="1" t="n">
-        <v>1598892</v>
+        <v>1604593</v>
       </c>
       <c r="B1637" s="1" t="n">
-        <v>27486</v>
+        <v>81</v>
       </c>
       <c r="C1637" s="1" t="n">
-        <v>45742</v>
+        <v>45955</v>
       </c>
       <c r="D1637" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MIC25X160SCAG</t>
+            <t xml:space="preserve">HCR20-2000-E10</t>
           </r>
         </is>
       </c>
       <c r="E1637" s="1" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F1637" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1638" customHeight="1" ht="20">
       <c r="A1638" s="1" t="n">
-        <v>1604593</v>
+        <v>1598892</v>
       </c>
       <c r="B1638" s="1" t="n">
-        <v>81</v>
+        <v>27486</v>
       </c>
       <c r="C1638" s="1" t="n">
-        <v>45956</v>
+        <v>45742</v>
       </c>
       <c r="D1638" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">HCR25-1300-E20</t>
+            <t xml:space="preserve">MIC25X160SCAG</t>
           </r>
         </is>
       </c>
       <c r="E1638" s="1" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F1638" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1639" customHeight="1" ht="20">
       <c r="A1639" s="1" t="n">
-        <v>1598892</v>
+        <v>1604593</v>
       </c>
       <c r="B1639" s="1" t="n">
-        <v>27486</v>
+        <v>81</v>
       </c>
       <c r="C1639" s="1" t="n">
-        <v>46101</v>
+        <v>45956</v>
       </c>
       <c r="D1639" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">3F21006G</t>
+            <t xml:space="preserve">HCR25-1300-E20</t>
           </r>
         </is>
       </c>
       <c r="E1639" s="1" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F1639" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -52573,19 +52573,19 @@
         <v>27486</v>
       </c>
       <c r="C1640" s="1" t="n">
-        <v>45747</v>
+        <v>46101</v>
       </c>
       <c r="D1640" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SAI40X40SNG</t>
+            <t xml:space="preserve">3F21006G</t>
           </r>
         </is>
       </c>
       <c r="E1640" s="1" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F1640" s="1" t="inlineStr">
         <is>
@@ -52605,19 +52605,19 @@
         <v>27486</v>
       </c>
       <c r="C1641" s="1" t="n">
-        <v>45785</v>
+        <v>45747</v>
       </c>
       <c r="D1641" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CPSV15CD</t>
+            <t xml:space="preserve">SAI40X40SNG</t>
           </r>
         </is>
       </c>
       <c r="E1641" s="1" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F1641" s="1" t="inlineStr">
         <is>
@@ -52631,64 +52631,64 @@
     </row>
     <row r="1642" customHeight="1" ht="20">
       <c r="A1642" s="1" t="n">
-        <v>1604593</v>
+        <v>1598892</v>
       </c>
       <c r="B1642" s="1" t="n">
-        <v>81</v>
+        <v>27486</v>
       </c>
       <c r="C1642" s="1" t="n">
-        <v>45957</v>
+        <v>45785</v>
       </c>
       <c r="D1642" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">HCR25-2000-E10</t>
+            <t xml:space="preserve">CPSV15CD</t>
           </r>
         </is>
       </c>
       <c r="E1642" s="1" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F1642" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1643" customHeight="1" ht="20">
       <c r="A1643" s="1" t="n">
-        <v>1598892</v>
+        <v>1604593</v>
       </c>
       <c r="B1643" s="1" t="n">
-        <v>27486</v>
+        <v>81</v>
       </c>
       <c r="C1643" s="1" t="n">
-        <v>45745</v>
+        <v>45957</v>
       </c>
       <c r="D1643" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SAI40X250SNG</t>
+            <t xml:space="preserve">HCR25-2000-E10</t>
           </r>
         </is>
       </c>
       <c r="E1643" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F1643" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -52701,19 +52701,19 @@
         <v>27486</v>
       </c>
       <c r="C1644" s="1" t="n">
-        <v>45786</v>
+        <v>45745</v>
       </c>
       <c r="D1644" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CPSV15ED</t>
+            <t xml:space="preserve">SAI40X250SNG</t>
           </r>
         </is>
       </c>
       <c r="E1644" s="1" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F1644" s="1" t="inlineStr">
         <is>
@@ -52733,19 +52733,19 @@
         <v>27486</v>
       </c>
       <c r="C1645" s="1" t="n">
-        <v>45778</v>
+        <v>45786</v>
       </c>
       <c r="D1645" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">F-SI63LB</t>
+            <t xml:space="preserve">CPSV15ED</t>
           </r>
         </is>
       </c>
       <c r="E1645" s="1" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F1645" s="1" t="inlineStr">
         <is>
@@ -52759,74 +52759,74 @@
     </row>
     <row r="1646" customHeight="1" ht="20">
       <c r="A1646" s="1" t="n">
-        <v>1604593</v>
+        <v>1598892</v>
       </c>
       <c r="B1646" s="1" t="n">
-        <v>81</v>
+        <v>27486</v>
       </c>
       <c r="C1646" s="1" t="n">
-        <v>45946</v>
+        <v>45778</v>
       </c>
       <c r="D1646" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">EIXO-12-1000</t>
+            <t xml:space="preserve">F-SI63LB</t>
           </r>
         </is>
       </c>
       <c r="E1646" s="1" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F1646" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1647" customHeight="1" ht="20">
       <c r="A1647" s="1" t="n">
-        <v>1634902</v>
+        <v>1604593</v>
       </c>
       <c r="B1647" s="1" t="n">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="C1647" s="1" t="n">
-        <v>45589</v>
+        <v>45946</v>
       </c>
       <c r="D1647" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LU630P-BR</t>
+            <t xml:space="preserve">EIXO-12-1000</t>
           </r>
         </is>
       </c>
       <c r="E1647" s="1" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="F1647" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/10/2026</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1648" customHeight="1" ht="20">
       <c r="A1648" s="1" t="n">
-        <v>1628645</v>
+        <v>1634902</v>
       </c>
       <c r="B1648" s="1" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C1648" s="1" t="n">
         <v>45589</v>
@@ -52841,46 +52841,46 @@
         </is>
       </c>
       <c r="E1648" s="1" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F1648" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">27/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1649" customHeight="1" ht="20">
       <c r="A1649" s="1" t="n">
-        <v>1598892</v>
+        <v>1628645</v>
       </c>
       <c r="B1649" s="1" t="n">
-        <v>27486</v>
+        <v>45</v>
       </c>
       <c r="C1649" s="1" t="n">
-        <v>45748</v>
+        <v>45589</v>
       </c>
       <c r="D1649" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SAI50X160SNG</t>
+            <t xml:space="preserve">LU630P-BR</t>
           </r>
         </is>
       </c>
       <c r="E1649" s="1" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F1649" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">16/10/2026</t>
           </r>
         </is>
       </c>
@@ -52893,19 +52893,19 @@
         <v>27486</v>
       </c>
       <c r="C1650" s="1" t="n">
-        <v>45787</v>
+        <v>45748</v>
       </c>
       <c r="D1650" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CPSV15FD</t>
+            <t xml:space="preserve">SAI50X160SNG</t>
           </r>
         </is>
       </c>
       <c r="E1650" s="1" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F1650" s="1" t="inlineStr">
         <is>
@@ -52925,14 +52925,14 @@
         <v>27486</v>
       </c>
       <c r="C1651" s="1" t="n">
-        <v>45780</v>
+        <v>45787</v>
       </c>
       <c r="D1651" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">F-SI125LB</t>
+            <t xml:space="preserve">CPSV15FD</t>
           </r>
         </is>
       </c>
@@ -52951,128 +52951,128 @@
     </row>
     <row r="1652" customHeight="1" ht="20">
       <c r="A1652" s="1" t="n">
-        <v>1604593</v>
+        <v>1598892</v>
       </c>
       <c r="B1652" s="1" t="n">
-        <v>81</v>
+        <v>27486</v>
       </c>
       <c r="C1652" s="1" t="n">
-        <v>45949</v>
+        <v>45780</v>
       </c>
       <c r="D1652" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">EIXO-30-1000</t>
+            <t xml:space="preserve">F-SI125LB</t>
           </r>
         </is>
       </c>
       <c r="E1652" s="1" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F1652" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1653" customHeight="1" ht="20">
       <c r="A1653" s="1" t="n">
-        <v>1635772</v>
+        <v>1604593</v>
       </c>
       <c r="B1653" s="1" t="n">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="C1653" s="1" t="n">
-        <v>46445</v>
+        <v>45949</v>
       </c>
       <c r="D1653" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SFU5010-325-X98-110-BR</t>
+            <t xml:space="preserve">EIXO-30-1000</t>
           </r>
         </is>
       </c>
       <c r="E1653" s="1" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="F1653" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1654" customHeight="1" ht="20">
       <c r="A1654" s="1" t="n">
-        <v>1604593</v>
+        <v>1635772</v>
       </c>
       <c r="B1654" s="1" t="n">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="C1654" s="1" t="n">
-        <v>45948</v>
+        <v>46445</v>
       </c>
       <c r="D1654" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">EIXO-16-500</t>
+            <t xml:space="preserve">SFU5010-325-X98-110-BR</t>
           </r>
         </is>
       </c>
       <c r="E1654" s="1" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="F1654" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">01/01/2027</t>
+            <t xml:space="preserve">16/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1655" customHeight="1" ht="20">
       <c r="A1655" s="1" t="n">
-        <v>1624906</v>
+        <v>1604593</v>
       </c>
       <c r="B1655" s="1" t="n">
-        <v>29565</v>
+        <v>81</v>
       </c>
       <c r="C1655" s="1" t="n">
-        <v>46403</v>
+        <v>45948</v>
       </c>
       <c r="D1655" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">HLS12X50SAS</t>
+            <t xml:space="preserve">EIXO-16-500</t>
           </r>
         </is>
       </c>
       <c r="E1655" s="1" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="F1655" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/11/2026</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -53097,7 +53097,7 @@
         </is>
       </c>
       <c r="E1656" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1656" s="1" t="inlineStr">
         <is>
@@ -53111,64 +53111,64 @@
     </row>
     <row r="1657" customHeight="1" ht="20">
       <c r="A1657" s="1" t="n">
-        <v>1617063</v>
+        <v>1624906</v>
       </c>
       <c r="B1657" s="1" t="n">
-        <v>29511</v>
+        <v>29565</v>
       </c>
       <c r="C1657" s="1" t="n">
-        <v>46409</v>
+        <v>46403</v>
       </c>
       <c r="D1657" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">EGT190</t>
+            <t xml:space="preserve">HLS12X50SAS</t>
           </r>
         </is>
       </c>
       <c r="E1657" s="1" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F1657" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/12/2026</t>
+            <t xml:space="preserve">08/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1658" customHeight="1" ht="20">
       <c r="A1658" s="1" t="n">
-        <v>1598892</v>
+        <v>1617063</v>
       </c>
       <c r="B1658" s="1" t="n">
-        <v>27486</v>
+        <v>29511</v>
       </c>
       <c r="C1658" s="1" t="n">
-        <v>45741</v>
+        <v>46409</v>
       </c>
       <c r="D1658" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MI25X35SCAG</t>
+            <t xml:space="preserve">EGT190</t>
           </r>
         </is>
       </c>
       <c r="E1658" s="1" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F1658" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">08/12/2026</t>
           </r>
         </is>
       </c>
@@ -53181,19 +53181,19 @@
         <v>27486</v>
       </c>
       <c r="C1659" s="1" t="n">
-        <v>45783</v>
+        <v>45741</v>
       </c>
       <c r="D1659" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CPSV15AD</t>
+            <t xml:space="preserve">MI25X35SCAG</t>
           </r>
         </is>
       </c>
       <c r="E1659" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F1659" s="1" t="inlineStr">
         <is>
@@ -53207,64 +53207,64 @@
     </row>
     <row r="1660" customHeight="1" ht="20">
       <c r="A1660" s="1" t="n">
-        <v>1624906</v>
+        <v>1598892</v>
       </c>
       <c r="B1660" s="1" t="n">
-        <v>29565</v>
+        <v>27486</v>
       </c>
       <c r="C1660" s="1" t="n">
-        <v>46338</v>
+        <v>45783</v>
       </c>
       <c r="D1660" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MBLJ20X125-100S</t>
+            <t xml:space="preserve">CPSV15AD</t>
           </r>
         </is>
       </c>
       <c r="E1660" s="1" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F1660" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/11/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1661" customHeight="1" ht="20">
       <c r="A1661" s="1" t="n">
-        <v>1598892</v>
+        <v>1624906</v>
       </c>
       <c r="B1661" s="1" t="n">
-        <v>27486</v>
+        <v>29565</v>
       </c>
       <c r="C1661" s="1" t="n">
-        <v>45735</v>
+        <v>46338</v>
       </c>
       <c r="D1661" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">2WA15015BG</t>
+            <t xml:space="preserve">MBLJ20X125-100S</t>
           </r>
         </is>
       </c>
       <c r="E1661" s="1" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F1661" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">08/11/2026</t>
           </r>
         </is>
       </c>
@@ -53277,19 +53277,19 @@
         <v>27486</v>
       </c>
       <c r="C1662" s="1" t="n">
-        <v>45782</v>
+        <v>45735</v>
       </c>
       <c r="D1662" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">F-SI200LB</t>
+            <t xml:space="preserve">2WA15015BG</t>
           </r>
         </is>
       </c>
       <c r="E1662" s="1" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F1662" s="1" t="inlineStr">
         <is>
@@ -53309,19 +53309,19 @@
         <v>27486</v>
       </c>
       <c r="C1663" s="1" t="n">
-        <v>45467</v>
+        <v>45782</v>
       </c>
       <c r="D1663" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">GPH601</t>
+            <t xml:space="preserve">F-SI200LB</t>
           </r>
         </is>
       </c>
       <c r="E1663" s="1" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F1663" s="1" t="inlineStr">
         <is>
@@ -53341,19 +53341,19 @@
         <v>27486</v>
       </c>
       <c r="C1664" s="1" t="n">
-        <v>45473</v>
+        <v>45467</v>
       </c>
       <c r="D1664" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">GPH1002</t>
+            <t xml:space="preserve">GPH601</t>
           </r>
         </is>
       </c>
       <c r="E1664" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F1664" s="1" t="inlineStr">
         <is>
@@ -53373,19 +53373,19 @@
         <v>27486</v>
       </c>
       <c r="C1665" s="1" t="n">
-        <v>45784</v>
+        <v>45473</v>
       </c>
       <c r="D1665" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CPSV15BD</t>
+            <t xml:space="preserve">GPH1002</t>
           </r>
         </is>
       </c>
       <c r="E1665" s="1" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="F1665" s="1" t="inlineStr">
         <is>
@@ -53405,19 +53405,19 @@
         <v>27486</v>
       </c>
       <c r="C1666" s="1" t="n">
-        <v>45779</v>
+        <v>45784</v>
       </c>
       <c r="D1666" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">F-SI100LB</t>
+            <t xml:space="preserve">CPSV15BD</t>
           </r>
         </is>
       </c>
       <c r="E1666" s="1" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F1666" s="1" t="inlineStr">
         <is>
@@ -53437,19 +53437,19 @@
         <v>27486</v>
       </c>
       <c r="C1667" s="1" t="n">
-        <v>45781</v>
+        <v>45779</v>
       </c>
       <c r="D1667" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">F-SI160LB</t>
+            <t xml:space="preserve">F-SI100LB</t>
           </r>
         </is>
       </c>
       <c r="E1667" s="1" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F1667" s="1" t="inlineStr">
         <is>
@@ -53463,64 +53463,64 @@
     </row>
     <row r="1668" customHeight="1" ht="20">
       <c r="A1668" s="1" t="n">
-        <v>1607866</v>
+        <v>1598892</v>
       </c>
       <c r="B1668" s="1" t="n">
-        <v>82</v>
+        <v>27486</v>
       </c>
       <c r="C1668" s="1" t="n">
-        <v>45905</v>
+        <v>45781</v>
       </c>
       <c r="D1668" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BF25</t>
+            <t xml:space="preserve">F-SI160LB</t>
           </r>
         </is>
       </c>
       <c r="E1668" s="1" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F1668" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/11/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1669" customHeight="1" ht="20">
       <c r="A1669" s="1" t="n">
-        <v>1625869</v>
+        <v>1607866</v>
       </c>
       <c r="B1669" s="1" t="n">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="C1669" s="1" t="n">
-        <v>46778</v>
+        <v>45905</v>
       </c>
       <c r="D1669" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VR320G</t>
+            <t xml:space="preserve">BF25</t>
           </r>
         </is>
       </c>
       <c r="E1669" s="1" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="F1669" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">19/11/2026</t>
           </r>
         </is>
       </c>
@@ -53533,19 +53533,19 @@
         <v>43</v>
       </c>
       <c r="C1670" s="1" t="n">
-        <v>46753</v>
+        <v>46778</v>
       </c>
       <c r="D1670" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BU2520G</t>
+            <t xml:space="preserve">VR320G</t>
           </r>
         </is>
       </c>
       <c r="E1670" s="1" t="n">
-        <v>1400</v>
+        <v>90</v>
       </c>
       <c r="F1670" s="1" t="inlineStr">
         <is>
@@ -53565,19 +53565,19 @@
         <v>43</v>
       </c>
       <c r="C1671" s="1" t="n">
-        <v>46776</v>
+        <v>46753</v>
       </c>
       <c r="D1671" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VR200G</t>
+            <t xml:space="preserve">BU2520G</t>
           </r>
         </is>
       </c>
       <c r="E1671" s="1" t="n">
-        <v>120</v>
+        <v>1400</v>
       </c>
       <c r="F1671" s="1" t="inlineStr">
         <is>
@@ -53591,128 +53591,128 @@
     </row>
     <row r="1672" customHeight="1" ht="20">
       <c r="A1672" s="1" t="n">
-        <v>1563222</v>
+        <v>1625869</v>
       </c>
       <c r="B1672" s="1" t="n">
-        <v>25042</v>
+        <v>43</v>
       </c>
       <c r="C1672" s="1" t="n">
-        <v>46564</v>
+        <v>46776</v>
       </c>
       <c r="D1672" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">DG10P-02</t>
+            <t xml:space="preserve">VR200G</t>
           </r>
         </is>
       </c>
       <c r="E1672" s="1" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="F1672" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">09/11/2026</t>
+            <t xml:space="preserve">26/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1673" customHeight="1" ht="20">
       <c r="A1673" s="1" t="n">
-        <v>1624906</v>
+        <v>1635888</v>
       </c>
       <c r="B1673" s="1" t="n">
-        <v>29565</v>
+        <v>49</v>
       </c>
       <c r="C1673" s="1" t="n">
-        <v>46585</v>
+        <v>47030</v>
       </c>
       <c r="D1673" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACQD40X50SBG</t>
+            <t xml:space="preserve">WMD-90-BR</t>
           </r>
         </is>
       </c>
       <c r="E1673" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1673" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/11/2026</t>
+            <t xml:space="preserve">30/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1674" customHeight="1" ht="20">
       <c r="A1674" s="1" t="n">
-        <v>1625869</v>
+        <v>1563222</v>
       </c>
       <c r="B1674" s="1" t="n">
-        <v>43</v>
+        <v>25042</v>
       </c>
       <c r="C1674" s="1" t="n">
-        <v>46743</v>
+        <v>46564</v>
       </c>
       <c r="D1674" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BU3225P</t>
+            <t xml:space="preserve">DG10P-02</t>
           </r>
         </is>
       </c>
       <c r="E1674" s="1" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="F1674" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">09/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1675" customHeight="1" ht="20">
       <c r="A1675" s="1" t="n">
-        <v>1625869</v>
+        <v>1624906</v>
       </c>
       <c r="B1675" s="1" t="n">
-        <v>43</v>
+        <v>29565</v>
       </c>
       <c r="C1675" s="1" t="n">
-        <v>46750</v>
+        <v>46585</v>
       </c>
       <c r="D1675" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CL630P</t>
+            <t xml:space="preserve">ACQD40X50SBG</t>
           </r>
         </is>
       </c>
       <c r="E1675" s="1" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="F1675" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">08/11/2026</t>
           </r>
         </is>
       </c>
@@ -53725,19 +53725,19 @@
         <v>43</v>
       </c>
       <c r="C1676" s="1" t="n">
-        <v>46768</v>
+        <v>46743</v>
       </c>
       <c r="D1676" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SCK-40</t>
+            <t xml:space="preserve">BU3225P</t>
           </r>
         </is>
       </c>
       <c r="E1676" s="1" t="n">
-        <v>4500</v>
+        <v>800</v>
       </c>
       <c r="F1676" s="1" t="inlineStr">
         <is>
@@ -53757,19 +53757,19 @@
         <v>43</v>
       </c>
       <c r="C1677" s="1" t="n">
-        <v>46752</v>
+        <v>46750</v>
       </c>
       <c r="D1677" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RES900P</t>
+            <t xml:space="preserve">CL630P</t>
           </r>
         </is>
       </c>
       <c r="E1677" s="1" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="F1677" s="1" t="inlineStr">
         <is>
@@ -53789,19 +53789,19 @@
         <v>43</v>
       </c>
       <c r="C1678" s="1" t="n">
-        <v>46761</v>
+        <v>46768</v>
       </c>
       <c r="D1678" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CL400G</t>
+            <t xml:space="preserve">SCK-40</t>
           </r>
         </is>
       </c>
       <c r="E1678" s="1" t="n">
-        <v>120</v>
+        <v>4500</v>
       </c>
       <c r="F1678" s="1" t="inlineStr">
         <is>
@@ -53815,32 +53815,32 @@
     </row>
     <row r="1679" customHeight="1" ht="20">
       <c r="A1679" s="1" t="n">
-        <v>1625869</v>
+        <v>1635888</v>
       </c>
       <c r="B1679" s="1" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C1679" s="1" t="n">
-        <v>46744</v>
+        <v>47027</v>
       </c>
       <c r="D1679" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BU5032P</t>
+            <t xml:space="preserve">WMD-50-BR</t>
           </r>
         </is>
       </c>
       <c r="E1679" s="1" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="F1679" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">30/10/2026</t>
           </r>
         </is>
       </c>
@@ -53853,19 +53853,19 @@
         <v>43</v>
       </c>
       <c r="C1680" s="1" t="n">
-        <v>46745</v>
+        <v>46752</v>
       </c>
       <c r="D1680" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BU5040P</t>
+            <t xml:space="preserve">RES900P</t>
           </r>
         </is>
       </c>
       <c r="E1680" s="1" t="n">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="F1680" s="1" t="inlineStr">
         <is>
@@ -53885,19 +53885,19 @@
         <v>43</v>
       </c>
       <c r="C1681" s="1" t="n">
-        <v>46759</v>
+        <v>46761</v>
       </c>
       <c r="D1681" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MI252525G</t>
+            <t xml:space="preserve">CL400G</t>
           </r>
         </is>
       </c>
       <c r="E1681" s="1" t="n">
-        <v>1560</v>
+        <v>120</v>
       </c>
       <c r="F1681" s="1" t="inlineStr">
         <is>
@@ -53911,32 +53911,32 @@
     </row>
     <row r="1682" customHeight="1" ht="20">
       <c r="A1682" s="1" t="n">
-        <v>1634902</v>
+        <v>1625869</v>
       </c>
       <c r="B1682" s="1" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C1682" s="1" t="n">
-        <v>46993</v>
+        <v>46744</v>
       </c>
       <c r="D1682" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CP1600P-BR</t>
+            <t xml:space="preserve">BU5032P</t>
           </r>
         </is>
       </c>
       <c r="E1682" s="1" t="n">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="F1682" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/10/2026</t>
+            <t xml:space="preserve">26/01/2027</t>
           </r>
         </is>
       </c>
@@ -53949,19 +53949,19 @@
         <v>43</v>
       </c>
       <c r="C1683" s="1" t="n">
-        <v>46777</v>
+        <v>46745</v>
       </c>
       <c r="D1683" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VR250G</t>
+            <t xml:space="preserve">BU5040P</t>
           </r>
         </is>
       </c>
       <c r="E1683" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F1683" s="1" t="inlineStr">
         <is>
@@ -53981,19 +53981,19 @@
         <v>43</v>
       </c>
       <c r="C1684" s="1" t="n">
-        <v>46773</v>
+        <v>46759</v>
       </c>
       <c r="D1684" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">JMF20120G</t>
+            <t xml:space="preserve">MI252525G</t>
           </r>
         </is>
       </c>
       <c r="E1684" s="1" t="n">
-        <v>180</v>
+        <v>1560</v>
       </c>
       <c r="F1684" s="1" t="inlineStr">
         <is>
@@ -54007,32 +54007,32 @@
     </row>
     <row r="1685" customHeight="1" ht="20">
       <c r="A1685" s="1" t="n">
-        <v>1625869</v>
+        <v>1634902</v>
       </c>
       <c r="B1685" s="1" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C1685" s="1" t="n">
-        <v>46775</v>
+        <v>46993</v>
       </c>
       <c r="D1685" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">RES750G</t>
+            <t xml:space="preserve">CP1600P-BR</t>
           </r>
         </is>
       </c>
       <c r="E1685" s="1" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F1685" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">27/10/2026</t>
           </r>
         </is>
       </c>
@@ -54045,19 +54045,19 @@
         <v>43</v>
       </c>
       <c r="C1686" s="1" t="n">
-        <v>46760</v>
+        <v>46777</v>
       </c>
       <c r="D1686" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CL320G</t>
+            <t xml:space="preserve">VR250G</t>
           </r>
         </is>
       </c>
       <c r="E1686" s="1" t="n">
-        <v>512</v>
+        <v>100</v>
       </c>
       <c r="F1686" s="1" t="inlineStr">
         <is>
@@ -54077,19 +54077,19 @@
         <v>43</v>
       </c>
       <c r="C1687" s="1" t="n">
-        <v>46762</v>
+        <v>46773</v>
       </c>
       <c r="D1687" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CL500G</t>
+            <t xml:space="preserve">JMF20120G</t>
           </r>
         </is>
       </c>
       <c r="E1687" s="1" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="F1687" s="1" t="inlineStr">
         <is>
@@ -54103,96 +54103,96 @@
     </row>
     <row r="1688" customHeight="1" ht="20">
       <c r="A1688" s="1" t="n">
-        <v>1635908</v>
+        <v>1625869</v>
       </c>
       <c r="B1688" s="1" t="n">
-        <v>29601</v>
+        <v>43</v>
       </c>
       <c r="C1688" s="1" t="n">
-        <v>46998</v>
+        <v>46775</v>
       </c>
       <c r="D1688" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CHAPA-NYLON-X90-841-BR</t>
+            <t xml:space="preserve">RES750G</t>
           </r>
         </is>
       </c>
       <c r="E1688" s="1" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F1688" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/11/2026</t>
+            <t xml:space="preserve">26/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1689" customHeight="1" ht="20">
       <c r="A1689" s="1" t="n">
-        <v>1563222</v>
+        <v>1625869</v>
       </c>
       <c r="B1689" s="1" t="n">
-        <v>25042</v>
+        <v>43</v>
       </c>
       <c r="C1689" s="1" t="n">
-        <v>46629</v>
+        <v>46760</v>
       </c>
       <c r="D1689" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">P-L200B</t>
+            <t xml:space="preserve">CL320G</t>
           </r>
         </is>
       </c>
       <c r="E1689" s="1" t="n">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="F1689" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">09/11/2026</t>
+            <t xml:space="preserve">26/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1690" customHeight="1" ht="20">
       <c r="A1690" s="1" t="n">
-        <v>1635908</v>
+        <v>1625869</v>
       </c>
       <c r="B1690" s="1" t="n">
-        <v>29601</v>
+        <v>43</v>
       </c>
       <c r="C1690" s="1" t="n">
-        <v>46996</v>
+        <v>46762</v>
       </c>
       <c r="D1690" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CHAPA-MOVEL-X90-841-BR</t>
+            <t xml:space="preserve">CL500G</t>
           </r>
         </is>
       </c>
       <c r="E1690" s="1" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="F1690" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/11/2026</t>
+            <t xml:space="preserve">26/01/2027</t>
           </r>
         </is>
       </c>
@@ -54205,14 +54205,14 @@
         <v>29601</v>
       </c>
       <c r="C1691" s="1" t="n">
-        <v>46997</v>
+        <v>46998</v>
       </c>
       <c r="D1691" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CHAPA-FIXA-X90-841-BR</t>
+            <t xml:space="preserve">CHAPA-NYLON-X90-841-BR</t>
           </r>
         </is>
       </c>
@@ -54231,96 +54231,96 @@
     </row>
     <row r="1692" customHeight="1" ht="20">
       <c r="A1692" s="1" t="n">
-        <v>1625869</v>
+        <v>1563222</v>
       </c>
       <c r="B1692" s="1" t="n">
-        <v>43</v>
+        <v>25042</v>
       </c>
       <c r="C1692" s="1" t="n">
-        <v>46740</v>
+        <v>46629</v>
       </c>
       <c r="D1692" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CP110P</t>
+            <t xml:space="preserve">P-L200B</t>
           </r>
         </is>
       </c>
       <c r="E1692" s="1" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="F1692" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">09/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1693" customHeight="1" ht="20">
       <c r="A1693" s="1" t="n">
-        <v>1633775</v>
+        <v>1635908</v>
       </c>
       <c r="B1693" s="1" t="n">
-        <v>29593</v>
+        <v>29601</v>
       </c>
       <c r="C1693" s="1" t="n">
-        <v>46956</v>
+        <v>46996</v>
       </c>
       <c r="D1693" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BRP-75-3C-6M</t>
+            <t xml:space="preserve">CHAPA-MOVEL-X90-841-BR</t>
           </r>
         </is>
       </c>
       <c r="E1693" s="1" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="F1693" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/02/2027</t>
+            <t xml:space="preserve">04/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1694" customHeight="1" ht="20">
       <c r="A1694" s="1" t="n">
-        <v>1625869</v>
+        <v>1635908</v>
       </c>
       <c r="B1694" s="1" t="n">
-        <v>43</v>
+        <v>29601</v>
       </c>
       <c r="C1694" s="1" t="n">
-        <v>46749</v>
+        <v>46997</v>
       </c>
       <c r="D1694" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CL500P</t>
+            <t xml:space="preserve">CHAPA-FIXA-X90-841-BR</t>
           </r>
         </is>
       </c>
       <c r="E1694" s="1" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="F1694" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">04/11/2026</t>
           </r>
         </is>
       </c>
@@ -54333,19 +54333,19 @@
         <v>43</v>
       </c>
       <c r="C1695" s="1" t="n">
-        <v>46772</v>
+        <v>46740</v>
       </c>
       <c r="D1695" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">JK160000</t>
+            <t xml:space="preserve">CP110P</t>
           </r>
         </is>
       </c>
       <c r="E1695" s="1" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F1695" s="1" t="inlineStr">
         <is>
@@ -54359,64 +54359,64 @@
     </row>
     <row r="1696" customHeight="1" ht="20">
       <c r="A1696" s="1" t="n">
-        <v>1624906</v>
+        <v>1633775</v>
       </c>
       <c r="B1696" s="1" t="n">
-        <v>29565</v>
+        <v>29593</v>
       </c>
       <c r="C1696" s="1" t="n">
-        <v>46560</v>
+        <v>46956</v>
       </c>
       <c r="D1696" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SDA32X25BG</t>
+            <t xml:space="preserve">BRP-75-3C-6M</t>
           </r>
         </is>
       </c>
       <c r="E1696" s="1" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="F1696" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/11/2026</t>
+            <t xml:space="preserve">04/02/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1697" customHeight="1" ht="20">
       <c r="A1697" s="1" t="n">
-        <v>1563222</v>
+        <v>1634795</v>
       </c>
       <c r="B1697" s="1" t="n">
-        <v>25042</v>
+        <v>29605</v>
       </c>
       <c r="C1697" s="1" t="n">
-        <v>46619</v>
+        <v>47002</v>
       </c>
       <c r="D1697" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">P-4H230C</t>
+            <t xml:space="preserve">FH06M-00-BR</t>
           </r>
         </is>
       </c>
       <c r="E1697" s="1" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="F1697" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">09/11/2026</t>
+            <t xml:space="preserve">16/10/2026</t>
           </r>
         </is>
       </c>
@@ -54429,19 +54429,19 @@
         <v>43</v>
       </c>
       <c r="C1698" s="1" t="n">
-        <v>46779</v>
+        <v>46749</v>
       </c>
       <c r="D1698" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">FY200G</t>
+            <t xml:space="preserve">CL500P</t>
           </r>
         </is>
       </c>
       <c r="E1698" s="1" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="F1698" s="1" t="inlineStr">
         <is>
@@ -54461,14 +54461,14 @@
         <v>43</v>
       </c>
       <c r="C1699" s="1" t="n">
-        <v>46780</v>
+        <v>46772</v>
       </c>
       <c r="D1699" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">FY250G</t>
+            <t xml:space="preserve">JK160000</t>
           </r>
         </is>
       </c>
@@ -54487,96 +54487,96 @@
     </row>
     <row r="1700" customHeight="1" ht="20">
       <c r="A1700" s="1" t="n">
-        <v>1625869</v>
+        <v>1624906</v>
       </c>
       <c r="B1700" s="1" t="n">
-        <v>43</v>
+        <v>29565</v>
       </c>
       <c r="C1700" s="1" t="n">
-        <v>46534</v>
+        <v>46560</v>
       </c>
       <c r="D1700" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">JK750000</t>
+            <t xml:space="preserve">SDA32X25BG</t>
           </r>
         </is>
       </c>
       <c r="E1700" s="1" t="n">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="F1700" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">08/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1701" customHeight="1" ht="20">
       <c r="A1701" s="1" t="n">
-        <v>1633775</v>
+        <v>1563222</v>
       </c>
       <c r="B1701" s="1" t="n">
-        <v>29593</v>
+        <v>25042</v>
       </c>
       <c r="C1701" s="1" t="n">
-        <v>46959</v>
+        <v>46619</v>
       </c>
       <c r="D1701" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BRP-160-3C-6M</t>
+            <t xml:space="preserve">P-4H230C</t>
           </r>
         </is>
       </c>
       <c r="E1701" s="1" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="F1701" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/02/2027</t>
+            <t xml:space="preserve">09/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1702" customHeight="1" ht="20">
       <c r="A1702" s="1" t="n">
-        <v>1633775</v>
+        <v>1625869</v>
       </c>
       <c r="B1702" s="1" t="n">
-        <v>29593</v>
+        <v>43</v>
       </c>
       <c r="C1702" s="1" t="n">
-        <v>46963</v>
+        <v>46779</v>
       </c>
       <c r="D1702" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VE900G</t>
+            <t xml:space="preserve">FY200G</t>
           </r>
         </is>
       </c>
       <c r="E1702" s="1" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="F1702" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/02/2027</t>
+            <t xml:space="preserve">26/01/2027</t>
           </r>
         </is>
       </c>
@@ -54589,19 +54589,19 @@
         <v>43</v>
       </c>
       <c r="C1703" s="1" t="n">
-        <v>46741</v>
+        <v>46780</v>
       </c>
       <c r="D1703" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BU2520P</t>
+            <t xml:space="preserve">FY250G</t>
           </r>
         </is>
       </c>
       <c r="E1703" s="1" t="n">
-        <v>1400</v>
+        <v>100</v>
       </c>
       <c r="F1703" s="1" t="inlineStr">
         <is>
@@ -54615,160 +54615,160 @@
     </row>
     <row r="1704" customHeight="1" ht="20">
       <c r="A1704" s="1" t="n">
-        <v>1633775</v>
+        <v>1625869</v>
       </c>
       <c r="B1704" s="1" t="n">
-        <v>29593</v>
+        <v>43</v>
       </c>
       <c r="C1704" s="1" t="n">
-        <v>46957</v>
+        <v>46534</v>
       </c>
       <c r="D1704" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BRP-90-3C-6M</t>
+            <t xml:space="preserve">JK750000</t>
           </r>
         </is>
       </c>
       <c r="E1704" s="1" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="F1704" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/02/2027</t>
+            <t xml:space="preserve">26/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1705" customHeight="1" ht="20">
       <c r="A1705" s="1" t="n">
-        <v>1625869</v>
+        <v>1633775</v>
       </c>
       <c r="B1705" s="1" t="n">
-        <v>43</v>
+        <v>29593</v>
       </c>
       <c r="C1705" s="1" t="n">
-        <v>46758</v>
+        <v>46959</v>
       </c>
       <c r="D1705" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">MI202020G</t>
+            <t xml:space="preserve">BRP-160-3C-6M</t>
           </r>
         </is>
       </c>
       <c r="E1705" s="1" t="n">
-        <v>2560</v>
+        <v>200</v>
       </c>
       <c r="F1705" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">04/02/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1706" customHeight="1" ht="20">
       <c r="A1706" s="1" t="n">
-        <v>1625869</v>
+        <v>1633775</v>
       </c>
       <c r="B1706" s="1" t="n">
-        <v>43</v>
+        <v>29593</v>
       </c>
       <c r="C1706" s="1" t="n">
-        <v>46748</v>
+        <v>46963</v>
       </c>
       <c r="D1706" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CL400P</t>
+            <t xml:space="preserve">VE900G</t>
           </r>
         </is>
       </c>
       <c r="E1706" s="1" t="n">
-        <v>240</v>
+        <v>50</v>
       </c>
       <c r="F1706" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">04/02/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1707" customHeight="1" ht="20">
       <c r="A1707" s="1" t="n">
-        <v>1633775</v>
+        <v>1625869</v>
       </c>
       <c r="B1707" s="1" t="n">
-        <v>29593</v>
+        <v>43</v>
       </c>
       <c r="C1707" s="1" t="n">
-        <v>46817</v>
+        <v>46741</v>
       </c>
       <c r="D1707" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BRG-160-3C-6M</t>
+            <t xml:space="preserve">BU2520P</t>
           </r>
         </is>
       </c>
       <c r="E1707" s="1" t="n">
-        <v>100</v>
+        <v>1400</v>
       </c>
       <c r="F1707" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/02/2027</t>
+            <t xml:space="preserve">26/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1708" customHeight="1" ht="20">
       <c r="A1708" s="1" t="n">
-        <v>1625869</v>
+        <v>1633775</v>
       </c>
       <c r="B1708" s="1" t="n">
-        <v>43</v>
+        <v>29593</v>
       </c>
       <c r="C1708" s="1" t="n">
-        <v>46754</v>
+        <v>46957</v>
       </c>
       <c r="D1708" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BU3220G</t>
+            <t xml:space="preserve">BRP-90-3C-6M</t>
           </r>
         </is>
       </c>
       <c r="E1708" s="1" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="F1708" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">04/02/2027</t>
           </r>
         </is>
       </c>
@@ -54781,19 +54781,19 @@
         <v>43</v>
       </c>
       <c r="C1709" s="1" t="n">
-        <v>46755</v>
+        <v>46758</v>
       </c>
       <c r="D1709" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BU3225G</t>
+            <t xml:space="preserve">MI202020G</t>
           </r>
         </is>
       </c>
       <c r="E1709" s="1" t="n">
-        <v>800</v>
+        <v>2560</v>
       </c>
       <c r="F1709" s="1" t="inlineStr">
         <is>
@@ -54813,19 +54813,19 @@
         <v>43</v>
       </c>
       <c r="C1710" s="1" t="n">
-        <v>46781</v>
+        <v>46748</v>
       </c>
       <c r="D1710" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">FY320G</t>
+            <t xml:space="preserve">CL400P</t>
           </r>
         </is>
       </c>
       <c r="E1710" s="1" t="n">
-        <v>70</v>
+        <v>240</v>
       </c>
       <c r="F1710" s="1" t="inlineStr">
         <is>
@@ -54839,64 +54839,64 @@
     </row>
     <row r="1711" customHeight="1" ht="20">
       <c r="A1711" s="1" t="n">
-        <v>1624885</v>
+        <v>1633775</v>
       </c>
       <c r="B1711" s="1" t="n">
-        <v>29564</v>
+        <v>29593</v>
       </c>
       <c r="C1711" s="1" t="n">
-        <v>46557</v>
+        <v>46817</v>
       </c>
       <c r="D1711" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">180-4E1-83-PSL</t>
+            <t xml:space="preserve">BRG-160-3C-6M</t>
           </r>
         </is>
       </c>
       <c r="E1711" s="1" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="F1711" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/11/2026</t>
+            <t xml:space="preserve">04/02/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1712" customHeight="1" ht="20">
       <c r="A1712" s="1" t="n">
-        <v>1563222</v>
+        <v>1625869</v>
       </c>
       <c r="B1712" s="1" t="n">
-        <v>25042</v>
+        <v>43</v>
       </c>
       <c r="C1712" s="1" t="n">
-        <v>46628</v>
+        <v>46754</v>
       </c>
       <c r="D1712" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">DUST-BLOWING</t>
+            <t xml:space="preserve">BU3220G</t>
           </r>
         </is>
       </c>
       <c r="E1712" s="1" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="F1712" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">09/11/2026</t>
+            <t xml:space="preserve">26/01/2027</t>
           </r>
         </is>
       </c>
@@ -54909,19 +54909,19 @@
         <v>43</v>
       </c>
       <c r="C1713" s="1" t="n">
-        <v>46737</v>
+        <v>46755</v>
       </c>
       <c r="D1713" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BRP-90-6M</t>
+            <t xml:space="preserve">BU3225G</t>
           </r>
         </is>
       </c>
       <c r="E1713" s="1" t="n">
-        <v>501</v>
+        <v>800</v>
       </c>
       <c r="F1713" s="1" t="inlineStr">
         <is>
@@ -54941,19 +54941,19 @@
         <v>43</v>
       </c>
       <c r="C1714" s="1" t="n">
-        <v>46742</v>
+        <v>46781</v>
       </c>
       <c r="D1714" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BU3220P</t>
+            <t xml:space="preserve">FY320G</t>
           </r>
         </is>
       </c>
       <c r="E1714" s="1" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="F1714" s="1" t="inlineStr">
         <is>
@@ -54967,64 +54967,64 @@
     </row>
     <row r="1715" customHeight="1" ht="20">
       <c r="A1715" s="1" t="n">
-        <v>1625869</v>
+        <v>1624885</v>
       </c>
       <c r="B1715" s="1" t="n">
-        <v>43</v>
+        <v>29564</v>
       </c>
       <c r="C1715" s="1" t="n">
-        <v>46764</v>
+        <v>46557</v>
       </c>
       <c r="D1715" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SP200</t>
+            <t xml:space="preserve">180-4E1-83-PSL</t>
           </r>
         </is>
       </c>
       <c r="E1715" s="1" t="n">
-        <v>22000</v>
+        <v>2</v>
       </c>
       <c r="F1715" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">08/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1716" customHeight="1" ht="20">
       <c r="A1716" s="1" t="n">
-        <v>1625869</v>
+        <v>1563222</v>
       </c>
       <c r="B1716" s="1" t="n">
-        <v>43</v>
+        <v>25042</v>
       </c>
       <c r="C1716" s="1" t="n">
-        <v>46766</v>
+        <v>46628</v>
       </c>
       <c r="D1716" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SP320</t>
+            <t xml:space="preserve">DUST-BLOWING</t>
           </r>
         </is>
       </c>
       <c r="E1716" s="1" t="n">
-        <v>10000</v>
+        <v>50</v>
       </c>
       <c r="F1716" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">09/11/2026</t>
           </r>
         </is>
       </c>
@@ -55037,19 +55037,19 @@
         <v>43</v>
       </c>
       <c r="C1717" s="1" t="n">
-        <v>46738</v>
+        <v>46737</v>
       </c>
       <c r="D1717" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">JO110P</t>
+            <t xml:space="preserve">BRP-90-6M</t>
           </r>
         </is>
       </c>
       <c r="E1717" s="1" t="n">
-        <v>32</v>
+        <v>501</v>
       </c>
       <c r="F1717" s="1" t="inlineStr">
         <is>
@@ -55063,256 +55063,256 @@
     </row>
     <row r="1718" customHeight="1" ht="20">
       <c r="A1718" s="1" t="n">
-        <v>1628645</v>
+        <v>1625869</v>
       </c>
       <c r="B1718" s="1" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C1718" s="1" t="n">
-        <v>46796</v>
+        <v>46742</v>
       </c>
       <c r="D1718" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">AD90030P-BR</t>
+            <t xml:space="preserve">BU3220P</t>
           </r>
         </is>
       </c>
       <c r="E1718" s="1" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="F1718" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">16/10/2026</t>
+            <t xml:space="preserve">26/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1719" customHeight="1" ht="20">
       <c r="A1719" s="1" t="n">
-        <v>1633775</v>
+        <v>1625869</v>
       </c>
       <c r="B1719" s="1" t="n">
-        <v>29593</v>
+        <v>43</v>
       </c>
       <c r="C1719" s="1" t="n">
-        <v>46954</v>
+        <v>46764</v>
       </c>
       <c r="D1719" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BRG-90-3C-6M</t>
+            <t xml:space="preserve">SP200</t>
           </r>
         </is>
       </c>
       <c r="E1719" s="1" t="n">
-        <v>200</v>
+        <v>22000</v>
       </c>
       <c r="F1719" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/02/2027</t>
+            <t xml:space="preserve">26/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1720" customHeight="1" ht="20">
       <c r="A1720" s="1" t="n">
-        <v>1633775</v>
+        <v>1625869</v>
       </c>
       <c r="B1720" s="1" t="n">
-        <v>29593</v>
+        <v>43</v>
       </c>
       <c r="C1720" s="1" t="n">
-        <v>46958</v>
+        <v>46766</v>
       </c>
       <c r="D1720" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BRP-110-3C-6M</t>
+            <t xml:space="preserve">SP320</t>
           </r>
         </is>
       </c>
       <c r="E1720" s="1" t="n">
-        <v>200</v>
+        <v>10000</v>
       </c>
       <c r="F1720" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/02/2027</t>
+            <t xml:space="preserve">26/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1721" customHeight="1" ht="20">
       <c r="A1721" s="1" t="n">
-        <v>1633775</v>
+        <v>1625869</v>
       </c>
       <c r="B1721" s="1" t="n">
-        <v>29593</v>
+        <v>43</v>
       </c>
       <c r="C1721" s="1" t="n">
-        <v>46962</v>
+        <v>46738</v>
       </c>
       <c r="D1721" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">VE750G</t>
+            <t xml:space="preserve">JO110P</t>
           </r>
         </is>
       </c>
       <c r="E1721" s="1" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F1721" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/02/2027</t>
+            <t xml:space="preserve">26/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1722" customHeight="1" ht="20">
       <c r="A1722" s="1" t="n">
-        <v>1625869</v>
+        <v>1628645</v>
       </c>
       <c r="B1722" s="1" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C1722" s="1" t="n">
-        <v>46751</v>
+        <v>46796</v>
       </c>
       <c r="D1722" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">AD40112P</t>
+            <t xml:space="preserve">AD90030P-BR</t>
           </r>
         </is>
       </c>
       <c r="E1722" s="1" t="n">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F1722" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">16/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1723" customHeight="1" ht="20">
       <c r="A1723" s="1" t="n">
-        <v>1625869</v>
+        <v>1633775</v>
       </c>
       <c r="B1723" s="1" t="n">
-        <v>43</v>
+        <v>29593</v>
       </c>
       <c r="C1723" s="1" t="n">
-        <v>46767</v>
+        <v>46954</v>
       </c>
       <c r="D1723" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SP400</t>
+            <t xml:space="preserve">BRG-90-3C-6M</t>
           </r>
         </is>
       </c>
       <c r="E1723" s="1" t="n">
-        <v>5000</v>
+        <v>200</v>
       </c>
       <c r="F1723" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">04/02/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1724" customHeight="1" ht="20">
       <c r="A1724" s="1" t="n">
-        <v>1625869</v>
+        <v>1633775</v>
       </c>
       <c r="B1724" s="1" t="n">
-        <v>43</v>
+        <v>29593</v>
       </c>
       <c r="C1724" s="1" t="n">
-        <v>46739</v>
+        <v>46958</v>
       </c>
       <c r="D1724" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LU110P</t>
+            <t xml:space="preserve">BRP-110-3C-6M</t>
           </r>
         </is>
       </c>
       <c r="E1724" s="1" t="n">
-        <v>512</v>
+        <v>200</v>
       </c>
       <c r="F1724" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">04/02/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1725" customHeight="1" ht="20">
       <c r="A1725" s="1" t="n">
-        <v>1625869</v>
+        <v>1633775</v>
       </c>
       <c r="B1725" s="1" t="n">
-        <v>43</v>
+        <v>29593</v>
       </c>
       <c r="C1725" s="1" t="n">
-        <v>46763</v>
+        <v>46962</v>
       </c>
       <c r="D1725" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CL630G</t>
+            <t xml:space="preserve">VE750G</t>
           </r>
         </is>
       </c>
       <c r="E1725" s="1" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="F1725" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">04/02/2027</t>
           </r>
         </is>
       </c>
@@ -55325,19 +55325,19 @@
         <v>43</v>
       </c>
       <c r="C1726" s="1" t="n">
-        <v>46769</v>
+        <v>46751</v>
       </c>
       <c r="D1726" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">JK500000</t>
+            <t xml:space="preserve">AD40112P</t>
           </r>
         </is>
       </c>
       <c r="E1726" s="1" t="n">
-        <v>500</v>
+        <v>104</v>
       </c>
       <c r="F1726" s="1" t="inlineStr">
         <is>
@@ -55351,32 +55351,32 @@
     </row>
     <row r="1727" customHeight="1" ht="20">
       <c r="A1727" s="1" t="n">
-        <v>1633775</v>
+        <v>1625869</v>
       </c>
       <c r="B1727" s="1" t="n">
-        <v>29593</v>
+        <v>43</v>
       </c>
       <c r="C1727" s="1" t="n">
-        <v>46955</v>
+        <v>46767</v>
       </c>
       <c r="D1727" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BRG-110-3C-6M</t>
+            <t xml:space="preserve">SP400</t>
           </r>
         </is>
       </c>
       <c r="E1727" s="1" t="n">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="F1727" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/02/2027</t>
+            <t xml:space="preserve">26/01/2027</t>
           </r>
         </is>
       </c>
@@ -55389,19 +55389,19 @@
         <v>43</v>
       </c>
       <c r="C1728" s="1" t="n">
-        <v>46770</v>
+        <v>46739</v>
       </c>
       <c r="D1728" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">JK900000</t>
+            <t xml:space="preserve">LU110P</t>
           </r>
         </is>
       </c>
       <c r="E1728" s="1" t="n">
-        <v>300</v>
+        <v>512</v>
       </c>
       <c r="F1728" s="1" t="inlineStr">
         <is>
@@ -55421,19 +55421,19 @@
         <v>43</v>
       </c>
       <c r="C1729" s="1" t="n">
-        <v>46774</v>
+        <v>46763</v>
       </c>
       <c r="D1729" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">JMF25340G</t>
+            <t xml:space="preserve">CL630G</t>
           </r>
         </is>
       </c>
       <c r="E1729" s="1" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="F1729" s="1" t="inlineStr">
         <is>
@@ -55447,32 +55447,32 @@
     </row>
     <row r="1730" customHeight="1" ht="20">
       <c r="A1730" s="1" t="n">
-        <v>1633775</v>
+        <v>1625869</v>
       </c>
       <c r="B1730" s="1" t="n">
-        <v>29593</v>
+        <v>43</v>
       </c>
       <c r="C1730" s="1" t="n">
-        <v>46960</v>
+        <v>46769</v>
       </c>
       <c r="D1730" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CP160P</t>
+            <t xml:space="preserve">JK500000</t>
           </r>
         </is>
       </c>
       <c r="E1730" s="1" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="F1730" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/02/2027</t>
+            <t xml:space="preserve">26/01/2027</t>
           </r>
         </is>
       </c>
@@ -55485,19 +55485,19 @@
         <v>29593</v>
       </c>
       <c r="C1731" s="1" t="n">
-        <v>46961</v>
+        <v>46955</v>
       </c>
       <c r="D1731" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">LU160P</t>
+            <t xml:space="preserve">BRG-110-3C-6M</t>
           </r>
         </is>
       </c>
       <c r="E1731" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F1731" s="1" t="inlineStr">
         <is>
@@ -55517,19 +55517,19 @@
         <v>43</v>
       </c>
       <c r="C1732" s="1" t="n">
-        <v>46782</v>
+        <v>46770</v>
       </c>
       <c r="D1732" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">FY400G</t>
+            <t xml:space="preserve">JK900000</t>
           </r>
         </is>
       </c>
       <c r="E1732" s="1" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="F1732" s="1" t="inlineStr">
         <is>
@@ -55543,96 +55543,96 @@
     </row>
     <row r="1733" customHeight="1" ht="20">
       <c r="A1733" s="1" t="n">
-        <v>1624906</v>
+        <v>1625869</v>
       </c>
       <c r="B1733" s="1" t="n">
-        <v>29565</v>
+        <v>43</v>
       </c>
       <c r="C1733" s="1" t="n">
-        <v>46584</v>
+        <v>46774</v>
       </c>
       <c r="D1733" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">ACQD40X80SBG</t>
+            <t xml:space="preserve">JMF25340G</t>
           </r>
         </is>
       </c>
       <c r="E1733" s="1" t="n">
-        <v>2</v>
+        <v>240</v>
       </c>
       <c r="F1733" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/11/2026</t>
+            <t xml:space="preserve">26/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1734" customHeight="1" ht="20">
       <c r="A1734" s="1" t="n">
-        <v>1624906</v>
+        <v>1633775</v>
       </c>
       <c r="B1734" s="1" t="n">
-        <v>29565</v>
+        <v>29593</v>
       </c>
       <c r="C1734" s="1" t="n">
-        <v>46684</v>
+        <v>46960</v>
       </c>
       <c r="D1734" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">F-SC80CB</t>
+            <t xml:space="preserve">CP160P</t>
           </r>
         </is>
       </c>
       <c r="E1734" s="1" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F1734" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/11/2026</t>
+            <t xml:space="preserve">04/02/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1735" customHeight="1" ht="20">
       <c r="A1735" s="1" t="n">
-        <v>1625869</v>
+        <v>1633775</v>
       </c>
       <c r="B1735" s="1" t="n">
-        <v>43</v>
+        <v>29593</v>
       </c>
       <c r="C1735" s="1" t="n">
-        <v>46747</v>
+        <v>46961</v>
       </c>
       <c r="D1735" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">CL320P</t>
+            <t xml:space="preserve">LU160P</t>
           </r>
         </is>
       </c>
       <c r="E1735" s="1" t="n">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="F1735" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">04/02/2027</t>
           </r>
         </is>
       </c>
@@ -55645,19 +55645,19 @@
         <v>43</v>
       </c>
       <c r="C1736" s="1" t="n">
-        <v>46756</v>
+        <v>46782</v>
       </c>
       <c r="D1736" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BU5032G</t>
+            <t xml:space="preserve">FY400G</t>
           </r>
         </is>
       </c>
       <c r="E1736" s="1" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="F1736" s="1" t="inlineStr">
         <is>
@@ -55671,128 +55671,128 @@
     </row>
     <row r="1737" customHeight="1" ht="20">
       <c r="A1737" s="1" t="n">
-        <v>1625869</v>
+        <v>1635888</v>
       </c>
       <c r="B1737" s="1" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C1737" s="1" t="n">
-        <v>46757</v>
+        <v>47028</v>
       </c>
       <c r="D1737" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">BU5040G</t>
+            <t xml:space="preserve">WMD-63-BR</t>
           </r>
         </is>
       </c>
       <c r="E1737" s="1" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="F1737" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">30/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1738" customHeight="1" ht="20">
       <c r="A1738" s="1" t="n">
-        <v>1625869</v>
+        <v>1635888</v>
       </c>
       <c r="B1738" s="1" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C1738" s="1" t="n">
-        <v>46765</v>
+        <v>47029</v>
       </c>
       <c r="D1738" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">SP250</t>
+            <t xml:space="preserve">WMD-75-BR</t>
           </r>
         </is>
       </c>
       <c r="E1738" s="1" t="n">
-        <v>20000</v>
+        <v>1</v>
       </c>
       <c r="F1738" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">30/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1739" customHeight="1" ht="20">
       <c r="A1739" s="1" t="n">
-        <v>1625869</v>
+        <v>1624906</v>
       </c>
       <c r="B1739" s="1" t="n">
-        <v>43</v>
+        <v>29565</v>
       </c>
       <c r="C1739" s="1" t="n">
-        <v>46746</v>
+        <v>46584</v>
       </c>
       <c r="D1739" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">TR9025P</t>
+            <t xml:space="preserve">ACQD40X80SBG</t>
           </r>
         </is>
       </c>
       <c r="E1739" s="1" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="F1739" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">08/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1740" customHeight="1" ht="20">
       <c r="A1740" s="1" t="n">
-        <v>1625869</v>
+        <v>1624906</v>
       </c>
       <c r="B1740" s="1" t="n">
-        <v>43</v>
+        <v>29565</v>
       </c>
       <c r="C1740" s="1" t="n">
-        <v>46771</v>
+        <v>46684</v>
       </c>
       <c r="D1740" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">JK110000</t>
+            <t xml:space="preserve">F-SC80CB</t>
           </r>
         </is>
       </c>
       <c r="E1740" s="1" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="F1740" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">08/11/2026</t>
           </r>
         </is>
       </c>
@@ -55805,9 +55805,201 @@
         <v>43</v>
       </c>
       <c r="C1741" s="1" t="n">
+        <v>46747</v>
+      </c>
+      <c r="D1741" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">CL320P</t>
+          </r>
+        </is>
+      </c>
+      <c r="E1741" s="1" t="n">
+        <v>512</v>
+      </c>
+      <c r="F1741" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">26/01/2027</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="1742" customHeight="1" ht="20">
+      <c r="A1742" s="1" t="n">
+        <v>1625869</v>
+      </c>
+      <c r="B1742" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="C1742" s="1" t="n">
+        <v>46756</v>
+      </c>
+      <c r="D1742" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">BU5032G</t>
+          </r>
+        </is>
+      </c>
+      <c r="E1742" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="F1742" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">26/01/2027</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="1743" customHeight="1" ht="20">
+      <c r="A1743" s="1" t="n">
+        <v>1625869</v>
+      </c>
+      <c r="B1743" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="C1743" s="1" t="n">
+        <v>46757</v>
+      </c>
+      <c r="D1743" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">BU5040G</t>
+          </r>
+        </is>
+      </c>
+      <c r="E1743" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1743" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">26/01/2027</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="1744" customHeight="1" ht="20">
+      <c r="A1744" s="1" t="n">
+        <v>1625869</v>
+      </c>
+      <c r="B1744" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="C1744" s="1" t="n">
+        <v>46765</v>
+      </c>
+      <c r="D1744" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">SP250</t>
+          </r>
+        </is>
+      </c>
+      <c r="E1744" s="1" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F1744" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">26/01/2027</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="1745" customHeight="1" ht="20">
+      <c r="A1745" s="1" t="n">
+        <v>1625869</v>
+      </c>
+      <c r="B1745" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="C1745" s="1" t="n">
+        <v>46746</v>
+      </c>
+      <c r="D1745" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">TR9025P</t>
+          </r>
+        </is>
+      </c>
+      <c r="E1745" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="F1745" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">26/01/2027</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="1746" customHeight="1" ht="20">
+      <c r="A1746" s="1" t="n">
+        <v>1625869</v>
+      </c>
+      <c r="B1746" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="C1746" s="1" t="n">
+        <v>46771</v>
+      </c>
+      <c r="D1746" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">JK110000</t>
+          </r>
+        </is>
+      </c>
+      <c r="E1746" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="F1746" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+       </rPr>
+            <t xml:space="preserve">26/01/2027</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="1747" customHeight="1" ht="20">
+      <c r="A1747" s="1" t="n">
+        <v>1625869</v>
+      </c>
+      <c r="B1747" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="C1747" s="1" t="n">
         <v>46736</v>
       </c>
-      <c r="D1741" s="1" t="inlineStr">
+      <c r="D1747" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -55816,10 +56008,10 @@
           </r>
         </is>
       </c>
-      <c r="E1741" s="1" t="n">
+      <c r="E1747" s="1" t="n">
         <v>201</v>
       </c>
-      <c r="F1741" s="1" t="inlineStr">
+      <c r="F1747" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>

--- a/data/COMPRAS_PENDENTES.xlsx
+++ b/data/COMPRAS_PENDENTES.xlsx
@@ -2461,10 +2461,10 @@
     </row>
     <row r="74" customHeight="1" ht="20">
       <c r="A74" s="1" t="n">
-        <v>1607866</v>
+        <v>1604593</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C74" s="1" t="n">
         <v>9584</v>
@@ -2479,24 +2479,24 @@
         </is>
       </c>
       <c r="E74" s="1" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/11/2026</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="75" customHeight="1" ht="20">
       <c r="A75" s="1" t="n">
-        <v>1604593</v>
+        <v>1607866</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C75" s="1" t="n">
         <v>9584</v>
@@ -2511,14 +2511,14 @@
         </is>
       </c>
       <c r="E75" s="1" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">20/01/2027</t>
+            <t xml:space="preserve">19/11/2026</t>
           </r>
         </is>
       </c>
@@ -15389,10 +15389,10 @@
     </row>
     <row r="478" customHeight="1" ht="20">
       <c r="A478" s="1" t="n">
-        <v>1523488</v>
+        <v>1587245</v>
       </c>
       <c r="B478" s="1" t="n">
-        <v>24896</v>
+        <v>27413</v>
       </c>
       <c r="C478" s="1" t="n">
         <v>14733</v>
@@ -15407,24 +15407,24 @@
         </is>
       </c>
       <c r="E478" s="1" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F478" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="479" customHeight="1" ht="20">
       <c r="A479" s="1" t="n">
-        <v>1587245</v>
+        <v>1523488</v>
       </c>
       <c r="B479" s="1" t="n">
-        <v>27413</v>
+        <v>24896</v>
       </c>
       <c r="C479" s="1" t="n">
         <v>14733</v>
@@ -15439,14 +15439,14 @@
         </is>
       </c>
       <c r="E479" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F479" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>

--- a/data/COMPRAS_PENDENTES.xlsx
+++ b/data/COMPRAS_PENDENTES.xlsx
@@ -2461,10 +2461,10 @@
     </row>
     <row r="74" customHeight="1" ht="20">
       <c r="A74" s="1" t="n">
-        <v>1604593</v>
+        <v>1607866</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C74" s="1" t="n">
         <v>9584</v>
@@ -2479,24 +2479,24 @@
         </is>
       </c>
       <c r="E74" s="1" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">20/01/2027</t>
+            <t xml:space="preserve">19/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="75" customHeight="1" ht="20">
       <c r="A75" s="1" t="n">
-        <v>1607866</v>
+        <v>1604593</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C75" s="1" t="n">
         <v>9584</v>
@@ -2511,14 +2511,14 @@
         </is>
       </c>
       <c r="E75" s="1" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">19/11/2026</t>
+            <t xml:space="preserve">20/01/2027</t>
           </r>
         </is>
       </c>
@@ -7293,10 +7293,10 @@
     </row>
     <row r="225" customHeight="1" ht="20">
       <c r="A225" s="1" t="n">
-        <v>1542689</v>
+        <v>1470722</v>
       </c>
       <c r="B225" s="1" t="n">
-        <v>24951</v>
+        <v>24616</v>
       </c>
       <c r="C225" s="1" t="n">
         <v>10807</v>
@@ -7311,24 +7311,24 @@
         </is>
       </c>
       <c r="E225" s="1" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="F225" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="226" customHeight="1" ht="20">
       <c r="A226" s="1" t="n">
-        <v>1470722</v>
+        <v>1542689</v>
       </c>
       <c r="B226" s="1" t="n">
-        <v>24616</v>
+        <v>24951</v>
       </c>
       <c r="C226" s="1" t="n">
         <v>10807</v>
@@ -7343,14 +7343,14 @@
         </is>
       </c>
       <c r="E226" s="1" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="F226" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">23/11/2026</t>
           </r>
         </is>
       </c>
@@ -8029,10 +8029,10 @@
     </row>
     <row r="248" customHeight="1" ht="20">
       <c r="A248" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B248" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C248" s="1" t="n">
         <v>12593</v>
@@ -8047,24 +8047,24 @@
         </is>
       </c>
       <c r="E248" s="1" t="n">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="F248" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="249" customHeight="1" ht="20">
       <c r="A249" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B249" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C249" s="1" t="n">
         <v>12593</v>
@@ -8079,14 +8079,14 @@
         </is>
       </c>
       <c r="E249" s="1" t="n">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="F249" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
@@ -10877,10 +10877,10 @@
     </row>
     <row r="337" customHeight="1" ht="20">
       <c r="A337" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B337" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C337" s="1" t="n">
         <v>13318</v>
@@ -10895,24 +10895,24 @@
         </is>
       </c>
       <c r="E337" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F337" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="338" customHeight="1" ht="20">
       <c r="A338" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B338" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C338" s="1" t="n">
         <v>13318</v>
@@ -10927,14 +10927,14 @@
         </is>
       </c>
       <c r="E338" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F338" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
@@ -15261,10 +15261,10 @@
     </row>
     <row r="474" customHeight="1" ht="20">
       <c r="A474" s="1" t="n">
-        <v>1587245</v>
+        <v>1523488</v>
       </c>
       <c r="B474" s="1" t="n">
-        <v>27413</v>
+        <v>24896</v>
       </c>
       <c r="C474" s="1" t="n">
         <v>14730</v>
@@ -15279,24 +15279,24 @@
         </is>
       </c>
       <c r="E474" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F474" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="475" customHeight="1" ht="20">
       <c r="A475" s="1" t="n">
-        <v>1523488</v>
+        <v>1587245</v>
       </c>
       <c r="B475" s="1" t="n">
-        <v>24896</v>
+        <v>27413</v>
       </c>
       <c r="C475" s="1" t="n">
         <v>14730</v>
@@ -15311,14 +15311,14 @@
         </is>
       </c>
       <c r="E475" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F475" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
@@ -15389,10 +15389,10 @@
     </row>
     <row r="478" customHeight="1" ht="20">
       <c r="A478" s="1" t="n">
-        <v>1587245</v>
+        <v>1523488</v>
       </c>
       <c r="B478" s="1" t="n">
-        <v>27413</v>
+        <v>24896</v>
       </c>
       <c r="C478" s="1" t="n">
         <v>14733</v>
@@ -15407,14 +15407,14 @@
         </is>
       </c>
       <c r="E478" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F478" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -15453,10 +15453,10 @@
     </row>
     <row r="480" customHeight="1" ht="20">
       <c r="A480" s="1" t="n">
-        <v>1523488</v>
+        <v>1587245</v>
       </c>
       <c r="B480" s="1" t="n">
-        <v>24896</v>
+        <v>27413</v>
       </c>
       <c r="C480" s="1" t="n">
         <v>14733</v>
@@ -15471,14 +15471,14 @@
         </is>
       </c>
       <c r="E480" s="1" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F480" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
@@ -31631,7 +31631,7 @@
         </is>
       </c>
       <c r="E985" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F985" s="1" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         </is>
       </c>
       <c r="E986" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F986" s="1" t="inlineStr">
         <is>
@@ -37213,10 +37213,10 @@
     </row>
     <row r="1160" customHeight="1" ht="20">
       <c r="A1160" s="1" t="n">
-        <v>1587245</v>
+        <v>1523488</v>
       </c>
       <c r="B1160" s="1" t="n">
-        <v>27413</v>
+        <v>24896</v>
       </c>
       <c r="C1160" s="1" t="n">
         <v>31738</v>
@@ -37231,14 +37231,14 @@
         </is>
       </c>
       <c r="E1160" s="1" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F1160" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
@@ -37277,10 +37277,10 @@
     </row>
     <row r="1162" customHeight="1" ht="20">
       <c r="A1162" s="1" t="n">
-        <v>1523488</v>
+        <v>1587245</v>
       </c>
       <c r="B1162" s="1" t="n">
-        <v>24896</v>
+        <v>27413</v>
       </c>
       <c r="C1162" s="1" t="n">
         <v>31738</v>
@@ -37295,14 +37295,14 @@
         </is>
       </c>
       <c r="E1162" s="1" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F1162" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
@@ -37437,10 +37437,10 @@
     </row>
     <row r="1167" customHeight="1" ht="20">
       <c r="A1167" s="1" t="n">
-        <v>1587245</v>
+        <v>1523488</v>
       </c>
       <c r="B1167" s="1" t="n">
-        <v>27413</v>
+        <v>24896</v>
       </c>
       <c r="C1167" s="1" t="n">
         <v>31737</v>
@@ -37455,24 +37455,24 @@
         </is>
       </c>
       <c r="E1167" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F1167" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1168" customHeight="1" ht="20">
       <c r="A1168" s="1" t="n">
-        <v>1523488</v>
+        <v>1587245</v>
       </c>
       <c r="B1168" s="1" t="n">
-        <v>24896</v>
+        <v>27413</v>
       </c>
       <c r="C1168" s="1" t="n">
         <v>31737</v>
@@ -37487,14 +37487,14 @@
         </is>
       </c>
       <c r="E1168" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F1168" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
@@ -39741,10 +39741,10 @@
     </row>
     <row r="1239" customHeight="1" ht="20">
       <c r="A1239" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1239" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1239" s="1" t="n">
         <v>33659</v>
@@ -39759,24 +39759,24 @@
         </is>
       </c>
       <c r="E1239" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F1239" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1240" customHeight="1" ht="20">
       <c r="A1240" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1240" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1240" s="1" t="n">
         <v>33659</v>
@@ -39791,14 +39791,14 @@
         </is>
       </c>
       <c r="E1240" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F1240" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
@@ -43645,10 +43645,10 @@
     </row>
     <row r="1361" customHeight="1" ht="20">
       <c r="A1361" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1361" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1361" s="1" t="n">
         <v>37934</v>
@@ -43663,24 +43663,24 @@
         </is>
       </c>
       <c r="E1361" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F1361" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1362" customHeight="1" ht="20">
       <c r="A1362" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1362" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1362" s="1" t="n">
         <v>37934</v>
@@ -43695,14 +43695,14 @@
         </is>
       </c>
       <c r="E1362" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F1362" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
@@ -43773,10 +43773,10 @@
     </row>
     <row r="1365" customHeight="1" ht="20">
       <c r="A1365" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1365" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1365" s="1" t="n">
         <v>39413</v>
@@ -43791,24 +43791,24 @@
         </is>
       </c>
       <c r="E1365" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1365" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1366" customHeight="1" ht="20">
       <c r="A1366" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1366" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1366" s="1" t="n">
         <v>39413</v>
@@ -43823,14 +43823,14 @@
         </is>
       </c>
       <c r="E1366" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1366" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
@@ -48125,10 +48125,10 @@
     </row>
     <row r="1501" customHeight="1" ht="20">
       <c r="A1501" s="1" t="n">
-        <v>1624906</v>
+        <v>1598892</v>
       </c>
       <c r="B1501" s="1" t="n">
-        <v>29565</v>
+        <v>27486</v>
       </c>
       <c r="C1501" s="1" t="n">
         <v>43440</v>
@@ -48143,24 +48143,24 @@
         </is>
       </c>
       <c r="E1501" s="1" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F1501" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/11/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1502" customHeight="1" ht="20">
       <c r="A1502" s="1" t="n">
-        <v>1598892</v>
+        <v>1624906</v>
       </c>
       <c r="B1502" s="1" t="n">
-        <v>27486</v>
+        <v>29565</v>
       </c>
       <c r="C1502" s="1" t="n">
         <v>43440</v>
@@ -48175,14 +48175,14 @@
         </is>
       </c>
       <c r="E1502" s="1" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F1502" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">08/11/2026</t>
           </r>
         </is>
       </c>
@@ -48445,10 +48445,10 @@
     </row>
     <row r="1511" customHeight="1" ht="20">
       <c r="A1511" s="1" t="n">
-        <v>1624906</v>
+        <v>1598892</v>
       </c>
       <c r="B1511" s="1" t="n">
-        <v>29565</v>
+        <v>27486</v>
       </c>
       <c r="C1511" s="1" t="n">
         <v>43441</v>
@@ -48463,14 +48463,14 @@
         </is>
       </c>
       <c r="E1511" s="1" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F1511" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/11/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
@@ -48495,7 +48495,7 @@
         </is>
       </c>
       <c r="E1512" s="1" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="F1512" s="1" t="inlineStr">
         <is>
@@ -48509,10 +48509,10 @@
     </row>
     <row r="1513" customHeight="1" ht="20">
       <c r="A1513" s="1" t="n">
-        <v>1598892</v>
+        <v>1624906</v>
       </c>
       <c r="B1513" s="1" t="n">
-        <v>27486</v>
+        <v>29565</v>
       </c>
       <c r="C1513" s="1" t="n">
         <v>43441</v>
@@ -48527,14 +48527,14 @@
         </is>
       </c>
       <c r="E1513" s="1" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F1513" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">08/11/2026</t>
           </r>
         </is>
       </c>
@@ -48701,10 +48701,10 @@
     </row>
     <row r="1519" customHeight="1" ht="20">
       <c r="A1519" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1519" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1519" s="1" t="n">
         <v>44178</v>
@@ -48726,17 +48726,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1520" customHeight="1" ht="20">
       <c r="A1520" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1520" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1520" s="1" t="n">
         <v>44178</v>
@@ -48758,7 +48758,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
@@ -49085,10 +49085,10 @@
     </row>
     <row r="1531" customHeight="1" ht="20">
       <c r="A1531" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1531" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1531" s="1" t="n">
         <v>44087</v>
@@ -49103,24 +49103,24 @@
         </is>
       </c>
       <c r="E1531" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1531" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">23/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1532" customHeight="1" ht="20">
       <c r="A1532" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1532" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1532" s="1" t="n">
         <v>44087</v>
@@ -49135,14 +49135,14 @@
         </is>
       </c>
       <c r="E1532" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1532" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">23/10/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
@@ -49693,10 +49693,10 @@
     </row>
     <row r="1550" customHeight="1" ht="20">
       <c r="A1550" s="1" t="n">
-        <v>1624906</v>
+        <v>1598892</v>
       </c>
       <c r="B1550" s="1" t="n">
-        <v>29565</v>
+        <v>27486</v>
       </c>
       <c r="C1550" s="1" t="n">
         <v>43437</v>
@@ -49711,24 +49711,24 @@
         </is>
       </c>
       <c r="E1550" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F1550" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">08/11/2026</t>
+            <t xml:space="preserve">30/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1551" customHeight="1" ht="20">
       <c r="A1551" s="1" t="n">
-        <v>1598892</v>
+        <v>1624906</v>
       </c>
       <c r="B1551" s="1" t="n">
-        <v>27486</v>
+        <v>29565</v>
       </c>
       <c r="C1551" s="1" t="n">
         <v>43437</v>
@@ -49743,14 +49743,14 @@
         </is>
       </c>
       <c r="E1551" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F1551" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/11/2026</t>
+            <t xml:space="preserve">08/11/2026</t>
           </r>
         </is>
       </c>

--- a/data/COMPRAS_PENDENTES.xlsx
+++ b/data/COMPRAS_PENDENTES.xlsx
@@ -4829,10 +4829,10 @@
     </row>
     <row r="148" customHeight="1" ht="20">
       <c r="A148" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B148" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C148" s="1" t="n">
         <v>9411</v>
@@ -4847,24 +4847,24 @@
         </is>
       </c>
       <c r="E148" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F148" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="149" customHeight="1" ht="20">
       <c r="A149" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B149" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C149" s="1" t="n">
         <v>9411</v>
@@ -4879,14 +4879,14 @@
         </is>
       </c>
       <c r="E149" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F149" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -5277,10 +5277,10 @@
     </row>
     <row r="162" customHeight="1" ht="20">
       <c r="A162" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B162" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C162" s="1" t="n">
         <v>9418</v>
@@ -5295,24 +5295,24 @@
         </is>
       </c>
       <c r="E162" s="1" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F162" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="163" customHeight="1" ht="20">
       <c r="A163" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B163" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C163" s="1" t="n">
         <v>9418</v>
@@ -5327,14 +5327,14 @@
         </is>
       </c>
       <c r="E163" s="1" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F163" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -5501,10 +5501,10 @@
     </row>
     <row r="169" customHeight="1" ht="20">
       <c r="A169" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B169" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C169" s="1" t="n">
         <v>9423</v>
@@ -5526,17 +5526,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="170" customHeight="1" ht="20">
       <c r="A170" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B170" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C170" s="1" t="n">
         <v>9423</v>
@@ -5558,7 +5558,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -6717,10 +6717,10 @@
     </row>
     <row r="207" customHeight="1" ht="20">
       <c r="A207" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B207" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C207" s="1" t="n">
         <v>11311</v>
@@ -6742,17 +6742,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="208" customHeight="1" ht="20">
       <c r="A208" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B208" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C208" s="1" t="n">
         <v>11311</v>
@@ -6774,7 +6774,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -11837,10 +11837,10 @@
     </row>
     <row r="367" customHeight="1" ht="20">
       <c r="A367" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B367" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C367" s="1" t="n">
         <v>13665</v>
@@ -11855,24 +11855,24 @@
         </is>
       </c>
       <c r="E367" s="1" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F367" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="368" customHeight="1" ht="20">
       <c r="A368" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B368" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C368" s="1" t="n">
         <v>13665</v>
@@ -11887,14 +11887,14 @@
         </is>
       </c>
       <c r="E368" s="1" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F368" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -12029,10 +12029,10 @@
     </row>
     <row r="373" customHeight="1" ht="20">
       <c r="A373" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B373" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C373" s="1" t="n">
         <v>13761</v>
@@ -12047,24 +12047,24 @@
         </is>
       </c>
       <c r="E373" s="1" t="n">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="F373" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="374" customHeight="1" ht="20">
       <c r="A374" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B374" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C374" s="1" t="n">
         <v>13761</v>
@@ -12079,14 +12079,14 @@
         </is>
       </c>
       <c r="E374" s="1" t="n">
-        <v>200</v>
+        <v>3000</v>
       </c>
       <c r="F374" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -12797,10 +12797,10 @@
     </row>
     <row r="397" customHeight="1" ht="20">
       <c r="A397" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B397" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C397" s="1" t="n">
         <v>13763</v>
@@ -12815,24 +12815,24 @@
         </is>
       </c>
       <c r="E397" s="1" t="n">
-        <v>2000</v>
+        <v>300</v>
       </c>
       <c r="F397" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="398" customHeight="1" ht="20">
       <c r="A398" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B398" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C398" s="1" t="n">
         <v>13763</v>
@@ -12847,24 +12847,24 @@
         </is>
       </c>
       <c r="E398" s="1" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="F398" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="399" customHeight="1" ht="20">
       <c r="A399" s="1" t="n">
-        <v>1630636</v>
+        <v>1523488</v>
       </c>
       <c r="B399" s="1" t="n">
-        <v>29656</v>
+        <v>24896</v>
       </c>
       <c r="C399" s="1" t="n">
         <v>13766</v>
@@ -12879,24 +12879,24 @@
         </is>
       </c>
       <c r="E399" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F399" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="400" customHeight="1" ht="20">
       <c r="A400" s="1" t="n">
-        <v>1523488</v>
+        <v>1630636</v>
       </c>
       <c r="B400" s="1" t="n">
-        <v>24896</v>
+        <v>29656</v>
       </c>
       <c r="C400" s="1" t="n">
         <v>13766</v>
@@ -12911,14 +12911,14 @@
         </is>
       </c>
       <c r="E400" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F400" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -13309,10 +13309,10 @@
     </row>
     <row r="413" customHeight="1" ht="20">
       <c r="A413" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B413" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C413" s="1" t="n">
         <v>13185</v>
@@ -13327,24 +13327,24 @@
         </is>
       </c>
       <c r="E413" s="1" t="n">
-        <v>3000</v>
+        <v>300</v>
       </c>
       <c r="F413" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="414" customHeight="1" ht="20">
       <c r="A414" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B414" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C414" s="1" t="n">
         <v>13185</v>
@@ -13359,14 +13359,14 @@
         </is>
       </c>
       <c r="E414" s="1" t="n">
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="F414" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -13725,10 +13725,10 @@
     </row>
     <row r="426" customHeight="1" ht="20">
       <c r="A426" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B426" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C426" s="1" t="n">
         <v>13939</v>
@@ -13743,24 +13743,24 @@
         </is>
       </c>
       <c r="E426" s="1" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F426" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="427" customHeight="1" ht="20">
       <c r="A427" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B427" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C427" s="1" t="n">
         <v>13939</v>
@@ -13775,14 +13775,14 @@
         </is>
       </c>
       <c r="E427" s="1" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F427" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
@@ -15197,10 +15197,10 @@
     </row>
     <row r="472" customHeight="1" ht="20">
       <c r="A472" s="1" t="n">
-        <v>1630636</v>
+        <v>1523488</v>
       </c>
       <c r="B472" s="1" t="n">
-        <v>29656</v>
+        <v>24896</v>
       </c>
       <c r="C472" s="1" t="n">
         <v>13503</v>
@@ -15222,17 +15222,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="473" customHeight="1" ht="20">
       <c r="A473" s="1" t="n">
-        <v>1523488</v>
+        <v>1630636</v>
       </c>
       <c r="B473" s="1" t="n">
-        <v>24896</v>
+        <v>29656</v>
       </c>
       <c r="C473" s="1" t="n">
         <v>13503</v>
@@ -15254,7 +15254,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -15453,10 +15453,10 @@
     </row>
     <row r="480" customHeight="1" ht="20">
       <c r="A480" s="1" t="n">
-        <v>1630636</v>
+        <v>1523488</v>
       </c>
       <c r="B480" s="1" t="n">
-        <v>29656</v>
+        <v>24896</v>
       </c>
       <c r="C480" s="1" t="n">
         <v>13507</v>
@@ -15471,24 +15471,24 @@
         </is>
       </c>
       <c r="E480" s="1" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F480" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="481" customHeight="1" ht="20">
       <c r="A481" s="1" t="n">
-        <v>1523488</v>
+        <v>1630636</v>
       </c>
       <c r="B481" s="1" t="n">
-        <v>24896</v>
+        <v>29656</v>
       </c>
       <c r="C481" s="1" t="n">
         <v>13507</v>
@@ -15503,24 +15503,24 @@
         </is>
       </c>
       <c r="E481" s="1" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F481" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="482" customHeight="1" ht="20">
       <c r="A482" s="1" t="n">
-        <v>1630636</v>
+        <v>1523488</v>
       </c>
       <c r="B482" s="1" t="n">
-        <v>29656</v>
+        <v>24896</v>
       </c>
       <c r="C482" s="1" t="n">
         <v>13508</v>
@@ -15535,24 +15535,24 @@
         </is>
       </c>
       <c r="E482" s="1" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F482" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="483" customHeight="1" ht="20">
       <c r="A483" s="1" t="n">
-        <v>1523488</v>
+        <v>1630636</v>
       </c>
       <c r="B483" s="1" t="n">
-        <v>24896</v>
+        <v>29656</v>
       </c>
       <c r="C483" s="1" t="n">
         <v>13508</v>
@@ -15567,14 +15567,14 @@
         </is>
       </c>
       <c r="E483" s="1" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F483" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -15677,10 +15677,10 @@
     </row>
     <row r="487" customHeight="1" ht="20">
       <c r="A487" s="1" t="n">
-        <v>1630636</v>
+        <v>1523488</v>
       </c>
       <c r="B487" s="1" t="n">
-        <v>29656</v>
+        <v>24896</v>
       </c>
       <c r="C487" s="1" t="n">
         <v>13510</v>
@@ -15702,17 +15702,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="488" customHeight="1" ht="20">
       <c r="A488" s="1" t="n">
-        <v>1523488</v>
+        <v>1630636</v>
       </c>
       <c r="B488" s="1" t="n">
-        <v>24896</v>
+        <v>29656</v>
       </c>
       <c r="C488" s="1" t="n">
         <v>13510</v>
@@ -15734,7 +15734,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -16541,10 +16541,10 @@
     </row>
     <row r="514" customHeight="1" ht="20">
       <c r="A514" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B514" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C514" s="1" t="n">
         <v>13182</v>
@@ -16566,17 +16566,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="515" customHeight="1" ht="20">
       <c r="A515" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B515" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C515" s="1" t="n">
         <v>13182</v>
@@ -16598,7 +16598,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -16957,10 +16957,10 @@
     </row>
     <row r="527" customHeight="1" ht="20">
       <c r="A527" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B527" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C527" s="1" t="n">
         <v>13764</v>
@@ -16975,24 +16975,24 @@
         </is>
       </c>
       <c r="E527" s="1" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F527" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="528" customHeight="1" ht="20">
       <c r="A528" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B528" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C528" s="1" t="n">
         <v>13764</v>
@@ -17007,24 +17007,24 @@
         </is>
       </c>
       <c r="E528" s="1" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F528" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="529" customHeight="1" ht="20">
       <c r="A529" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B529" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C529" s="1" t="n">
         <v>13765</v>
@@ -17046,17 +17046,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="530" customHeight="1" ht="20">
       <c r="A530" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B530" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C530" s="1" t="n">
         <v>13765</v>
@@ -17078,7 +17078,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -17117,10 +17117,10 @@
     </row>
     <row r="532" customHeight="1" ht="20">
       <c r="A532" s="1" t="n">
-        <v>1630636</v>
+        <v>1523488</v>
       </c>
       <c r="B532" s="1" t="n">
-        <v>29656</v>
+        <v>24896</v>
       </c>
       <c r="C532" s="1" t="n">
         <v>13770</v>
@@ -17135,24 +17135,24 @@
         </is>
       </c>
       <c r="E532" s="1" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F532" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="533" customHeight="1" ht="20">
       <c r="A533" s="1" t="n">
-        <v>1523488</v>
+        <v>1630636</v>
       </c>
       <c r="B533" s="1" t="n">
-        <v>24896</v>
+        <v>29656</v>
       </c>
       <c r="C533" s="1" t="n">
         <v>13770</v>
@@ -17167,14 +17167,14 @@
         </is>
       </c>
       <c r="E533" s="1" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F533" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -17629,10 +17629,10 @@
     </row>
     <row r="548" customHeight="1" ht="20">
       <c r="A548" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B548" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C548" s="1" t="n">
         <v>13437</v>
@@ -17654,17 +17654,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="549" customHeight="1" ht="20">
       <c r="A549" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B549" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C549" s="1" t="n">
         <v>13437</v>
@@ -17686,7 +17686,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -17725,10 +17725,10 @@
     </row>
     <row r="551" customHeight="1" ht="20">
       <c r="A551" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B551" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C551" s="1" t="n">
         <v>13664</v>
@@ -17750,17 +17750,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="552" customHeight="1" ht="20">
       <c r="A552" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B552" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C552" s="1" t="n">
         <v>13664</v>
@@ -17782,7 +17782,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -18237,10 +18237,10 @@
     </row>
     <row r="567" customHeight="1" ht="20">
       <c r="A567" s="1" t="n">
-        <v>1630636</v>
+        <v>1523488</v>
       </c>
       <c r="B567" s="1" t="n">
-        <v>29656</v>
+        <v>24896</v>
       </c>
       <c r="C567" s="1" t="n">
         <v>13449</v>
@@ -18262,17 +18262,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="568" customHeight="1" ht="20">
       <c r="A568" s="1" t="n">
-        <v>1523488</v>
+        <v>1630636</v>
       </c>
       <c r="B568" s="1" t="n">
-        <v>24896</v>
+        <v>29656</v>
       </c>
       <c r="C568" s="1" t="n">
         <v>13449</v>
@@ -18294,7 +18294,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -18653,10 +18653,10 @@
     </row>
     <row r="580" customHeight="1" ht="20">
       <c r="A580" s="1" t="n">
-        <v>1630636</v>
+        <v>1523488</v>
       </c>
       <c r="B580" s="1" t="n">
-        <v>29656</v>
+        <v>24896</v>
       </c>
       <c r="C580" s="1" t="n">
         <v>14218</v>
@@ -18678,17 +18678,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="581" customHeight="1" ht="20">
       <c r="A581" s="1" t="n">
-        <v>1523488</v>
+        <v>1630636</v>
       </c>
       <c r="B581" s="1" t="n">
-        <v>24896</v>
+        <v>29656</v>
       </c>
       <c r="C581" s="1" t="n">
         <v>14218</v>
@@ -18710,7 +18710,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -18941,10 +18941,10 @@
     </row>
     <row r="589" customHeight="1" ht="20">
       <c r="A589" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B589" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C589" s="1" t="n">
         <v>14811</v>
@@ -18959,24 +18959,24 @@
         </is>
       </c>
       <c r="E589" s="1" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="F589" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="590" customHeight="1" ht="20">
       <c r="A590" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B590" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C590" s="1" t="n">
         <v>14811</v>
@@ -18991,24 +18991,24 @@
         </is>
       </c>
       <c r="E590" s="1" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F590" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="591" customHeight="1" ht="20">
       <c r="A591" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B591" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C591" s="1" t="n">
         <v>14843</v>
@@ -19023,24 +19023,24 @@
         </is>
       </c>
       <c r="E591" s="1" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F591" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="592" customHeight="1" ht="20">
       <c r="A592" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B592" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C592" s="1" t="n">
         <v>14843</v>
@@ -19055,14 +19055,14 @@
         </is>
       </c>
       <c r="E592" s="1" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F592" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -19325,10 +19325,10 @@
     </row>
     <row r="601" customHeight="1" ht="20">
       <c r="A601" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B601" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C601" s="1" t="n">
         <v>14791</v>
@@ -19350,17 +19350,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="602" customHeight="1" ht="20">
       <c r="A602" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B602" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C602" s="1" t="n">
         <v>14791</v>
@@ -19382,7 +19382,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
@@ -19549,10 +19549,10 @@
     </row>
     <row r="608" customHeight="1" ht="20">
       <c r="A608" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B608" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C608" s="1" t="n">
         <v>14986</v>
@@ -19574,17 +19574,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="609" customHeight="1" ht="20">
       <c r="A609" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B609" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C609" s="1" t="n">
         <v>14986</v>
@@ -19606,7 +19606,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -19997,10 +19997,10 @@
     </row>
     <row r="622" customHeight="1" ht="20">
       <c r="A622" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B622" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C622" s="1" t="n">
         <v>14491</v>
@@ -20015,24 +20015,24 @@
         </is>
       </c>
       <c r="E622" s="1" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F622" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="623" customHeight="1" ht="20">
       <c r="A623" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B623" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C623" s="1" t="n">
         <v>14491</v>
@@ -20047,14 +20047,14 @@
         </is>
       </c>
       <c r="E623" s="1" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F623" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -20253,10 +20253,10 @@
     </row>
     <row r="630" customHeight="1" ht="20">
       <c r="A630" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B630" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C630" s="1" t="n">
         <v>14495</v>
@@ -20271,24 +20271,24 @@
         </is>
       </c>
       <c r="E630" s="1" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F630" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="631" customHeight="1" ht="20">
       <c r="A631" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B631" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C631" s="1" t="n">
         <v>14495</v>
@@ -20303,14 +20303,14 @@
         </is>
       </c>
       <c r="E631" s="1" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F631" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -21053,10 +21053,10 @@
     </row>
     <row r="655" customHeight="1" ht="20">
       <c r="A655" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B655" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C655" s="1" t="n">
         <v>14494</v>
@@ -21078,17 +21078,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="656" customHeight="1" ht="20">
       <c r="A656" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B656" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C656" s="1" t="n">
         <v>14494</v>
@@ -21110,7 +21110,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -21661,10 +21661,10 @@
     </row>
     <row r="674" customHeight="1" ht="20">
       <c r="A674" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B674" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C674" s="1" t="n">
         <v>14493</v>
@@ -21679,24 +21679,24 @@
         </is>
       </c>
       <c r="E674" s="1" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F674" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="675" customHeight="1" ht="20">
       <c r="A675" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B675" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C675" s="1" t="n">
         <v>14493</v>
@@ -21711,14 +21711,14 @@
         </is>
       </c>
       <c r="E675" s="1" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F675" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -21981,10 +21981,10 @@
     </row>
     <row r="684" customHeight="1" ht="20">
       <c r="A684" s="1" t="n">
-        <v>1635939</v>
+        <v>1598892</v>
       </c>
       <c r="B684" s="1" t="n">
-        <v>29609</v>
+        <v>27486</v>
       </c>
       <c r="C684" s="1" t="n">
         <v>14137</v>
@@ -21999,24 +21999,24 @@
         </is>
       </c>
       <c r="E684" s="1" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F684" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/11/2026</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="685" customHeight="1" ht="20">
       <c r="A685" s="1" t="n">
-        <v>1598892</v>
+        <v>1635939</v>
       </c>
       <c r="B685" s="1" t="n">
-        <v>27486</v>
+        <v>29609</v>
       </c>
       <c r="C685" s="1" t="n">
         <v>14137</v>
@@ -22031,14 +22031,14 @@
         </is>
       </c>
       <c r="E685" s="1" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F685" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">13/11/2026</t>
           </r>
         </is>
       </c>
@@ -23069,10 +23069,10 @@
     </row>
     <row r="718" customHeight="1" ht="20">
       <c r="A718" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B718" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C718" s="1" t="n">
         <v>15498</v>
@@ -23087,24 +23087,24 @@
         </is>
       </c>
       <c r="E718" s="1" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F718" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="719" customHeight="1" ht="20">
       <c r="A719" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B719" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C719" s="1" t="n">
         <v>15498</v>
@@ -23119,24 +23119,24 @@
         </is>
       </c>
       <c r="E719" s="1" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F719" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="720" customHeight="1" ht="20">
       <c r="A720" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B720" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C720" s="1" t="n">
         <v>15499</v>
@@ -23151,24 +23151,24 @@
         </is>
       </c>
       <c r="E720" s="1" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F720" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="721" customHeight="1" ht="20">
       <c r="A721" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B721" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C721" s="1" t="n">
         <v>15499</v>
@@ -23183,14 +23183,14 @@
         </is>
       </c>
       <c r="E721" s="1" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F721" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -23741,10 +23741,10 @@
     </row>
     <row r="739" customHeight="1" ht="20">
       <c r="A739" s="1" t="n">
-        <v>1630636</v>
+        <v>1523488</v>
       </c>
       <c r="B739" s="1" t="n">
-        <v>29656</v>
+        <v>24896</v>
       </c>
       <c r="C739" s="1" t="n">
         <v>15479</v>
@@ -23759,24 +23759,24 @@
         </is>
       </c>
       <c r="E739" s="1" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="F739" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="740" customHeight="1" ht="20">
       <c r="A740" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B740" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C740" s="1" t="n">
         <v>15479</v>
@@ -23791,24 +23791,24 @@
         </is>
       </c>
       <c r="E740" s="1" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F740" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="741" customHeight="1" ht="20">
       <c r="A741" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B741" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C741" s="1" t="n">
         <v>15479</v>
@@ -23823,14 +23823,14 @@
         </is>
       </c>
       <c r="E741" s="1" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F741" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -23869,10 +23869,10 @@
     </row>
     <row r="743" customHeight="1" ht="20">
       <c r="A743" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B743" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C743" s="1" t="n">
         <v>15864</v>
@@ -23887,24 +23887,24 @@
         </is>
       </c>
       <c r="E743" s="1" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F743" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="744" customHeight="1" ht="20">
       <c r="A744" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B744" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C744" s="1" t="n">
         <v>15864</v>
@@ -23919,14 +23919,14 @@
         </is>
       </c>
       <c r="E744" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F744" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -24029,10 +24029,10 @@
     </row>
     <row r="748" customHeight="1" ht="20">
       <c r="A748" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B748" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C748" s="1" t="n">
         <v>15485</v>
@@ -24047,24 +24047,24 @@
         </is>
       </c>
       <c r="E748" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F748" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="749" customHeight="1" ht="20">
       <c r="A749" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B749" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C749" s="1" t="n">
         <v>15485</v>
@@ -24079,14 +24079,14 @@
         </is>
       </c>
       <c r="E749" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F749" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -24349,10 +24349,10 @@
     </row>
     <row r="758" customHeight="1" ht="20">
       <c r="A758" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B758" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C758" s="1" t="n">
         <v>15507</v>
@@ -24367,14 +24367,14 @@
         </is>
       </c>
       <c r="E758" s="1" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F758" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
@@ -24399,7 +24399,7 @@
         </is>
       </c>
       <c r="E759" s="1" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F759" s="1" t="inlineStr">
         <is>
@@ -24413,10 +24413,10 @@
     </row>
     <row r="760" customHeight="1" ht="20">
       <c r="A760" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B760" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C760" s="1" t="n">
         <v>15507</v>
@@ -24431,14 +24431,14 @@
         </is>
       </c>
       <c r="E760" s="1" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F760" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -24477,10 +24477,10 @@
     </row>
     <row r="762" customHeight="1" ht="20">
       <c r="A762" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B762" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C762" s="1" t="n">
         <v>15484</v>
@@ -24495,24 +24495,24 @@
         </is>
       </c>
       <c r="E762" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F762" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="763" customHeight="1" ht="20">
       <c r="A763" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B763" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C763" s="1" t="n">
         <v>15484</v>
@@ -24527,14 +24527,14 @@
         </is>
       </c>
       <c r="E763" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F763" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -24669,10 +24669,10 @@
     </row>
     <row r="768" customHeight="1" ht="20">
       <c r="A768" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B768" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C768" s="1" t="n">
         <v>15377</v>
@@ -24687,24 +24687,24 @@
         </is>
       </c>
       <c r="E768" s="1" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="F768" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="769" customHeight="1" ht="20">
       <c r="A769" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B769" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C769" s="1" t="n">
         <v>15377</v>
@@ -24719,14 +24719,14 @@
         </is>
       </c>
       <c r="E769" s="1" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="F769" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -24797,10 +24797,10 @@
     </row>
     <row r="772" customHeight="1" ht="20">
       <c r="A772" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B772" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C772" s="1" t="n">
         <v>15178</v>
@@ -24822,17 +24822,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="773" customHeight="1" ht="20">
       <c r="A773" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B773" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C773" s="1" t="n">
         <v>15178</v>
@@ -24854,7 +24854,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -24957,10 +24957,10 @@
     </row>
     <row r="777" customHeight="1" ht="20">
       <c r="A777" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B777" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C777" s="1" t="n">
         <v>15505</v>
@@ -24975,14 +24975,14 @@
         </is>
       </c>
       <c r="E777" s="1" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F777" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
@@ -25007,7 +25007,7 @@
         </is>
       </c>
       <c r="E778" s="1" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F778" s="1" t="inlineStr">
         <is>
@@ -25021,10 +25021,10 @@
     </row>
     <row r="779" customHeight="1" ht="20">
       <c r="A779" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B779" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C779" s="1" t="n">
         <v>15505</v>
@@ -25039,14 +25039,14 @@
         </is>
       </c>
       <c r="E779" s="1" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F779" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -25309,10 +25309,10 @@
     </row>
     <row r="788" customHeight="1" ht="20">
       <c r="A788" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B788" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C788" s="1" t="n">
         <v>15378</v>
@@ -25327,24 +25327,24 @@
         </is>
       </c>
       <c r="E788" s="1" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F788" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="789" customHeight="1" ht="20">
       <c r="A789" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B789" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C789" s="1" t="n">
         <v>15378</v>
@@ -25359,14 +25359,14 @@
         </is>
       </c>
       <c r="E789" s="1" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F789" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -25437,10 +25437,10 @@
     </row>
     <row r="792" customHeight="1" ht="20">
       <c r="A792" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B792" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C792" s="1" t="n">
         <v>15660</v>
@@ -25462,17 +25462,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="793" customHeight="1" ht="20">
       <c r="A793" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B793" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C793" s="1" t="n">
         <v>15660</v>
@@ -25494,7 +25494,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -25533,10 +25533,10 @@
     </row>
     <row r="795" customHeight="1" ht="20">
       <c r="A795" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B795" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C795" s="1" t="n">
         <v>15662</v>
@@ -25558,17 +25558,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="796" customHeight="1" ht="20">
       <c r="A796" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B796" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C796" s="1" t="n">
         <v>15662</v>
@@ -25590,7 +25590,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -26045,10 +26045,10 @@
     </row>
     <row r="811" customHeight="1" ht="20">
       <c r="A811" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B811" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C811" s="1" t="n">
         <v>15867</v>
@@ -26070,17 +26070,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="812" customHeight="1" ht="20">
       <c r="A812" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B812" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C812" s="1" t="n">
         <v>15867</v>
@@ -26102,7 +26102,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -26301,10 +26301,10 @@
     </row>
     <row r="819" customHeight="1" ht="20">
       <c r="A819" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B819" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C819" s="1" t="n">
         <v>15856</v>
@@ -26326,17 +26326,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="820" customHeight="1" ht="20">
       <c r="A820" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B820" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C820" s="1" t="n">
         <v>15856</v>
@@ -26358,7 +26358,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -26461,10 +26461,10 @@
     </row>
     <row r="824" customHeight="1" ht="20">
       <c r="A824" s="1" t="n">
-        <v>1630636</v>
+        <v>1523488</v>
       </c>
       <c r="B824" s="1" t="n">
-        <v>29656</v>
+        <v>24896</v>
       </c>
       <c r="C824" s="1" t="n">
         <v>15183</v>
@@ -26479,24 +26479,24 @@
         </is>
       </c>
       <c r="E824" s="1" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F824" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="825" customHeight="1" ht="20">
       <c r="A825" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B825" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C825" s="1" t="n">
         <v>15183</v>
@@ -26511,24 +26511,24 @@
         </is>
       </c>
       <c r="E825" s="1" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F825" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="826" customHeight="1" ht="20">
       <c r="A826" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B826" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C826" s="1" t="n">
         <v>15183</v>
@@ -26543,14 +26543,14 @@
         </is>
       </c>
       <c r="E826" s="1" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F826" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -26781,10 +26781,10 @@
     </row>
     <row r="834" customHeight="1" ht="20">
       <c r="A834" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B834" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C834" s="1" t="n">
         <v>15376</v>
@@ -26799,24 +26799,24 @@
         </is>
       </c>
       <c r="E834" s="1" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F834" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="835" customHeight="1" ht="20">
       <c r="A835" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B835" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C835" s="1" t="n">
         <v>15376</v>
@@ -26831,14 +26831,14 @@
         </is>
       </c>
       <c r="E835" s="1" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F835" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -27421,10 +27421,10 @@
     </row>
     <row r="854" customHeight="1" ht="20">
       <c r="A854" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B854" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C854" s="1" t="n">
         <v>24866</v>
@@ -27446,17 +27446,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="855" customHeight="1" ht="20">
       <c r="A855" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B855" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C855" s="1" t="n">
         <v>24866</v>
@@ -27478,7 +27478,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -27581,10 +27581,10 @@
     </row>
     <row r="859" customHeight="1" ht="20">
       <c r="A859" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B859" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C859" s="1" t="n">
         <v>24865</v>
@@ -27606,17 +27606,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="860" customHeight="1" ht="20">
       <c r="A860" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B860" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C860" s="1" t="n">
         <v>24865</v>
@@ -27638,7 +27638,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -28669,10 +28669,10 @@
     </row>
     <row r="893" customHeight="1" ht="20">
       <c r="A893" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B893" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C893" s="1" t="n">
         <v>25879</v>
@@ -28687,24 +28687,24 @@
         </is>
       </c>
       <c r="E893" s="1" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F893" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="894" customHeight="1" ht="20">
       <c r="A894" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B894" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C894" s="1" t="n">
         <v>25879</v>
@@ -28719,14 +28719,14 @@
         </is>
       </c>
       <c r="E894" s="1" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F894" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
@@ -29181,10 +29181,10 @@
     </row>
     <row r="909" customHeight="1" ht="20">
       <c r="A909" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B909" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C909" s="1" t="n">
         <v>26413</v>
@@ -29199,24 +29199,24 @@
         </is>
       </c>
       <c r="E909" s="1" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="F909" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="910" customHeight="1" ht="20">
       <c r="A910" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B910" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C910" s="1" t="n">
         <v>26413</v>
@@ -29231,24 +29231,24 @@
         </is>
       </c>
       <c r="E910" s="1" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F910" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="911" customHeight="1" ht="20">
       <c r="A911" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B911" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C911" s="1" t="n">
         <v>26414</v>
@@ -29270,17 +29270,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="912" customHeight="1" ht="20">
       <c r="A912" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B912" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C912" s="1" t="n">
         <v>26414</v>
@@ -29302,7 +29302,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -29373,10 +29373,10 @@
     </row>
     <row r="915" customHeight="1" ht="20">
       <c r="A915" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B915" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C915" s="1" t="n">
         <v>26417</v>
@@ -29398,17 +29398,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="916" customHeight="1" ht="20">
       <c r="A916" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B916" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C916" s="1" t="n">
         <v>26417</v>
@@ -29430,7 +29430,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -30429,10 +30429,10 @@
     </row>
     <row r="948" customHeight="1" ht="20">
       <c r="A948" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B948" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C948" s="1" t="n">
         <v>26083</v>
@@ -30454,17 +30454,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="949" customHeight="1" ht="20">
       <c r="A949" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B949" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C949" s="1" t="n">
         <v>26083</v>
@@ -30486,7 +30486,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -30621,10 +30621,10 @@
     </row>
     <row r="954" customHeight="1" ht="20">
       <c r="A954" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B954" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C954" s="1" t="n">
         <v>26474</v>
@@ -30639,24 +30639,24 @@
         </is>
       </c>
       <c r="E954" s="1" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F954" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="955" customHeight="1" ht="20">
       <c r="A955" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B955" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C955" s="1" t="n">
         <v>26474</v>
@@ -30671,24 +30671,24 @@
         </is>
       </c>
       <c r="E955" s="1" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F955" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="956" customHeight="1" ht="20">
       <c r="A956" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B956" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C956" s="1" t="n">
         <v>26475</v>
@@ -30703,24 +30703,24 @@
         </is>
       </c>
       <c r="E956" s="1" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F956" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="957" customHeight="1" ht="20">
       <c r="A957" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B957" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C957" s="1" t="n">
         <v>26475</v>
@@ -30735,14 +30735,14 @@
         </is>
       </c>
       <c r="E957" s="1" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="F957" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -30941,10 +30941,10 @@
     </row>
     <row r="964" customHeight="1" ht="20">
       <c r="A964" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B964" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C964" s="1" t="n">
         <v>26479</v>
@@ -30966,17 +30966,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="965" customHeight="1" ht="20">
       <c r="A965" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B965" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C965" s="1" t="n">
         <v>26479</v>
@@ -30998,7 +30998,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -31453,10 +31453,10 @@
     </row>
     <row r="980" customHeight="1" ht="20">
       <c r="A980" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B980" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C980" s="1" t="n">
         <v>26497</v>
@@ -31471,24 +31471,24 @@
         </is>
       </c>
       <c r="E980" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F980" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="981" customHeight="1" ht="20">
       <c r="A981" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B981" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C981" s="1" t="n">
         <v>26497</v>
@@ -31503,14 +31503,14 @@
         </is>
       </c>
       <c r="E981" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F981" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -31549,10 +31549,10 @@
     </row>
     <row r="983" customHeight="1" ht="20">
       <c r="A983" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B983" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C983" s="1" t="n">
         <v>26501</v>
@@ -31567,24 +31567,24 @@
         </is>
       </c>
       <c r="E983" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F983" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="984" customHeight="1" ht="20">
       <c r="A984" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B984" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C984" s="1" t="n">
         <v>26501</v>
@@ -31599,14 +31599,14 @@
         </is>
       </c>
       <c r="E984" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F984" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -33117,10 +33117,10 @@
     </row>
     <row r="1032" customHeight="1" ht="20">
       <c r="A1032" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B1032" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C1032" s="1" t="n">
         <v>26469</v>
@@ -33142,17 +33142,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1033" customHeight="1" ht="20">
       <c r="A1033" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B1033" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C1033" s="1" t="n">
         <v>26469</v>
@@ -33174,7 +33174,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -35293,10 +35293,10 @@
     </row>
     <row r="1100" customHeight="1" ht="20">
       <c r="A1100" s="1" t="n">
-        <v>1630636</v>
+        <v>1523488</v>
       </c>
       <c r="B1100" s="1" t="n">
-        <v>29656</v>
+        <v>24896</v>
       </c>
       <c r="C1100" s="1" t="n">
         <v>26539</v>
@@ -35311,24 +35311,24 @@
         </is>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F1100" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1101" customHeight="1" ht="20">
       <c r="A1101" s="1" t="n">
-        <v>1523488</v>
+        <v>1630636</v>
       </c>
       <c r="B1101" s="1" t="n">
-        <v>24896</v>
+        <v>29656</v>
       </c>
       <c r="C1101" s="1" t="n">
         <v>26539</v>
@@ -35343,14 +35343,14 @@
         </is>
       </c>
       <c r="E1101" s="1" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F1101" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -35421,10 +35421,10 @@
     </row>
     <row r="1104" customHeight="1" ht="20">
       <c r="A1104" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B1104" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C1104" s="1" t="n">
         <v>26503</v>
@@ -35446,17 +35446,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1105" customHeight="1" ht="20">
       <c r="A1105" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B1105" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C1105" s="1" t="n">
         <v>26503</v>
@@ -35478,7 +35478,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -35517,10 +35517,10 @@
     </row>
     <row r="1107" customHeight="1" ht="20">
       <c r="A1107" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B1107" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C1107" s="1" t="n">
         <v>26504</v>
@@ -35535,24 +35535,24 @@
         </is>
       </c>
       <c r="E1107" s="1" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F1107" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1108" customHeight="1" ht="20">
       <c r="A1108" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B1108" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C1108" s="1" t="n">
         <v>26504</v>
@@ -35567,14 +35567,14 @@
         </is>
       </c>
       <c r="E1108" s="1" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F1108" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -35677,10 +35677,10 @@
     </row>
     <row r="1112" customHeight="1" ht="20">
       <c r="A1112" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B1112" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C1112" s="1" t="n">
         <v>26508</v>
@@ -35702,17 +35702,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1113" customHeight="1" ht="20">
       <c r="A1113" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B1113" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C1113" s="1" t="n">
         <v>26508</v>
@@ -35734,7 +35734,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -35997,10 +35997,10 @@
     </row>
     <row r="1122" customHeight="1" ht="20">
       <c r="A1122" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B1122" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C1122" s="1" t="n">
         <v>27415</v>
@@ -36022,17 +36022,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1123" customHeight="1" ht="20">
       <c r="A1123" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B1123" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C1123" s="1" t="n">
         <v>27415</v>
@@ -36054,7 +36054,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -36797,10 +36797,10 @@
     </row>
     <row r="1147" customHeight="1" ht="20">
       <c r="A1147" s="1" t="n">
-        <v>1630636</v>
+        <v>1523488</v>
       </c>
       <c r="B1147" s="1" t="n">
-        <v>29656</v>
+        <v>24896</v>
       </c>
       <c r="C1147" s="1" t="n">
         <v>27413</v>
@@ -36815,24 +36815,24 @@
         </is>
       </c>
       <c r="E1147" s="1" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F1147" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1148" customHeight="1" ht="20">
       <c r="A1148" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1148" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1148" s="1" t="n">
         <v>27413</v>
@@ -36847,24 +36847,24 @@
         </is>
       </c>
       <c r="E1148" s="1" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F1148" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1149" customHeight="1" ht="20">
       <c r="A1149" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B1149" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C1149" s="1" t="n">
         <v>27413</v>
@@ -36886,7 +36886,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -37181,10 +37181,10 @@
     </row>
     <row r="1159" customHeight="1" ht="20">
       <c r="A1159" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B1159" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C1159" s="1" t="n">
         <v>27646</v>
@@ -37199,24 +37199,24 @@
         </is>
       </c>
       <c r="E1159" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F1159" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1160" customHeight="1" ht="20">
       <c r="A1160" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B1160" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C1160" s="1" t="n">
         <v>27646</v>
@@ -37231,14 +37231,14 @@
         </is>
       </c>
       <c r="E1160" s="1" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F1160" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -37533,10 +37533,10 @@
     </row>
     <row r="1170" customHeight="1" ht="20">
       <c r="A1170" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1170" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1170" s="1" t="n">
         <v>27756</v>
@@ -37551,24 +37551,24 @@
         </is>
       </c>
       <c r="E1170" s="1" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F1170" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1171" customHeight="1" ht="20">
       <c r="A1171" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1171" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1171" s="1" t="n">
         <v>27756</v>
@@ -37583,14 +37583,14 @@
         </is>
       </c>
       <c r="E1171" s="1" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F1171" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
@@ -40687,7 +40687,7 @@
         </is>
       </c>
       <c r="E1268" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F1268" s="1" t="inlineStr">
         <is>
@@ -40719,7 +40719,7 @@
         </is>
       </c>
       <c r="E1269" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F1269" s="1" t="inlineStr">
         <is>
@@ -47325,10 +47325,10 @@
     </row>
     <row r="1476" customHeight="1" ht="20">
       <c r="A1476" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B1476" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C1476" s="1" t="n">
         <v>31114</v>
@@ -47343,24 +47343,24 @@
         </is>
       </c>
       <c r="E1476" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1476" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1477" customHeight="1" ht="20">
       <c r="A1477" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B1477" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C1477" s="1" t="n">
         <v>31114</v>
@@ -47375,14 +47375,14 @@
         </is>
       </c>
       <c r="E1477" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F1477" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -48605,10 +48605,10 @@
     </row>
     <row r="1516" customHeight="1" ht="20">
       <c r="A1516" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B1516" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C1516" s="1" t="n">
         <v>32987</v>
@@ -48630,17 +48630,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1517" customHeight="1" ht="20">
       <c r="A1517" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B1517" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C1517" s="1" t="n">
         <v>32987</v>
@@ -48662,7 +48662,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -48861,10 +48861,10 @@
     </row>
     <row r="1524" customHeight="1" ht="20">
       <c r="A1524" s="1" t="n">
-        <v>1630636</v>
+        <v>1523488</v>
       </c>
       <c r="B1524" s="1" t="n">
-        <v>29656</v>
+        <v>24896</v>
       </c>
       <c r="C1524" s="1" t="n">
         <v>32696</v>
@@ -48886,17 +48886,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1525" customHeight="1" ht="20">
       <c r="A1525" s="1" t="n">
-        <v>1523488</v>
+        <v>1630636</v>
       </c>
       <c r="B1525" s="1" t="n">
-        <v>24896</v>
+        <v>29656</v>
       </c>
       <c r="C1525" s="1" t="n">
         <v>32696</v>
@@ -48918,7 +48918,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -52765,10 +52765,10 @@
     </row>
     <row r="1646" customHeight="1" ht="20">
       <c r="A1646" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1646" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1646" s="1" t="n">
         <v>37398</v>
@@ -52790,17 +52790,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1647" customHeight="1" ht="20">
       <c r="A1647" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1647" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1647" s="1" t="n">
         <v>37398</v>
@@ -52822,7 +52822,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
@@ -54461,10 +54461,10 @@
     </row>
     <row r="1699" customHeight="1" ht="20">
       <c r="A1699" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B1699" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C1699" s="1" t="n">
         <v>39295</v>
@@ -54479,24 +54479,24 @@
         </is>
       </c>
       <c r="E1699" s="1" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F1699" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1700" customHeight="1" ht="20">
       <c r="A1700" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B1700" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C1700" s="1" t="n">
         <v>39295</v>
@@ -54511,14 +54511,14 @@
         </is>
       </c>
       <c r="E1700" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F1700" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -54973,10 +54973,10 @@
     </row>
     <row r="1715" customHeight="1" ht="20">
       <c r="A1715" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B1715" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C1715" s="1" t="n">
         <v>39299</v>
@@ -54991,24 +54991,24 @@
         </is>
       </c>
       <c r="E1715" s="1" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F1715" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1716" customHeight="1" ht="20">
       <c r="A1716" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B1716" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C1716" s="1" t="n">
         <v>39299</v>
@@ -55023,24 +55023,24 @@
         </is>
       </c>
       <c r="E1716" s="1" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F1716" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1717" customHeight="1" ht="20">
       <c r="A1717" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1717" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1717" s="1" t="n">
         <v>39347</v>
@@ -55055,24 +55055,24 @@
         </is>
       </c>
       <c r="E1717" s="1" t="n">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="F1717" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1718" customHeight="1" ht="20">
       <c r="A1718" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1718" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1718" s="1" t="n">
         <v>39347</v>
@@ -55087,14 +55087,14 @@
         </is>
       </c>
       <c r="E1718" s="1" t="n">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="F1718" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
@@ -55293,10 +55293,10 @@
     </row>
     <row r="1725" customHeight="1" ht="20">
       <c r="A1725" s="1" t="n">
-        <v>1630636</v>
+        <v>1598892</v>
       </c>
       <c r="B1725" s="1" t="n">
-        <v>29656</v>
+        <v>27486</v>
       </c>
       <c r="C1725" s="1" t="n">
         <v>39296</v>
@@ -55311,24 +55311,24 @@
         </is>
       </c>
       <c r="E1725" s="1" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F1725" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1726" customHeight="1" ht="20">
       <c r="A1726" s="1" t="n">
-        <v>1598892</v>
+        <v>1630636</v>
       </c>
       <c r="B1726" s="1" t="n">
-        <v>27486</v>
+        <v>29656</v>
       </c>
       <c r="C1726" s="1" t="n">
         <v>39296</v>
@@ -55343,24 +55343,24 @@
         </is>
       </c>
       <c r="E1726" s="1" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F1726" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1727" customHeight="1" ht="20">
       <c r="A1727" s="1" t="n">
-        <v>1630636</v>
+        <v>1523488</v>
       </c>
       <c r="B1727" s="1" t="n">
-        <v>29656</v>
+        <v>24896</v>
       </c>
       <c r="C1727" s="1" t="n">
         <v>39300</v>
@@ -55375,24 +55375,24 @@
         </is>
       </c>
       <c r="E1727" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F1727" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1728" customHeight="1" ht="20">
       <c r="A1728" s="1" t="n">
-        <v>1523488</v>
+        <v>1630636</v>
       </c>
       <c r="B1728" s="1" t="n">
-        <v>24896</v>
+        <v>29656</v>
       </c>
       <c r="C1728" s="1" t="n">
         <v>39300</v>
@@ -55407,14 +55407,14 @@
         </is>
       </c>
       <c r="E1728" s="1" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F1728" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -57821,10 +57821,10 @@
     </row>
     <row r="1804" customHeight="1" ht="20">
       <c r="A1804" s="1" t="n">
-        <v>1598892</v>
+        <v>1523488</v>
       </c>
       <c r="B1804" s="1" t="n">
-        <v>27486</v>
+        <v>24896</v>
       </c>
       <c r="C1804" s="1" t="n">
         <v>42112</v>
@@ -57839,24 +57839,24 @@
         </is>
       </c>
       <c r="E1804" s="1" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F1804" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1805" customHeight="1" ht="20">
       <c r="A1805" s="1" t="n">
-        <v>1523488</v>
+        <v>1598892</v>
       </c>
       <c r="B1805" s="1" t="n">
-        <v>24896</v>
+        <v>27486</v>
       </c>
       <c r="C1805" s="1" t="n">
         <v>42112</v>
@@ -57871,14 +57871,14 @@
         </is>
       </c>
       <c r="E1805" s="1" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F1805" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
@@ -59325,10 +59325,10 @@
     </row>
     <row r="1851" customHeight="1" ht="20">
       <c r="A1851" s="1" t="n">
-        <v>1630636</v>
+        <v>1523488</v>
       </c>
       <c r="B1851" s="1" t="n">
-        <v>29656</v>
+        <v>24896</v>
       </c>
       <c r="C1851" s="1" t="n">
         <v>44196</v>
@@ -59343,24 +59343,24 @@
         </is>
       </c>
       <c r="E1851" s="1" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="F1851" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1852" customHeight="1" ht="20">
       <c r="A1852" s="1" t="n">
-        <v>1523488</v>
+        <v>1630636</v>
       </c>
       <c r="B1852" s="1" t="n">
-        <v>24896</v>
+        <v>29656</v>
       </c>
       <c r="C1852" s="1" t="n">
         <v>44196</v>
@@ -59375,14 +59375,14 @@
         </is>
       </c>
       <c r="E1852" s="1" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="F1852" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -61053,10 +61053,10 @@
     </row>
     <row r="1905" customHeight="1" ht="20">
       <c r="A1905" s="1" t="n">
-        <v>1630636</v>
+        <v>1523488</v>
       </c>
       <c r="B1905" s="1" t="n">
-        <v>29656</v>
+        <v>24896</v>
       </c>
       <c r="C1905" s="1" t="n">
         <v>44199</v>
@@ -61071,24 +61071,24 @@
         </is>
       </c>
       <c r="E1905" s="1" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F1905" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1906" customHeight="1" ht="20">
       <c r="A1906" s="1" t="n">
-        <v>1523488</v>
+        <v>1630636</v>
       </c>
       <c r="B1906" s="1" t="n">
-        <v>24896</v>
+        <v>29656</v>
       </c>
       <c r="C1906" s="1" t="n">
         <v>44199</v>
@@ -61103,14 +61103,14 @@
         </is>
       </c>
       <c r="E1906" s="1" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F1906" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>

--- a/data/COMPRAS_PENDENTES.xlsx
+++ b/data/COMPRAS_PENDENTES.xlsx
@@ -19485,10 +19485,10 @@
     </row>
     <row r="606" customHeight="1" ht="20">
       <c r="A606" s="1" t="n">
-        <v>1630636</v>
+        <v>1523488</v>
       </c>
       <c r="B606" s="1" t="n">
-        <v>29656</v>
+        <v>24896</v>
       </c>
       <c r="C606" s="1" t="n">
         <v>14161</v>
@@ -19510,17 +19510,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">30/01/2027</t>
+            <t xml:space="preserve">26/10/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="607" customHeight="1" ht="20">
       <c r="A607" s="1" t="n">
-        <v>1523488</v>
+        <v>1630636</v>
       </c>
       <c r="B607" s="1" t="n">
-        <v>24896</v>
+        <v>29656</v>
       </c>
       <c r="C607" s="1" t="n">
         <v>14161</v>
@@ -19542,7 +19542,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/10/2026</t>
+            <t xml:space="preserve">30/01/2027</t>
           </r>
         </is>
       </c>
@@ -21981,10 +21981,10 @@
     </row>
     <row r="684" customHeight="1" ht="20">
       <c r="A684" s="1" t="n">
-        <v>1598892</v>
+        <v>1635939</v>
       </c>
       <c r="B684" s="1" t="n">
-        <v>27486</v>
+        <v>29609</v>
       </c>
       <c r="C684" s="1" t="n">
         <v>14137</v>
@@ -21999,24 +21999,24 @@
         </is>
       </c>
       <c r="E684" s="1" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F684" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">10/12/2026</t>
+            <t xml:space="preserve">13/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="685" customHeight="1" ht="20">
       <c r="A685" s="1" t="n">
-        <v>1635939</v>
+        <v>1598892</v>
       </c>
       <c r="B685" s="1" t="n">
-        <v>29609</v>
+        <v>27486</v>
       </c>
       <c r="C685" s="1" t="n">
         <v>14137</v>
@@ -22031,14 +22031,14 @@
         </is>
       </c>
       <c r="E685" s="1" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F685" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">13/11/2026</t>
+            <t xml:space="preserve">10/12/2026</t>
           </r>
         </is>
       </c>
@@ -40829,10 +40829,10 @@
     </row>
     <row r="1273" customHeight="1" ht="20">
       <c r="A1273" s="1" t="n">
-        <v>1633775</v>
+        <v>1625869</v>
       </c>
       <c r="B1273" s="1" t="n">
-        <v>29593</v>
+        <v>43</v>
       </c>
       <c r="C1273" s="1" t="n">
         <v>30716</v>
@@ -40847,24 +40847,24 @@
         </is>
       </c>
       <c r="E1273" s="1" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F1273" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/02/2027</t>
+            <t xml:space="preserve">26/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1274" customHeight="1" ht="20">
       <c r="A1274" s="1" t="n">
-        <v>1625869</v>
+        <v>1633775</v>
       </c>
       <c r="B1274" s="1" t="n">
-        <v>43</v>
+        <v>29593</v>
       </c>
       <c r="C1274" s="1" t="n">
         <v>30716</v>
@@ -40879,24 +40879,24 @@
         </is>
       </c>
       <c r="E1274" s="1" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F1274" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">04/02/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1275" customHeight="1" ht="20">
       <c r="A1275" s="1" t="n">
-        <v>1633775</v>
+        <v>1625869</v>
       </c>
       <c r="B1275" s="1" t="n">
-        <v>29593</v>
+        <v>43</v>
       </c>
       <c r="C1275" s="1" t="n">
         <v>30717</v>
@@ -40918,17 +40918,17 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">04/02/2027</t>
+            <t xml:space="preserve">26/01/2027</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1276" customHeight="1" ht="20">
       <c r="A1276" s="1" t="n">
-        <v>1625869</v>
+        <v>1633775</v>
       </c>
       <c r="B1276" s="1" t="n">
-        <v>43</v>
+        <v>29593</v>
       </c>
       <c r="C1276" s="1" t="n">
         <v>30717</v>
@@ -40950,7 +40950,7 @@
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">26/01/2027</t>
+            <t xml:space="preserve">04/02/2027</t>
           </r>
         </is>
       </c>
@@ -48733,10 +48733,10 @@
     </row>
     <row r="1520" customHeight="1" ht="20">
       <c r="A1520" s="1" t="n">
-        <v>1470722</v>
+        <v>1638359</v>
       </c>
       <c r="B1520" s="1" t="n">
-        <v>24616</v>
+        <v>29613</v>
       </c>
       <c r="C1520" s="1" t="n">
         <v>32670</v>
@@ -48751,24 +48751,24 @@
         </is>
       </c>
       <c r="E1520" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1520" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">27/10/2026</t>
+            <t xml:space="preserve">18/11/2026</t>
           </r>
         </is>
       </c>
     </row>
     <row r="1521" customHeight="1" ht="20">
       <c r="A1521" s="1" t="n">
-        <v>1638359</v>
+        <v>1470722</v>
       </c>
       <c r="B1521" s="1" t="n">
-        <v>29613</v>
+        <v>24616</v>
       </c>
       <c r="C1521" s="1" t="n">
         <v>32670</v>
@@ -48783,14 +48783,14 @@
         </is>
       </c>
       <c r="E1521" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F1521" s="1" t="inlineStr">
         <is>
           <r>
             <rPr>
        </rPr>
-            <t xml:space="preserve">18/11/2026</t>
+            <t xml:space="preserve">27/10/2026</t>
           </r>
         </is>
       </c>
